--- a/excel-service/plantilla_asistencia.xlsx
+++ b/excel-service/plantilla_asistencia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ricardoaguilar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAC55D63-2288-2740-A9D2-EB3C5773894E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFBA564-F6AB-984D-A4D6-A1B60672B85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1ER TRIMESTRE" sheetId="5" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6113" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6112" uniqueCount="56">
   <si>
     <t>UNIDAD EDUCATIVA PARTICULAR  “TIA BLANQUITA”</t>
   </si>
@@ -148,9 +148,6 @@
   </si>
   <si>
     <t>DOCENTE TUTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGUILAR ORELLANA  FREDDY JOEL </t>
   </si>
   <si>
     <t>LCDA. LXXXXXXXXXXXXXXXXXXX</t>
@@ -1135,32 +1132,53 @@
     <xf numFmtId="0" fontId="7" fillId="23" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1209,63 +1227,32 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="23" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1283,6 +1270,16 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3699,598 +3696,598 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:77" ht="28" x14ac:dyDescent="0.2">
-      <c r="A1" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
-      <c r="AB1" s="44"/>
-      <c r="AC1" s="44"/>
-      <c r="AD1" s="44"/>
-      <c r="AE1" s="44"/>
-      <c r="AF1" s="44"/>
-      <c r="AG1" s="44"/>
-      <c r="AH1" s="44"/>
-      <c r="AI1" s="44"/>
-      <c r="AJ1" s="44"/>
-      <c r="AK1" s="44"/>
-      <c r="AL1" s="44"/>
-      <c r="AM1" s="44"/>
-      <c r="AN1" s="44"/>
-      <c r="AO1" s="44"/>
-      <c r="AP1" s="44"/>
-      <c r="AQ1" s="44"/>
-      <c r="AR1" s="44"/>
-      <c r="AS1" s="44"/>
-      <c r="AT1" s="44"/>
-      <c r="AU1" s="44"/>
-      <c r="AV1" s="44"/>
-      <c r="AW1" s="44"/>
-      <c r="AX1" s="44"/>
-      <c r="AY1" s="44"/>
-      <c r="AZ1" s="44"/>
-      <c r="BA1" s="44"/>
-      <c r="BB1" s="44"/>
-      <c r="BC1" s="44"/>
-      <c r="BD1" s="44"/>
-      <c r="BE1" s="44"/>
-      <c r="BF1" s="44"/>
-      <c r="BG1" s="44"/>
-      <c r="BH1" s="44"/>
-      <c r="BI1" s="44"/>
-      <c r="BJ1" s="44"/>
-      <c r="BK1" s="44"/>
-      <c r="BL1" s="44"/>
-      <c r="BM1" s="44"/>
-      <c r="BN1" s="44"/>
-      <c r="BO1" s="44"/>
-      <c r="BP1" s="44"/>
-      <c r="BQ1" s="44"/>
-      <c r="BR1" s="44"/>
-      <c r="BS1" s="44"/>
-      <c r="BT1" s="44"/>
-      <c r="BU1" s="44"/>
-      <c r="BV1" s="44"/>
-      <c r="BW1" s="44"/>
-      <c r="BX1" s="44"/>
-      <c r="BY1" s="44"/>
+      <c r="A1" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
+      <c r="M1" s="90"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="90"/>
+      <c r="Q1" s="90"/>
+      <c r="R1" s="90"/>
+      <c r="S1" s="90"/>
+      <c r="T1" s="90"/>
+      <c r="U1" s="90"/>
+      <c r="V1" s="90"/>
+      <c r="W1" s="90"/>
+      <c r="X1" s="90"/>
+      <c r="Y1" s="90"/>
+      <c r="Z1" s="90"/>
+      <c r="AA1" s="90"/>
+      <c r="AB1" s="90"/>
+      <c r="AC1" s="90"/>
+      <c r="AD1" s="90"/>
+      <c r="AE1" s="90"/>
+      <c r="AF1" s="90"/>
+      <c r="AG1" s="90"/>
+      <c r="AH1" s="90"/>
+      <c r="AI1" s="90"/>
+      <c r="AJ1" s="90"/>
+      <c r="AK1" s="90"/>
+      <c r="AL1" s="90"/>
+      <c r="AM1" s="90"/>
+      <c r="AN1" s="90"/>
+      <c r="AO1" s="90"/>
+      <c r="AP1" s="90"/>
+      <c r="AQ1" s="90"/>
+      <c r="AR1" s="90"/>
+      <c r="AS1" s="90"/>
+      <c r="AT1" s="90"/>
+      <c r="AU1" s="90"/>
+      <c r="AV1" s="90"/>
+      <c r="AW1" s="90"/>
+      <c r="AX1" s="90"/>
+      <c r="AY1" s="90"/>
+      <c r="AZ1" s="90"/>
+      <c r="BA1" s="90"/>
+      <c r="BB1" s="90"/>
+      <c r="BC1" s="90"/>
+      <c r="BD1" s="90"/>
+      <c r="BE1" s="90"/>
+      <c r="BF1" s="90"/>
+      <c r="BG1" s="90"/>
+      <c r="BH1" s="90"/>
+      <c r="BI1" s="90"/>
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
     </row>
     <row r="2" spans="1:77" x14ac:dyDescent="0.2">
-      <c r="A2" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="46"/>
-      <c r="AC2" s="46"/>
-      <c r="AD2" s="46"/>
-      <c r="AE2" s="46"/>
-      <c r="AF2" s="46"/>
-      <c r="AG2" s="46"/>
-      <c r="AH2" s="46"/>
-      <c r="AI2" s="46"/>
-      <c r="AJ2" s="46"/>
-      <c r="AK2" s="46"/>
-      <c r="AL2" s="46"/>
-      <c r="AM2" s="46"/>
-      <c r="AN2" s="46"/>
-      <c r="AO2" s="46"/>
-      <c r="AP2" s="46"/>
-      <c r="AQ2" s="46"/>
-      <c r="AR2" s="46"/>
-      <c r="AS2" s="46"/>
-      <c r="AT2" s="46"/>
-      <c r="AU2" s="46"/>
-      <c r="AV2" s="46"/>
-      <c r="AW2" s="46"/>
-      <c r="AX2" s="46"/>
-      <c r="AY2" s="46"/>
-      <c r="AZ2" s="46"/>
-      <c r="BA2" s="46"/>
-      <c r="BB2" s="46"/>
-      <c r="BC2" s="46"/>
-      <c r="BD2" s="46"/>
-      <c r="BE2" s="46"/>
-      <c r="BF2" s="46"/>
-      <c r="BG2" s="46"/>
-      <c r="BH2" s="46"/>
-      <c r="BI2" s="46"/>
-      <c r="BJ2" s="46"/>
-      <c r="BK2" s="46"/>
-      <c r="BL2" s="46"/>
-      <c r="BM2" s="46"/>
-      <c r="BN2" s="46"/>
-      <c r="BO2" s="46"/>
-      <c r="BP2" s="46"/>
-      <c r="BQ2" s="46"/>
-      <c r="BR2" s="46"/>
-      <c r="BS2" s="46"/>
-      <c r="BT2" s="46"/>
-      <c r="BU2" s="46"/>
-      <c r="BV2" s="46"/>
-      <c r="BW2" s="46"/>
-      <c r="BX2" s="46"/>
-      <c r="BY2" s="46"/>
+      <c r="A2" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+      <c r="R2" s="92"/>
+      <c r="S2" s="92"/>
+      <c r="T2" s="92"/>
+      <c r="U2" s="92"/>
+      <c r="V2" s="92"/>
+      <c r="W2" s="92"/>
+      <c r="X2" s="92"/>
+      <c r="Y2" s="92"/>
+      <c r="Z2" s="92"/>
+      <c r="AA2" s="92"/>
+      <c r="AB2" s="92"/>
+      <c r="AC2" s="92"/>
+      <c r="AD2" s="92"/>
+      <c r="AE2" s="92"/>
+      <c r="AF2" s="92"/>
+      <c r="AG2" s="92"/>
+      <c r="AH2" s="92"/>
+      <c r="AI2" s="92"/>
+      <c r="AJ2" s="92"/>
+      <c r="AK2" s="92"/>
+      <c r="AL2" s="92"/>
+      <c r="AM2" s="92"/>
+      <c r="AN2" s="92"/>
+      <c r="AO2" s="92"/>
+      <c r="AP2" s="92"/>
+      <c r="AQ2" s="92"/>
+      <c r="AR2" s="92"/>
+      <c r="AS2" s="92"/>
+      <c r="AT2" s="92"/>
+      <c r="AU2" s="92"/>
+      <c r="AV2" s="92"/>
+      <c r="AW2" s="92"/>
+      <c r="AX2" s="92"/>
+      <c r="AY2" s="92"/>
+      <c r="AZ2" s="92"/>
+      <c r="BA2" s="92"/>
+      <c r="BB2" s="92"/>
+      <c r="BC2" s="92"/>
+      <c r="BD2" s="92"/>
+      <c r="BE2" s="92"/>
+      <c r="BF2" s="92"/>
+      <c r="BG2" s="92"/>
+      <c r="BH2" s="92"/>
+      <c r="BI2" s="92"/>
+      <c r="BJ2" s="92"/>
+      <c r="BK2" s="92"/>
+      <c r="BL2" s="92"/>
+      <c r="BM2" s="92"/>
+      <c r="BN2" s="92"/>
+      <c r="BO2" s="92"/>
+      <c r="BP2" s="92"/>
+      <c r="BQ2" s="92"/>
+      <c r="BR2" s="92"/>
+      <c r="BS2" s="92"/>
+      <c r="BT2" s="92"/>
+      <c r="BU2" s="92"/>
+      <c r="BV2" s="92"/>
+      <c r="BW2" s="92"/>
+      <c r="BX2" s="92"/>
+      <c r="BY2" s="92"/>
     </row>
     <row r="3" spans="1:77" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="46"/>
-      <c r="R3" s="46"/>
-      <c r="S3" s="46"/>
-      <c r="T3" s="46"/>
-      <c r="U3" s="46"/>
-      <c r="V3" s="46"/>
-      <c r="W3" s="46"/>
-      <c r="X3" s="46"/>
-      <c r="Y3" s="46"/>
-      <c r="Z3" s="46"/>
-      <c r="AA3" s="46"/>
-      <c r="AB3" s="46"/>
-      <c r="AC3" s="46"/>
-      <c r="AD3" s="46"/>
-      <c r="AE3" s="46"/>
-      <c r="AF3" s="46"/>
-      <c r="AG3" s="46"/>
-      <c r="AH3" s="46"/>
-      <c r="AI3" s="46"/>
-      <c r="AJ3" s="46"/>
-      <c r="AK3" s="46"/>
-      <c r="AL3" s="46"/>
-      <c r="AM3" s="46"/>
-      <c r="AN3" s="46"/>
-      <c r="AO3" s="46"/>
-      <c r="AP3" s="46"/>
-      <c r="AQ3" s="46"/>
-      <c r="AR3" s="46"/>
-      <c r="AS3" s="46"/>
-      <c r="AT3" s="46"/>
-      <c r="AU3" s="46"/>
-      <c r="AV3" s="46"/>
-      <c r="AW3" s="46"/>
-      <c r="AX3" s="46"/>
-      <c r="AY3" s="46"/>
-      <c r="AZ3" s="46"/>
-      <c r="BA3" s="46"/>
-      <c r="BB3" s="46"/>
-      <c r="BC3" s="46"/>
-      <c r="BD3" s="46"/>
-      <c r="BE3" s="46"/>
-      <c r="BF3" s="46"/>
-      <c r="BG3" s="46"/>
-      <c r="BH3" s="46"/>
-      <c r="BI3" s="46"/>
-      <c r="BJ3" s="46"/>
-      <c r="BK3" s="46"/>
-      <c r="BL3" s="46"/>
-      <c r="BM3" s="46"/>
-      <c r="BN3" s="46"/>
-      <c r="BO3" s="46"/>
-      <c r="BP3" s="46"/>
-      <c r="BQ3" s="46"/>
-      <c r="BR3" s="46"/>
-      <c r="BS3" s="46"/>
-      <c r="BT3" s="46"/>
-      <c r="BU3" s="46"/>
-      <c r="BV3" s="46"/>
-      <c r="BW3" s="46"/>
-      <c r="BX3" s="46"/>
-      <c r="BY3" s="46"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="92"/>
+      <c r="Q3" s="92"/>
+      <c r="R3" s="92"/>
+      <c r="S3" s="92"/>
+      <c r="T3" s="92"/>
+      <c r="U3" s="92"/>
+      <c r="V3" s="92"/>
+      <c r="W3" s="92"/>
+      <c r="X3" s="92"/>
+      <c r="Y3" s="92"/>
+      <c r="Z3" s="92"/>
+      <c r="AA3" s="92"/>
+      <c r="AB3" s="92"/>
+      <c r="AC3" s="92"/>
+      <c r="AD3" s="92"/>
+      <c r="AE3" s="92"/>
+      <c r="AF3" s="92"/>
+      <c r="AG3" s="92"/>
+      <c r="AH3" s="92"/>
+      <c r="AI3" s="92"/>
+      <c r="AJ3" s="92"/>
+      <c r="AK3" s="92"/>
+      <c r="AL3" s="92"/>
+      <c r="AM3" s="92"/>
+      <c r="AN3" s="92"/>
+      <c r="AO3" s="92"/>
+      <c r="AP3" s="92"/>
+      <c r="AQ3" s="92"/>
+      <c r="AR3" s="92"/>
+      <c r="AS3" s="92"/>
+      <c r="AT3" s="92"/>
+      <c r="AU3" s="92"/>
+      <c r="AV3" s="92"/>
+      <c r="AW3" s="92"/>
+      <c r="AX3" s="92"/>
+      <c r="AY3" s="92"/>
+      <c r="AZ3" s="92"/>
+      <c r="BA3" s="92"/>
+      <c r="BB3" s="92"/>
+      <c r="BC3" s="92"/>
+      <c r="BD3" s="92"/>
+      <c r="BE3" s="92"/>
+      <c r="BF3" s="92"/>
+      <c r="BG3" s="92"/>
+      <c r="BH3" s="92"/>
+      <c r="BI3" s="92"/>
+      <c r="BJ3" s="92"/>
+      <c r="BK3" s="92"/>
+      <c r="BL3" s="92"/>
+      <c r="BM3" s="92"/>
+      <c r="BN3" s="92"/>
+      <c r="BO3" s="92"/>
+      <c r="BP3" s="92"/>
+      <c r="BQ3" s="92"/>
+      <c r="BR3" s="92"/>
+      <c r="BS3" s="92"/>
+      <c r="BT3" s="92"/>
+      <c r="BU3" s="92"/>
+      <c r="BV3" s="92"/>
+      <c r="BW3" s="92"/>
+      <c r="BX3" s="92"/>
+      <c r="BY3" s="92"/>
     </row>
     <row r="4" spans="1:77" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="W4" s="48"/>
-      <c r="X4" s="48"/>
-      <c r="Y4" s="48"/>
-      <c r="Z4" s="48"/>
-      <c r="AA4" s="48"/>
-      <c r="AB4" s="48"/>
-      <c r="AC4" s="48"/>
-      <c r="AD4" s="48"/>
-      <c r="AE4" s="48"/>
-      <c r="AF4" s="48"/>
-      <c r="AG4" s="48"/>
-      <c r="AH4" s="48"/>
-      <c r="AI4" s="48"/>
-      <c r="AJ4" s="48"/>
-      <c r="AK4" s="48"/>
-      <c r="AL4" s="48"/>
-      <c r="AM4" s="48"/>
-      <c r="AN4" s="48"/>
-      <c r="AO4" s="48"/>
-      <c r="AP4" s="48"/>
-      <c r="AQ4" s="48"/>
-      <c r="AR4" s="48"/>
-      <c r="AS4" s="48"/>
-      <c r="AT4" s="48"/>
-      <c r="AU4" s="48"/>
-      <c r="AV4" s="48"/>
-      <c r="AW4" s="48"/>
-      <c r="AX4" s="48"/>
-      <c r="AY4" s="48"/>
-      <c r="AZ4" s="48"/>
-      <c r="BA4" s="48"/>
-      <c r="BB4" s="48"/>
-      <c r="BC4" s="48"/>
-      <c r="BD4" s="48"/>
-      <c r="BE4" s="48"/>
-      <c r="BF4" s="48"/>
-      <c r="BG4" s="48"/>
-      <c r="BH4" s="48"/>
-      <c r="BI4" s="48"/>
-      <c r="BJ4" s="48"/>
-      <c r="BK4" s="48"/>
-      <c r="BL4" s="48"/>
-      <c r="BM4" s="48"/>
-      <c r="BN4" s="48"/>
-      <c r="BO4" s="48"/>
-      <c r="BP4" s="48"/>
-      <c r="BQ4" s="48"/>
-      <c r="BR4" s="48"/>
-      <c r="BS4" s="48"/>
-      <c r="BT4" s="48"/>
-      <c r="BU4" s="48"/>
-      <c r="BV4" s="48"/>
-      <c r="BW4" s="48"/>
-      <c r="BX4" s="48"/>
-      <c r="BY4" s="48"/>
+      <c r="A4" s="93" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="94"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="94"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="94"/>
+      <c r="V4" s="94"/>
+      <c r="W4" s="94"/>
+      <c r="X4" s="94"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
+      <c r="AB4" s="94"/>
+      <c r="AC4" s="94"/>
+      <c r="AD4" s="94"/>
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="94"/>
+      <c r="AQ4" s="94"/>
+      <c r="AR4" s="94"/>
+      <c r="AS4" s="94"/>
+      <c r="AT4" s="94"/>
+      <c r="AU4" s="94"/>
+      <c r="AV4" s="94"/>
+      <c r="AW4" s="94"/>
+      <c r="AX4" s="94"/>
+      <c r="AY4" s="94"/>
+      <c r="AZ4" s="94"/>
+      <c r="BA4" s="94"/>
+      <c r="BB4" s="94"/>
+      <c r="BC4" s="94"/>
+      <c r="BD4" s="94"/>
+      <c r="BE4" s="94"/>
+      <c r="BF4" s="94"/>
+      <c r="BG4" s="94"/>
+      <c r="BH4" s="94"/>
+      <c r="BI4" s="94"/>
+      <c r="BJ4" s="94"/>
+      <c r="BK4" s="94"/>
+      <c r="BL4" s="94"/>
+      <c r="BM4" s="94"/>
+      <c r="BN4" s="94"/>
+      <c r="BO4" s="94"/>
+      <c r="BP4" s="94"/>
+      <c r="BQ4" s="94"/>
+      <c r="BR4" s="94"/>
+      <c r="BS4" s="94"/>
+      <c r="BT4" s="94"/>
+      <c r="BU4" s="94"/>
+      <c r="BV4" s="94"/>
+      <c r="BW4" s="94"/>
+      <c r="BX4" s="94"/>
+      <c r="BY4" s="94"/>
     </row>
     <row r="5" spans="1:77" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="44"/>
-      <c r="T5" s="44"/>
-      <c r="U5" s="44"/>
-      <c r="V5" s="44"/>
-      <c r="W5" s="44"/>
-      <c r="X5" s="44"/>
-      <c r="Y5" s="44"/>
-      <c r="Z5" s="44"/>
-      <c r="AA5" s="44"/>
-      <c r="AB5" s="44"/>
-      <c r="AC5" s="44"/>
-      <c r="AD5" s="44"/>
-      <c r="AE5" s="44"/>
-      <c r="AF5" s="44"/>
-      <c r="AG5" s="44"/>
-      <c r="AH5" s="44"/>
-      <c r="AI5" s="44"/>
-      <c r="AJ5" s="44"/>
-      <c r="AK5" s="44"/>
-      <c r="AL5" s="44"/>
-      <c r="AM5" s="44"/>
-      <c r="AN5" s="44"/>
-      <c r="AO5" s="44"/>
-      <c r="AP5" s="44"/>
-      <c r="AQ5" s="44"/>
-      <c r="AR5" s="44"/>
-      <c r="AS5" s="44"/>
-      <c r="AT5" s="44"/>
-      <c r="AU5" s="44"/>
-      <c r="AV5" s="44"/>
-      <c r="AW5" s="44"/>
-      <c r="AX5" s="44"/>
-      <c r="AY5" s="44"/>
-      <c r="AZ5" s="44"/>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44"/>
-      <c r="BC5" s="44"/>
-      <c r="BD5" s="44"/>
-      <c r="BE5" s="44"/>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
-      <c r="BI5" s="44"/>
-      <c r="BJ5" s="44"/>
-      <c r="BK5" s="44"/>
-      <c r="BL5" s="44"/>
-      <c r="BM5" s="44"/>
-      <c r="BN5" s="44"/>
-      <c r="BO5" s="44"/>
-      <c r="BP5" s="44"/>
-      <c r="BQ5" s="44"/>
-      <c r="BR5" s="44"/>
-      <c r="BS5" s="44"/>
-      <c r="BT5" s="44"/>
-      <c r="BU5" s="44"/>
-      <c r="BV5" s="44"/>
-      <c r="BW5" s="44"/>
-      <c r="BX5" s="44"/>
-      <c r="BY5" s="44"/>
+      <c r="A5" s="89" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="90"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
+      <c r="W5" s="90"/>
+      <c r="X5" s="90"/>
+      <c r="Y5" s="90"/>
+      <c r="Z5" s="90"/>
+      <c r="AA5" s="90"/>
+      <c r="AB5" s="90"/>
+      <c r="AC5" s="90"/>
+      <c r="AD5" s="90"/>
+      <c r="AE5" s="90"/>
+      <c r="AF5" s="90"/>
+      <c r="AG5" s="90"/>
+      <c r="AH5" s="90"/>
+      <c r="AI5" s="90"/>
+      <c r="AJ5" s="90"/>
+      <c r="AK5" s="90"/>
+      <c r="AL5" s="90"/>
+      <c r="AM5" s="90"/>
+      <c r="AN5" s="90"/>
+      <c r="AO5" s="90"/>
+      <c r="AP5" s="90"/>
+      <c r="AQ5" s="90"/>
+      <c r="AR5" s="90"/>
+      <c r="AS5" s="90"/>
+      <c r="AT5" s="90"/>
+      <c r="AU5" s="90"/>
+      <c r="AV5" s="90"/>
+      <c r="AW5" s="90"/>
+      <c r="AX5" s="90"/>
+      <c r="AY5" s="90"/>
+      <c r="AZ5" s="90"/>
+      <c r="BA5" s="90"/>
+      <c r="BB5" s="90"/>
+      <c r="BC5" s="90"/>
+      <c r="BD5" s="90"/>
+      <c r="BE5" s="90"/>
+      <c r="BF5" s="90"/>
+      <c r="BG5" s="90"/>
+      <c r="BH5" s="90"/>
+      <c r="BI5" s="90"/>
+      <c r="BJ5" s="90"/>
+      <c r="BK5" s="90"/>
+      <c r="BL5" s="90"/>
+      <c r="BM5" s="90"/>
+      <c r="BN5" s="90"/>
+      <c r="BO5" s="90"/>
+      <c r="BP5" s="90"/>
+      <c r="BQ5" s="90"/>
+      <c r="BR5" s="90"/>
+      <c r="BS5" s="90"/>
+      <c r="BT5" s="90"/>
+      <c r="BU5" s="90"/>
+      <c r="BV5" s="90"/>
+      <c r="BW5" s="90"/>
+      <c r="BX5" s="90"/>
+      <c r="BY5" s="90"/>
     </row>
     <row r="6" spans="1:77" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="38" t="s">
+      <c r="A6" s="95" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="96"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="39"/>
-      <c r="U6" s="39"/>
-      <c r="V6" s="40"/>
-      <c r="W6" s="41" t="s">
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="98"/>
+      <c r="K6" s="98"/>
+      <c r="L6" s="98"/>
+      <c r="M6" s="98"/>
+      <c r="N6" s="98"/>
+      <c r="O6" s="98"/>
+      <c r="P6" s="98"/>
+      <c r="Q6" s="98"/>
+      <c r="R6" s="98"/>
+      <c r="S6" s="98"/>
+      <c r="T6" s="98"/>
+      <c r="U6" s="98"/>
+      <c r="V6" s="99"/>
+      <c r="W6" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="X6" s="39"/>
-      <c r="Y6" s="39"/>
-      <c r="Z6" s="39"/>
-      <c r="AA6" s="39"/>
-      <c r="AB6" s="39"/>
-      <c r="AC6" s="39"/>
-      <c r="AD6" s="39"/>
-      <c r="AE6" s="39"/>
-      <c r="AF6" s="39"/>
-      <c r="AG6" s="39"/>
-      <c r="AH6" s="39"/>
-      <c r="AI6" s="39"/>
-      <c r="AJ6" s="39"/>
-      <c r="AK6" s="39"/>
-      <c r="AL6" s="39"/>
-      <c r="AM6" s="39"/>
-      <c r="AN6" s="39"/>
-      <c r="AO6" s="39"/>
-      <c r="AP6" s="42"/>
-      <c r="AQ6" s="42"/>
-      <c r="AR6" s="40"/>
-      <c r="AS6" s="41" t="s">
+      <c r="X6" s="98"/>
+      <c r="Y6" s="98"/>
+      <c r="Z6" s="98"/>
+      <c r="AA6" s="98"/>
+      <c r="AB6" s="98"/>
+      <c r="AC6" s="98"/>
+      <c r="AD6" s="98"/>
+      <c r="AE6" s="98"/>
+      <c r="AF6" s="98"/>
+      <c r="AG6" s="98"/>
+      <c r="AH6" s="98"/>
+      <c r="AI6" s="98"/>
+      <c r="AJ6" s="98"/>
+      <c r="AK6" s="98"/>
+      <c r="AL6" s="98"/>
+      <c r="AM6" s="98"/>
+      <c r="AN6" s="98"/>
+      <c r="AO6" s="98"/>
+      <c r="AP6" s="101"/>
+      <c r="AQ6" s="101"/>
+      <c r="AR6" s="99"/>
+      <c r="AS6" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="AT6" s="39"/>
-      <c r="AU6" s="39"/>
-      <c r="AV6" s="39"/>
-      <c r="AW6" s="39"/>
-      <c r="AX6" s="39"/>
-      <c r="AY6" s="39"/>
-      <c r="AZ6" s="39"/>
-      <c r="BA6" s="39"/>
-      <c r="BB6" s="39"/>
-      <c r="BC6" s="39"/>
-      <c r="BD6" s="39"/>
-      <c r="BE6" s="39"/>
-      <c r="BF6" s="39"/>
-      <c r="BG6" s="39"/>
-      <c r="BH6" s="39"/>
-      <c r="BI6" s="39"/>
-      <c r="BJ6" s="39"/>
-      <c r="BK6" s="39"/>
-      <c r="BL6" s="39"/>
-      <c r="BM6" s="39"/>
-      <c r="BN6" s="39"/>
-      <c r="BO6" s="40"/>
-      <c r="BP6" s="41" t="s">
+      <c r="AT6" s="98"/>
+      <c r="AU6" s="98"/>
+      <c r="AV6" s="98"/>
+      <c r="AW6" s="98"/>
+      <c r="AX6" s="98"/>
+      <c r="AY6" s="98"/>
+      <c r="AZ6" s="98"/>
+      <c r="BA6" s="98"/>
+      <c r="BB6" s="98"/>
+      <c r="BC6" s="98"/>
+      <c r="BD6" s="98"/>
+      <c r="BE6" s="98"/>
+      <c r="BF6" s="98"/>
+      <c r="BG6" s="98"/>
+      <c r="BH6" s="98"/>
+      <c r="BI6" s="98"/>
+      <c r="BJ6" s="98"/>
+      <c r="BK6" s="98"/>
+      <c r="BL6" s="98"/>
+      <c r="BM6" s="98"/>
+      <c r="BN6" s="98"/>
+      <c r="BO6" s="99"/>
+      <c r="BP6" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="BQ6" s="39"/>
-      <c r="BR6" s="39"/>
-      <c r="BS6" s="39"/>
-      <c r="BT6" s="39"/>
-      <c r="BU6" s="79" t="s">
+      <c r="BQ6" s="98"/>
+      <c r="BR6" s="98"/>
+      <c r="BS6" s="98"/>
+      <c r="BT6" s="98"/>
+      <c r="BU6" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="BV6" s="82" t="s">
+      <c r="BV6" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="BW6" s="85" t="s">
+      <c r="BW6" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="BX6" s="88" t="s">
+      <c r="BX6" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="BY6" s="91" t="s">
-        <v>48</v>
+      <c r="BY6" s="55" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:77" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="52" t="s">
+      <c r="A7" s="58"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
-      <c r="R7" s="53"/>
-      <c r="S7" s="53"/>
-      <c r="T7" s="53"/>
-      <c r="U7" s="53"/>
-      <c r="V7" s="54"/>
-      <c r="W7" s="58" t="s">
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="62"/>
+      <c r="S7" s="62"/>
+      <c r="T7" s="62"/>
+      <c r="U7" s="62"/>
+      <c r="V7" s="63"/>
+      <c r="W7" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="X7" s="53"/>
-      <c r="Y7" s="53"/>
-      <c r="Z7" s="53"/>
-      <c r="AA7" s="53"/>
-      <c r="AB7" s="53"/>
-      <c r="AC7" s="53"/>
-      <c r="AD7" s="53"/>
-      <c r="AE7" s="53"/>
-      <c r="AF7" s="53"/>
-      <c r="AG7" s="53"/>
-      <c r="AH7" s="53"/>
-      <c r="AI7" s="53"/>
-      <c r="AJ7" s="53"/>
-      <c r="AK7" s="53"/>
-      <c r="AL7" s="53"/>
-      <c r="AM7" s="53"/>
-      <c r="AN7" s="53"/>
-      <c r="AO7" s="53"/>
-      <c r="AP7" s="59"/>
-      <c r="AQ7" s="59"/>
-      <c r="AR7" s="54"/>
-      <c r="AS7" s="62" t="s">
+      <c r="X7" s="62"/>
+      <c r="Y7" s="62"/>
+      <c r="Z7" s="62"/>
+      <c r="AA7" s="62"/>
+      <c r="AB7" s="62"/>
+      <c r="AC7" s="62"/>
+      <c r="AD7" s="62"/>
+      <c r="AE7" s="62"/>
+      <c r="AF7" s="62"/>
+      <c r="AG7" s="62"/>
+      <c r="AH7" s="62"/>
+      <c r="AI7" s="62"/>
+      <c r="AJ7" s="62"/>
+      <c r="AK7" s="62"/>
+      <c r="AL7" s="62"/>
+      <c r="AM7" s="62"/>
+      <c r="AN7" s="62"/>
+      <c r="AO7" s="62"/>
+      <c r="AP7" s="68"/>
+      <c r="AQ7" s="68"/>
+      <c r="AR7" s="63"/>
+      <c r="AS7" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="AT7" s="63"/>
-      <c r="AU7" s="63"/>
-      <c r="AV7" s="63"/>
-      <c r="AW7" s="63"/>
-      <c r="AX7" s="63"/>
-      <c r="AY7" s="63"/>
-      <c r="AZ7" s="63"/>
-      <c r="BA7" s="63"/>
-      <c r="BB7" s="63"/>
-      <c r="BC7" s="63"/>
-      <c r="BD7" s="63"/>
-      <c r="BE7" s="63"/>
-      <c r="BF7" s="63"/>
-      <c r="BG7" s="63"/>
-      <c r="BH7" s="63"/>
-      <c r="BI7" s="63"/>
-      <c r="BJ7" s="63"/>
-      <c r="BK7" s="63"/>
-      <c r="BL7" s="63"/>
-      <c r="BM7" s="63"/>
-      <c r="BN7" s="63"/>
-      <c r="BO7" s="64"/>
-      <c r="BP7" s="68" t="s">
+      <c r="AT7" s="72"/>
+      <c r="AU7" s="72"/>
+      <c r="AV7" s="72"/>
+      <c r="AW7" s="72"/>
+      <c r="AX7" s="72"/>
+      <c r="AY7" s="72"/>
+      <c r="AZ7" s="72"/>
+      <c r="BA7" s="72"/>
+      <c r="BB7" s="72"/>
+      <c r="BC7" s="72"/>
+      <c r="BD7" s="72"/>
+      <c r="BE7" s="72"/>
+      <c r="BF7" s="72"/>
+      <c r="BG7" s="72"/>
+      <c r="BH7" s="72"/>
+      <c r="BI7" s="72"/>
+      <c r="BJ7" s="72"/>
+      <c r="BK7" s="72"/>
+      <c r="BL7" s="72"/>
+      <c r="BM7" s="72"/>
+      <c r="BN7" s="72"/>
+      <c r="BO7" s="73"/>
+      <c r="BP7" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="BQ7" s="63"/>
-      <c r="BR7" s="63"/>
-      <c r="BS7" s="63"/>
-      <c r="BT7" s="63"/>
-      <c r="BU7" s="80"/>
-      <c r="BV7" s="83"/>
-      <c r="BW7" s="86"/>
-      <c r="BX7" s="89"/>
-      <c r="BY7" s="92"/>
+      <c r="BQ7" s="72"/>
+      <c r="BR7" s="72"/>
+      <c r="BS7" s="72"/>
+      <c r="BT7" s="72"/>
+      <c r="BU7" s="44"/>
+      <c r="BV7" s="47"/>
+      <c r="BW7" s="50"/>
+      <c r="BX7" s="53"/>
+      <c r="BY7" s="56"/>
     </row>
     <row r="8" spans="1:77" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="79" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -4299,176 +4296,176 @@
       <c r="C8" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="55"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="56"/>
-      <c r="P8" s="56"/>
-      <c r="Q8" s="56"/>
-      <c r="R8" s="56"/>
-      <c r="S8" s="56"/>
-      <c r="T8" s="56"/>
-      <c r="U8" s="56"/>
-      <c r="V8" s="57"/>
-      <c r="W8" s="60"/>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="56"/>
-      <c r="Z8" s="56"/>
-      <c r="AA8" s="56"/>
-      <c r="AB8" s="56"/>
-      <c r="AC8" s="56"/>
-      <c r="AD8" s="56"/>
-      <c r="AE8" s="56"/>
-      <c r="AF8" s="56"/>
-      <c r="AG8" s="56"/>
-      <c r="AH8" s="56"/>
-      <c r="AI8" s="56"/>
-      <c r="AJ8" s="56"/>
-      <c r="AK8" s="56"/>
-      <c r="AL8" s="56"/>
-      <c r="AM8" s="56"/>
-      <c r="AN8" s="56"/>
-      <c r="AO8" s="56"/>
-      <c r="AP8" s="61"/>
-      <c r="AQ8" s="61"/>
-      <c r="AR8" s="57"/>
-      <c r="AS8" s="65"/>
-      <c r="AT8" s="66"/>
-      <c r="AU8" s="66"/>
-      <c r="AV8" s="66"/>
-      <c r="AW8" s="66"/>
-      <c r="AX8" s="66"/>
-      <c r="AY8" s="66"/>
-      <c r="AZ8" s="66"/>
-      <c r="BA8" s="66"/>
-      <c r="BB8" s="66"/>
-      <c r="BC8" s="66"/>
-      <c r="BD8" s="66"/>
-      <c r="BE8" s="66"/>
-      <c r="BF8" s="66"/>
-      <c r="BG8" s="66"/>
-      <c r="BH8" s="66"/>
-      <c r="BI8" s="66"/>
-      <c r="BJ8" s="66"/>
-      <c r="BK8" s="66"/>
-      <c r="BL8" s="66"/>
-      <c r="BM8" s="66"/>
-      <c r="BN8" s="66"/>
-      <c r="BO8" s="67"/>
-      <c r="BP8" s="69"/>
-      <c r="BQ8" s="66"/>
-      <c r="BR8" s="66"/>
-      <c r="BS8" s="66"/>
-      <c r="BT8" s="66"/>
-      <c r="BU8" s="80"/>
-      <c r="BV8" s="83"/>
-      <c r="BW8" s="86"/>
-      <c r="BX8" s="89"/>
-      <c r="BY8" s="92"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="65"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="65"/>
+      <c r="Q8" s="65"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="65"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="66"/>
+      <c r="W8" s="69"/>
+      <c r="X8" s="65"/>
+      <c r="Y8" s="65"/>
+      <c r="Z8" s="65"/>
+      <c r="AA8" s="65"/>
+      <c r="AB8" s="65"/>
+      <c r="AC8" s="65"/>
+      <c r="AD8" s="65"/>
+      <c r="AE8" s="65"/>
+      <c r="AF8" s="65"/>
+      <c r="AG8" s="65"/>
+      <c r="AH8" s="65"/>
+      <c r="AI8" s="65"/>
+      <c r="AJ8" s="65"/>
+      <c r="AK8" s="65"/>
+      <c r="AL8" s="65"/>
+      <c r="AM8" s="65"/>
+      <c r="AN8" s="65"/>
+      <c r="AO8" s="65"/>
+      <c r="AP8" s="70"/>
+      <c r="AQ8" s="70"/>
+      <c r="AR8" s="66"/>
+      <c r="AS8" s="74"/>
+      <c r="AT8" s="75"/>
+      <c r="AU8" s="75"/>
+      <c r="AV8" s="75"/>
+      <c r="AW8" s="75"/>
+      <c r="AX8" s="75"/>
+      <c r="AY8" s="75"/>
+      <c r="AZ8" s="75"/>
+      <c r="BA8" s="75"/>
+      <c r="BB8" s="75"/>
+      <c r="BC8" s="75"/>
+      <c r="BD8" s="75"/>
+      <c r="BE8" s="75"/>
+      <c r="BF8" s="75"/>
+      <c r="BG8" s="75"/>
+      <c r="BH8" s="75"/>
+      <c r="BI8" s="75"/>
+      <c r="BJ8" s="75"/>
+      <c r="BK8" s="75"/>
+      <c r="BL8" s="75"/>
+      <c r="BM8" s="75"/>
+      <c r="BN8" s="75"/>
+      <c r="BO8" s="76"/>
+      <c r="BP8" s="78"/>
+      <c r="BQ8" s="75"/>
+      <c r="BR8" s="75"/>
+      <c r="BS8" s="75"/>
+      <c r="BT8" s="75"/>
+      <c r="BU8" s="44"/>
+      <c r="BV8" s="47"/>
+      <c r="BW8" s="50"/>
+      <c r="BX8" s="53"/>
+      <c r="BY8" s="56"/>
     </row>
     <row r="9" spans="1:77" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="71"/>
+      <c r="A9" s="80"/>
       <c r="B9" s="25" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="26"/>
-      <c r="D9" s="73" t="s">
+      <c r="D9" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="74"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="74"/>
-      <c r="M9" s="74"/>
-      <c r="N9" s="74"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="74"/>
-      <c r="Q9" s="74"/>
-      <c r="R9" s="74"/>
-      <c r="S9" s="74"/>
-      <c r="T9" s="74"/>
-      <c r="U9" s="74"/>
-      <c r="V9" s="75"/>
-      <c r="W9" s="76" t="s">
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="83"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="83"/>
+      <c r="Q9" s="83"/>
+      <c r="R9" s="83"/>
+      <c r="S9" s="83"/>
+      <c r="T9" s="83"/>
+      <c r="U9" s="83"/>
+      <c r="V9" s="84"/>
+      <c r="W9" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="X9" s="74"/>
-      <c r="Y9" s="74"/>
-      <c r="Z9" s="74"/>
-      <c r="AA9" s="74"/>
-      <c r="AB9" s="74"/>
-      <c r="AC9" s="74"/>
-      <c r="AD9" s="74"/>
-      <c r="AE9" s="74"/>
-      <c r="AF9" s="74"/>
-      <c r="AG9" s="74"/>
-      <c r="AH9" s="74"/>
-      <c r="AI9" s="74"/>
-      <c r="AJ9" s="74"/>
-      <c r="AK9" s="74"/>
-      <c r="AL9" s="74"/>
-      <c r="AM9" s="74"/>
-      <c r="AN9" s="74"/>
-      <c r="AO9" s="74"/>
-      <c r="AP9" s="77"/>
-      <c r="AQ9" s="77"/>
-      <c r="AR9" s="75"/>
-      <c r="AS9" s="73" t="s">
+      <c r="X9" s="83"/>
+      <c r="Y9" s="83"/>
+      <c r="Z9" s="83"/>
+      <c r="AA9" s="83"/>
+      <c r="AB9" s="83"/>
+      <c r="AC9" s="83"/>
+      <c r="AD9" s="83"/>
+      <c r="AE9" s="83"/>
+      <c r="AF9" s="83"/>
+      <c r="AG9" s="83"/>
+      <c r="AH9" s="83"/>
+      <c r="AI9" s="83"/>
+      <c r="AJ9" s="83"/>
+      <c r="AK9" s="83"/>
+      <c r="AL9" s="83"/>
+      <c r="AM9" s="83"/>
+      <c r="AN9" s="83"/>
+      <c r="AO9" s="83"/>
+      <c r="AP9" s="86"/>
+      <c r="AQ9" s="86"/>
+      <c r="AR9" s="84"/>
+      <c r="AS9" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="AT9" s="74"/>
-      <c r="AU9" s="74"/>
-      <c r="AV9" s="74"/>
-      <c r="AW9" s="74"/>
-      <c r="AX9" s="74"/>
-      <c r="AY9" s="74"/>
-      <c r="AZ9" s="74"/>
-      <c r="BA9" s="74"/>
-      <c r="BB9" s="74"/>
-      <c r="BC9" s="74"/>
-      <c r="BD9" s="74"/>
-      <c r="BE9" s="74"/>
-      <c r="BF9" s="74"/>
-      <c r="BG9" s="74"/>
-      <c r="BH9" s="74"/>
-      <c r="BI9" s="74"/>
-      <c r="BJ9" s="74"/>
-      <c r="BK9" s="74"/>
-      <c r="BL9" s="74"/>
-      <c r="BM9" s="74"/>
-      <c r="BN9" s="74"/>
-      <c r="BO9" s="75"/>
-      <c r="BP9" s="76" t="s">
+      <c r="AT9" s="83"/>
+      <c r="AU9" s="83"/>
+      <c r="AV9" s="83"/>
+      <c r="AW9" s="83"/>
+      <c r="AX9" s="83"/>
+      <c r="AY9" s="83"/>
+      <c r="AZ9" s="83"/>
+      <c r="BA9" s="83"/>
+      <c r="BB9" s="83"/>
+      <c r="BC9" s="83"/>
+      <c r="BD9" s="83"/>
+      <c r="BE9" s="83"/>
+      <c r="BF9" s="83"/>
+      <c r="BG9" s="83"/>
+      <c r="BH9" s="83"/>
+      <c r="BI9" s="83"/>
+      <c r="BJ9" s="83"/>
+      <c r="BK9" s="83"/>
+      <c r="BL9" s="83"/>
+      <c r="BM9" s="83"/>
+      <c r="BN9" s="83"/>
+      <c r="BO9" s="84"/>
+      <c r="BP9" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="BQ9" s="74"/>
-      <c r="BR9" s="74"/>
-      <c r="BS9" s="74"/>
-      <c r="BT9" s="74"/>
-      <c r="BU9" s="80"/>
-      <c r="BV9" s="83"/>
-      <c r="BW9" s="86"/>
-      <c r="BX9" s="89"/>
-      <c r="BY9" s="92"/>
+      <c r="BQ9" s="83"/>
+      <c r="BR9" s="83"/>
+      <c r="BS9" s="83"/>
+      <c r="BT9" s="83"/>
+      <c r="BU9" s="44"/>
+      <c r="BV9" s="47"/>
+      <c r="BW9" s="50"/>
+      <c r="BX9" s="53"/>
+      <c r="BY9" s="56"/>
     </row>
     <row r="10" spans="1:77" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
-      <c r="B10" s="78" t="s">
+      <c r="A10" s="81"/>
+      <c r="B10" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="37"/>
+      <c r="C10" s="88"/>
       <c r="D10" s="6">
         <v>4</v>
       </c>
@@ -4676,20 +4673,18 @@
       <c r="BT10" s="4">
         <v>7</v>
       </c>
-      <c r="BU10" s="81"/>
-      <c r="BV10" s="84"/>
-      <c r="BW10" s="87"/>
-      <c r="BX10" s="90"/>
-      <c r="BY10" s="93"/>
+      <c r="BU10" s="45"/>
+      <c r="BV10" s="48"/>
+      <c r="BW10" s="51"/>
+      <c r="BX10" s="54"/>
+      <c r="BY10" s="57"/>
     </row>
     <row r="11" spans="1:77" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
-      <c r="B11" s="94" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="95"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="40"/>
       <c r="D11" s="11" t="s">
         <v>24</v>
       </c>
@@ -4922,8 +4917,8 @@
       <c r="A12" s="1">
         <v>2</v>
       </c>
-      <c r="B12" s="94"/>
-      <c r="C12" s="95"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
       <c r="D12" s="11" t="s">
         <v>24</v>
       </c>
@@ -5156,8 +5151,8 @@
       <c r="A13" s="1">
         <v>3</v>
       </c>
-      <c r="B13" s="94"/>
-      <c r="C13" s="95"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="40"/>
       <c r="D13" s="11" t="s">
         <v>24</v>
       </c>
@@ -5390,8 +5385,8 @@
       <c r="A14" s="1">
         <v>4</v>
       </c>
-      <c r="B14" s="94"/>
-      <c r="C14" s="95"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
       <c r="D14" s="11" t="s">
         <v>24</v>
       </c>
@@ -5624,8 +5619,8 @@
       <c r="A15" s="1">
         <v>5</v>
       </c>
-      <c r="B15" s="94"/>
-      <c r="C15" s="95"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="40"/>
       <c r="D15" s="11" t="s">
         <v>24</v>
       </c>
@@ -5858,8 +5853,8 @@
       <c r="A16" s="1">
         <v>6</v>
       </c>
-      <c r="B16" s="94"/>
-      <c r="C16" s="95"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="11" t="s">
         <v>24</v>
       </c>
@@ -6092,8 +6087,8 @@
       <c r="A17" s="1">
         <v>7</v>
       </c>
-      <c r="B17" s="94"/>
-      <c r="C17" s="95"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="11" t="s">
         <v>24</v>
       </c>
@@ -6326,8 +6321,8 @@
       <c r="A18" s="1">
         <v>8</v>
       </c>
-      <c r="B18" s="94"/>
-      <c r="C18" s="95"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="40"/>
       <c r="D18" s="11" t="s">
         <v>24</v>
       </c>
@@ -6560,8 +6555,8 @@
       <c r="A19" s="1">
         <v>9</v>
       </c>
-      <c r="B19" s="94"/>
-      <c r="C19" s="95"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="40"/>
       <c r="D19" s="11" t="s">
         <v>24</v>
       </c>
@@ -6794,8 +6789,8 @@
       <c r="A20" s="1">
         <v>10</v>
       </c>
-      <c r="B20" s="94"/>
-      <c r="C20" s="95"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
       <c r="D20" s="11" t="s">
         <v>24</v>
       </c>
@@ -7028,8 +7023,8 @@
       <c r="A21" s="1">
         <v>11</v>
       </c>
-      <c r="B21" s="94"/>
-      <c r="C21" s="95"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
       <c r="D21" s="11" t="s">
         <v>24</v>
       </c>
@@ -7262,8 +7257,8 @@
       <c r="A22" s="1">
         <v>12</v>
       </c>
-      <c r="B22" s="94"/>
-      <c r="C22" s="95"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="11" t="s">
         <v>24</v>
       </c>
@@ -7496,8 +7491,8 @@
       <c r="A23" s="1">
         <v>13</v>
       </c>
-      <c r="B23" s="94"/>
-      <c r="C23" s="95"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="11" t="s">
         <v>24</v>
       </c>
@@ -7730,8 +7725,8 @@
       <c r="A24" s="1">
         <v>14</v>
       </c>
-      <c r="B24" s="94"/>
-      <c r="C24" s="95"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
       <c r="D24" s="11" t="s">
         <v>24</v>
       </c>
@@ -7964,8 +7959,8 @@
       <c r="A25" s="1">
         <v>15</v>
       </c>
-      <c r="B25" s="94"/>
-      <c r="C25" s="95"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
       <c r="D25" s="11" t="s">
         <v>24</v>
       </c>
@@ -8198,8 +8193,8 @@
       <c r="A26" s="1">
         <v>16</v>
       </c>
-      <c r="B26" s="94"/>
-      <c r="C26" s="95"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="11" t="s">
         <v>24</v>
       </c>
@@ -8432,8 +8427,8 @@
       <c r="A27" s="1">
         <v>17</v>
       </c>
-      <c r="B27" s="94"/>
-      <c r="C27" s="95"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="11" t="s">
         <v>24</v>
       </c>
@@ -8666,8 +8661,8 @@
       <c r="A28" s="1">
         <v>18</v>
       </c>
-      <c r="B28" s="94"/>
-      <c r="C28" s="95"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="40"/>
       <c r="D28" s="11" t="s">
         <v>24</v>
       </c>
@@ -8900,8 +8895,8 @@
       <c r="A29" s="1">
         <v>19</v>
       </c>
-      <c r="B29" s="94"/>
-      <c r="C29" s="95"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="40"/>
       <c r="D29" s="11" t="s">
         <v>24</v>
       </c>
@@ -9134,8 +9129,8 @@
       <c r="A30" s="1">
         <v>20</v>
       </c>
-      <c r="B30" s="94"/>
-      <c r="C30" s="95"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="40"/>
       <c r="D30" s="11" t="s">
         <v>24</v>
       </c>
@@ -9368,8 +9363,8 @@
       <c r="A31" s="1">
         <v>21</v>
       </c>
-      <c r="B31" s="94"/>
-      <c r="C31" s="95"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="40"/>
       <c r="D31" s="11" t="s">
         <v>24</v>
       </c>
@@ -9602,8 +9597,8 @@
       <c r="A32" s="1">
         <v>22</v>
       </c>
-      <c r="B32" s="94"/>
-      <c r="C32" s="95"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="40"/>
       <c r="D32" s="11" t="s">
         <v>24</v>
       </c>
@@ -9836,8 +9831,8 @@
       <c r="A33" s="1">
         <v>23</v>
       </c>
-      <c r="B33" s="94"/>
-      <c r="C33" s="95"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="40"/>
       <c r="D33" s="11" t="s">
         <v>24</v>
       </c>
@@ -10070,8 +10065,8 @@
       <c r="A34" s="1">
         <v>24</v>
       </c>
-      <c r="B34" s="94"/>
-      <c r="C34" s="95"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="40"/>
       <c r="D34" s="11" t="s">
         <v>24</v>
       </c>
@@ -10304,8 +10299,8 @@
       <c r="A35" s="1">
         <v>25</v>
       </c>
-      <c r="B35" s="94"/>
-      <c r="C35" s="95"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="40"/>
       <c r="D35" s="11" t="s">
         <v>24</v>
       </c>
@@ -10538,8 +10533,8 @@
       <c r="A36" s="1">
         <v>26</v>
       </c>
-      <c r="B36" s="94"/>
-      <c r="C36" s="95"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="40"/>
       <c r="D36" s="11" t="s">
         <v>24</v>
       </c>
@@ -10772,8 +10767,8 @@
       <c r="A37" s="1">
         <v>27</v>
       </c>
-      <c r="B37" s="94"/>
-      <c r="C37" s="95"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="40"/>
       <c r="D37" s="11" t="s">
         <v>24</v>
       </c>
@@ -11006,8 +11001,8 @@
       <c r="A38" s="1">
         <v>28</v>
       </c>
-      <c r="B38" s="94"/>
-      <c r="C38" s="95"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="40"/>
       <c r="D38" s="11" t="s">
         <v>24</v>
       </c>
@@ -11240,8 +11235,8 @@
       <c r="A39" s="1">
         <v>29</v>
       </c>
-      <c r="B39" s="94"/>
-      <c r="C39" s="95"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="40"/>
       <c r="D39" s="11" t="s">
         <v>24</v>
       </c>
@@ -11474,8 +11469,8 @@
       <c r="A40" s="1">
         <v>30</v>
       </c>
-      <c r="B40" s="97"/>
-      <c r="C40" s="98"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="42"/>
       <c r="D40" s="14" t="s">
         <v>24</v>
       </c>
@@ -11710,21 +11705,21 @@
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-      <c r="D43" s="99"/>
-      <c r="E43" s="99"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
-      <c r="K43" s="99"/>
-      <c r="L43" s="99"/>
-      <c r="M43" s="99"/>
-      <c r="N43" s="99"/>
-      <c r="O43" s="99"/>
-      <c r="P43" s="99"/>
-      <c r="Q43" s="99"/>
-      <c r="R43" s="99"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="35"/>
+      <c r="L43" s="35"/>
+      <c r="M43" s="35"/>
+      <c r="N43" s="35"/>
+      <c r="O43" s="35"/>
+      <c r="P43" s="35"/>
+      <c r="Q43" s="35"/>
+      <c r="R43" s="35"/>
       <c r="S43" s="2"/>
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
@@ -11732,48 +11727,48 @@
       <c r="W43" s="2"/>
       <c r="X43" s="2"/>
       <c r="Y43" s="2"/>
-      <c r="Z43" s="99"/>
-      <c r="AA43" s="99"/>
-      <c r="AB43" s="99"/>
-      <c r="AC43" s="99"/>
-      <c r="AD43" s="99"/>
-      <c r="AE43" s="99"/>
-      <c r="AF43" s="99"/>
-      <c r="AG43" s="99"/>
-      <c r="AH43" s="99"/>
-      <c r="AI43" s="99"/>
-      <c r="AJ43" s="99"/>
-      <c r="AK43" s="99"/>
-      <c r="AL43" s="99"/>
-      <c r="AM43" s="99"/>
-      <c r="AN43" s="99"/>
-      <c r="AS43" s="99"/>
-      <c r="AT43" s="99"/>
-      <c r="AU43" s="99"/>
-      <c r="AV43" s="99"/>
-      <c r="AW43" s="99"/>
-      <c r="AX43" s="99"/>
-      <c r="AY43" s="99"/>
-      <c r="AZ43" s="99"/>
-      <c r="BA43" s="99"/>
-      <c r="BB43" s="99"/>
-      <c r="BC43" s="99"/>
-      <c r="BD43" s="99"/>
-      <c r="BE43" s="99"/>
-      <c r="BF43" s="99"/>
-      <c r="BG43" s="99"/>
-      <c r="BL43" s="99"/>
-      <c r="BM43" s="99"/>
-      <c r="BN43" s="99"/>
-      <c r="BO43" s="99"/>
-      <c r="BP43" s="99"/>
-      <c r="BQ43" s="99"/>
-      <c r="BR43" s="99"/>
-      <c r="BS43" s="99"/>
-      <c r="BT43" s="99"/>
-      <c r="BU43" s="99"/>
-      <c r="BV43" s="99"/>
-      <c r="BW43" s="99"/>
+      <c r="Z43" s="35"/>
+      <c r="AA43" s="35"/>
+      <c r="AB43" s="35"/>
+      <c r="AC43" s="35"/>
+      <c r="AD43" s="35"/>
+      <c r="AE43" s="35"/>
+      <c r="AF43" s="35"/>
+      <c r="AG43" s="35"/>
+      <c r="AH43" s="35"/>
+      <c r="AI43" s="35"/>
+      <c r="AJ43" s="35"/>
+      <c r="AK43" s="35"/>
+      <c r="AL43" s="35"/>
+      <c r="AM43" s="35"/>
+      <c r="AN43" s="35"/>
+      <c r="AS43" s="35"/>
+      <c r="AT43" s="35"/>
+      <c r="AU43" s="35"/>
+      <c r="AV43" s="35"/>
+      <c r="AW43" s="35"/>
+      <c r="AX43" s="35"/>
+      <c r="AY43" s="35"/>
+      <c r="AZ43" s="35"/>
+      <c r="BA43" s="35"/>
+      <c r="BB43" s="35"/>
+      <c r="BC43" s="35"/>
+      <c r="BD43" s="35"/>
+      <c r="BE43" s="35"/>
+      <c r="BF43" s="35"/>
+      <c r="BG43" s="35"/>
+      <c r="BL43" s="35"/>
+      <c r="BM43" s="35"/>
+      <c r="BN43" s="35"/>
+      <c r="BO43" s="35"/>
+      <c r="BP43" s="35"/>
+      <c r="BQ43" s="35"/>
+      <c r="BR43" s="35"/>
+      <c r="BS43" s="35"/>
+      <c r="BT43" s="35"/>
+      <c r="BU43" s="35"/>
+      <c r="BV43" s="35"/>
+      <c r="BW43" s="35"/>
       <c r="BX43" s="27"/>
       <c r="BY43" s="27"/>
       <c r="BZ43" s="27"/>
@@ -11782,139 +11777,139 @@
       <c r="CC43" s="28"/>
     </row>
     <row r="44" spans="1:81" s="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D44" s="100"/>
-      <c r="E44" s="100"/>
-      <c r="F44" s="100"/>
-      <c r="G44" s="100"/>
-      <c r="H44" s="100"/>
-      <c r="I44" s="100"/>
-      <c r="J44" s="100"/>
-      <c r="K44" s="100"/>
-      <c r="L44" s="100"/>
-      <c r="M44" s="100"/>
-      <c r="N44" s="100"/>
-      <c r="O44" s="100"/>
-      <c r="P44" s="100"/>
-      <c r="Q44" s="100"/>
-      <c r="R44" s="100"/>
-      <c r="Z44" s="100" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA44" s="100"/>
-      <c r="AB44" s="100"/>
-      <c r="AC44" s="100"/>
-      <c r="AD44" s="100"/>
-      <c r="AE44" s="100"/>
-      <c r="AF44" s="100"/>
-      <c r="AG44" s="100"/>
-      <c r="AH44" s="100"/>
-      <c r="AI44" s="100"/>
-      <c r="AJ44" s="100"/>
-      <c r="AK44" s="100"/>
-      <c r="AL44" s="100"/>
-      <c r="AM44" s="100"/>
-      <c r="AN44" s="100"/>
-      <c r="AS44" s="100" t="s">
-        <v>56</v>
-      </c>
-      <c r="AT44" s="100"/>
-      <c r="AU44" s="100"/>
-      <c r="AV44" s="100"/>
-      <c r="AW44" s="100"/>
-      <c r="AX44" s="100"/>
-      <c r="AY44" s="100"/>
-      <c r="AZ44" s="100"/>
-      <c r="BA44" s="100"/>
-      <c r="BB44" s="100"/>
-      <c r="BC44" s="100"/>
-      <c r="BD44" s="100"/>
-      <c r="BE44" s="100"/>
-      <c r="BF44" s="100"/>
-      <c r="BG44" s="100"/>
-      <c r="BL44" s="101" t="s">
-        <v>53</v>
-      </c>
-      <c r="BM44" s="101"/>
-      <c r="BN44" s="101"/>
-      <c r="BO44" s="101"/>
-      <c r="BP44" s="101"/>
-      <c r="BQ44" s="101"/>
-      <c r="BR44" s="101"/>
-      <c r="BS44" s="101"/>
-      <c r="BT44" s="101"/>
-      <c r="BU44" s="101"/>
-      <c r="BV44" s="101"/>
-      <c r="BW44" s="101"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="36"/>
+      <c r="M44" s="36"/>
+      <c r="N44" s="36"/>
+      <c r="O44" s="36"/>
+      <c r="P44" s="36"/>
+      <c r="Q44" s="36"/>
+      <c r="R44" s="36"/>
+      <c r="Z44" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA44" s="36"/>
+      <c r="AB44" s="36"/>
+      <c r="AC44" s="36"/>
+      <c r="AD44" s="36"/>
+      <c r="AE44" s="36"/>
+      <c r="AF44" s="36"/>
+      <c r="AG44" s="36"/>
+      <c r="AH44" s="36"/>
+      <c r="AI44" s="36"/>
+      <c r="AJ44" s="36"/>
+      <c r="AK44" s="36"/>
+      <c r="AL44" s="36"/>
+      <c r="AM44" s="36"/>
+      <c r="AN44" s="36"/>
+      <c r="AS44" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="AT44" s="36"/>
+      <c r="AU44" s="36"/>
+      <c r="AV44" s="36"/>
+      <c r="AW44" s="36"/>
+      <c r="AX44" s="36"/>
+      <c r="AY44" s="36"/>
+      <c r="AZ44" s="36"/>
+      <c r="BA44" s="36"/>
+      <c r="BB44" s="36"/>
+      <c r="BC44" s="36"/>
+      <c r="BD44" s="36"/>
+      <c r="BE44" s="36"/>
+      <c r="BF44" s="36"/>
+      <c r="BG44" s="36"/>
+      <c r="BL44" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="BM44" s="38"/>
+      <c r="BN44" s="38"/>
+      <c r="BO44" s="38"/>
+      <c r="BP44" s="38"/>
+      <c r="BQ44" s="38"/>
+      <c r="BR44" s="38"/>
+      <c r="BS44" s="38"/>
+      <c r="BT44" s="38"/>
+      <c r="BU44" s="38"/>
+      <c r="BV44" s="38"/>
+      <c r="BW44" s="38"/>
       <c r="BX44" s="32"/>
       <c r="BY44" s="32"/>
       <c r="BZ44" s="32"/>
     </row>
     <row r="45" spans="1:81" s="29" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D45" s="96" t="s">
+      <c r="D45" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="E45" s="96"/>
-      <c r="F45" s="96"/>
-      <c r="G45" s="96"/>
-      <c r="H45" s="96"/>
-      <c r="I45" s="96"/>
-      <c r="J45" s="96"/>
-      <c r="K45" s="96"/>
-      <c r="L45" s="96"/>
-      <c r="M45" s="96"/>
-      <c r="N45" s="96"/>
-      <c r="O45" s="96"/>
-      <c r="P45" s="96"/>
-      <c r="Q45" s="96"/>
-      <c r="R45" s="96"/>
-      <c r="Z45" s="96" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA45" s="96"/>
-      <c r="AB45" s="96"/>
-      <c r="AC45" s="96"/>
-      <c r="AD45" s="96"/>
-      <c r="AE45" s="96"/>
-      <c r="AF45" s="96"/>
-      <c r="AG45" s="96"/>
-      <c r="AH45" s="96"/>
-      <c r="AI45" s="96"/>
-      <c r="AJ45" s="96"/>
-      <c r="AK45" s="96"/>
-      <c r="AL45" s="96"/>
-      <c r="AM45" s="96"/>
-      <c r="AN45" s="96"/>
-      <c r="AS45" s="96" t="s">
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="37"/>
+      <c r="I45" s="37"/>
+      <c r="J45" s="37"/>
+      <c r="K45" s="37"/>
+      <c r="L45" s="37"/>
+      <c r="M45" s="37"/>
+      <c r="N45" s="37"/>
+      <c r="O45" s="37"/>
+      <c r="P45" s="37"/>
+      <c r="Q45" s="37"/>
+      <c r="R45" s="37"/>
+      <c r="Z45" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA45" s="37"/>
+      <c r="AB45" s="37"/>
+      <c r="AC45" s="37"/>
+      <c r="AD45" s="37"/>
+      <c r="AE45" s="37"/>
+      <c r="AF45" s="37"/>
+      <c r="AG45" s="37"/>
+      <c r="AH45" s="37"/>
+      <c r="AI45" s="37"/>
+      <c r="AJ45" s="37"/>
+      <c r="AK45" s="37"/>
+      <c r="AL45" s="37"/>
+      <c r="AM45" s="37"/>
+      <c r="AN45" s="37"/>
+      <c r="AS45" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="AT45" s="37"/>
+      <c r="AU45" s="37"/>
+      <c r="AV45" s="37"/>
+      <c r="AW45" s="37"/>
+      <c r="AX45" s="37"/>
+      <c r="AY45" s="37"/>
+      <c r="AZ45" s="37"/>
+      <c r="BA45" s="37"/>
+      <c r="BB45" s="37"/>
+      <c r="BC45" s="37"/>
+      <c r="BD45" s="37"/>
+      <c r="BE45" s="37"/>
+      <c r="BF45" s="37"/>
+      <c r="BG45" s="37"/>
+      <c r="BL45" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="AT45" s="96"/>
-      <c r="AU45" s="96"/>
-      <c r="AV45" s="96"/>
-      <c r="AW45" s="96"/>
-      <c r="AX45" s="96"/>
-      <c r="AY45" s="96"/>
-      <c r="AZ45" s="96"/>
-      <c r="BA45" s="96"/>
-      <c r="BB45" s="96"/>
-      <c r="BC45" s="96"/>
-      <c r="BD45" s="96"/>
-      <c r="BE45" s="96"/>
-      <c r="BF45" s="96"/>
-      <c r="BG45" s="96"/>
-      <c r="BL45" s="96" t="s">
-        <v>33</v>
-      </c>
-      <c r="BM45" s="96"/>
-      <c r="BN45" s="96"/>
-      <c r="BO45" s="96"/>
-      <c r="BP45" s="96"/>
-      <c r="BQ45" s="96"/>
-      <c r="BR45" s="96"/>
-      <c r="BS45" s="96"/>
-      <c r="BT45" s="96"/>
-      <c r="BU45" s="96"/>
-      <c r="BV45" s="96"/>
-      <c r="BW45" s="96"/>
+      <c r="BM45" s="37"/>
+      <c r="BN45" s="37"/>
+      <c r="BO45" s="37"/>
+      <c r="BP45" s="37"/>
+      <c r="BQ45" s="37"/>
+      <c r="BR45" s="37"/>
+      <c r="BS45" s="37"/>
+      <c r="BT45" s="37"/>
+      <c r="BU45" s="37"/>
+      <c r="BV45" s="37"/>
+      <c r="BW45" s="37"/>
       <c r="BX45" s="30"/>
       <c r="BY45" s="30"/>
       <c r="BZ45" s="30"/>
@@ -12960,12 +12955,56 @@
     <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="AS43:BG43"/>
-    <mergeCell ref="AS44:BG44"/>
-    <mergeCell ref="AS45:BG45"/>
-    <mergeCell ref="BL44:BW44"/>
-    <mergeCell ref="BL45:BW45"/>
-    <mergeCell ref="BL43:BW43"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:V6"/>
+    <mergeCell ref="W6:AR6"/>
+    <mergeCell ref="AS6:BO6"/>
+    <mergeCell ref="BP6:BT6"/>
+    <mergeCell ref="A1:BY1"/>
+    <mergeCell ref="A2:BY2"/>
+    <mergeCell ref="A3:BY3"/>
+    <mergeCell ref="A4:BY4"/>
+    <mergeCell ref="A5:BY5"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:V8"/>
+    <mergeCell ref="W7:AR8"/>
+    <mergeCell ref="AS7:BO8"/>
+    <mergeCell ref="BP7:BT8"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="D9:V9"/>
+    <mergeCell ref="W9:AR9"/>
+    <mergeCell ref="AS9:BO9"/>
+    <mergeCell ref="BP9:BT9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="BU6:BU10"/>
+    <mergeCell ref="BV6:BV10"/>
+    <mergeCell ref="BW6:BW10"/>
+    <mergeCell ref="BX6:BX10"/>
+    <mergeCell ref="BY6:BY10"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="D45:R45"/>
     <mergeCell ref="Z45:AN45"/>
     <mergeCell ref="B35:C35"/>
@@ -12978,56 +13017,12 @@
     <mergeCell ref="D44:R44"/>
     <mergeCell ref="Z44:AN44"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="BU6:BU10"/>
-    <mergeCell ref="BV6:BV10"/>
-    <mergeCell ref="BW6:BW10"/>
-    <mergeCell ref="BX6:BX10"/>
-    <mergeCell ref="BY6:BY10"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:V8"/>
-    <mergeCell ref="W7:AR8"/>
-    <mergeCell ref="AS7:BO8"/>
-    <mergeCell ref="BP7:BT8"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="D9:V9"/>
-    <mergeCell ref="W9:AR9"/>
-    <mergeCell ref="AS9:BO9"/>
-    <mergeCell ref="BP9:BT9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="A1:BY1"/>
-    <mergeCell ref="A2:BY2"/>
-    <mergeCell ref="A3:BY3"/>
-    <mergeCell ref="A4:BY4"/>
-    <mergeCell ref="A5:BY5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:V6"/>
-    <mergeCell ref="W6:AR6"/>
-    <mergeCell ref="AS6:BO6"/>
-    <mergeCell ref="BP6:BT6"/>
+    <mergeCell ref="AS43:BG43"/>
+    <mergeCell ref="AS44:BG44"/>
+    <mergeCell ref="AS45:BG45"/>
+    <mergeCell ref="BL44:BW44"/>
+    <mergeCell ref="BL45:BW45"/>
+    <mergeCell ref="BL43:BW43"/>
   </mergeCells>
   <conditionalFormatting sqref="D11:BT40">
     <cfRule type="containsText" dxfId="26" priority="5" operator="containsText" text="F">
@@ -13107,545 +13102,542 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:69" ht="28" x14ac:dyDescent="0.2">
-      <c r="A1" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
-      <c r="AB1" s="44"/>
-      <c r="AC1" s="44"/>
-      <c r="AD1" s="44"/>
-      <c r="AE1" s="44"/>
-      <c r="AF1" s="44"/>
-      <c r="AG1" s="44"/>
-      <c r="AH1" s="44"/>
-      <c r="AI1" s="44"/>
-      <c r="AJ1" s="44"/>
-      <c r="AK1" s="44"/>
-      <c r="AL1" s="44"/>
-      <c r="AM1" s="44"/>
-      <c r="AN1" s="44"/>
-      <c r="AO1" s="44"/>
-      <c r="AP1" s="44"/>
-      <c r="AQ1" s="44"/>
-      <c r="AR1" s="44"/>
-      <c r="AS1" s="44"/>
-      <c r="AT1" s="44"/>
-      <c r="AU1" s="44"/>
-      <c r="AV1" s="44"/>
-      <c r="AW1" s="44"/>
-      <c r="AX1" s="44"/>
-      <c r="AY1" s="44"/>
-      <c r="AZ1" s="44"/>
-      <c r="BA1" s="44"/>
-      <c r="BB1" s="44"/>
-      <c r="BC1" s="44"/>
-      <c r="BD1" s="44"/>
-      <c r="BE1" s="44"/>
-      <c r="BF1" s="44"/>
-      <c r="BG1" s="44"/>
-      <c r="BH1" s="44"/>
-      <c r="BI1" s="44"/>
-      <c r="BJ1" s="44"/>
-      <c r="BK1" s="44"/>
-      <c r="BL1" s="44"/>
-      <c r="BM1" s="44"/>
-      <c r="BN1" s="44"/>
-      <c r="BO1" s="44"/>
-      <c r="BP1" s="44"/>
-      <c r="BQ1" s="44"/>
+      <c r="A1" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
+      <c r="M1" s="90"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="90"/>
+      <c r="Q1" s="90"/>
+      <c r="R1" s="90"/>
+      <c r="S1" s="90"/>
+      <c r="T1" s="90"/>
+      <c r="U1" s="90"/>
+      <c r="V1" s="90"/>
+      <c r="W1" s="90"/>
+      <c r="X1" s="90"/>
+      <c r="Y1" s="90"/>
+      <c r="Z1" s="90"/>
+      <c r="AA1" s="90"/>
+      <c r="AB1" s="90"/>
+      <c r="AC1" s="90"/>
+      <c r="AD1" s="90"/>
+      <c r="AE1" s="90"/>
+      <c r="AF1" s="90"/>
+      <c r="AG1" s="90"/>
+      <c r="AH1" s="90"/>
+      <c r="AI1" s="90"/>
+      <c r="AJ1" s="90"/>
+      <c r="AK1" s="90"/>
+      <c r="AL1" s="90"/>
+      <c r="AM1" s="90"/>
+      <c r="AN1" s="90"/>
+      <c r="AO1" s="90"/>
+      <c r="AP1" s="90"/>
+      <c r="AQ1" s="90"/>
+      <c r="AR1" s="90"/>
+      <c r="AS1" s="90"/>
+      <c r="AT1" s="90"/>
+      <c r="AU1" s="90"/>
+      <c r="AV1" s="90"/>
+      <c r="AW1" s="90"/>
+      <c r="AX1" s="90"/>
+      <c r="AY1" s="90"/>
+      <c r="AZ1" s="90"/>
+      <c r="BA1" s="90"/>
+      <c r="BB1" s="90"/>
+      <c r="BC1" s="90"/>
+      <c r="BD1" s="90"/>
+      <c r="BE1" s="90"/>
+      <c r="BF1" s="90"/>
+      <c r="BG1" s="90"/>
+      <c r="BH1" s="90"/>
+      <c r="BI1" s="90"/>
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
     </row>
     <row r="2" spans="1:69" x14ac:dyDescent="0.2">
-      <c r="A2" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="45"/>
-      <c r="W2" s="45"/>
-      <c r="X2" s="45"/>
-      <c r="Y2" s="45"/>
-      <c r="Z2" s="45"/>
-      <c r="AA2" s="45"/>
-      <c r="AB2" s="45"/>
-      <c r="AC2" s="45"/>
-      <c r="AD2" s="45"/>
-      <c r="AE2" s="45"/>
-      <c r="AF2" s="45"/>
-      <c r="AG2" s="45"/>
-      <c r="AH2" s="45"/>
-      <c r="AI2" s="45"/>
-      <c r="AJ2" s="45"/>
-      <c r="AK2" s="45"/>
-      <c r="AL2" s="45"/>
-      <c r="AM2" s="45"/>
-      <c r="AN2" s="45"/>
-      <c r="AO2" s="45"/>
-      <c r="AP2" s="45"/>
-      <c r="AQ2" s="45"/>
-      <c r="AR2" s="45"/>
-      <c r="AS2" s="45"/>
-      <c r="AT2" s="45"/>
-      <c r="AU2" s="45"/>
-      <c r="AV2" s="45"/>
-      <c r="AW2" s="45"/>
-      <c r="AX2" s="45"/>
-      <c r="AY2" s="45"/>
-      <c r="AZ2" s="45"/>
-      <c r="BA2" s="45"/>
-      <c r="BB2" s="45"/>
-      <c r="BC2" s="45"/>
-      <c r="BD2" s="45"/>
-      <c r="BE2" s="45"/>
-      <c r="BF2" s="45"/>
-      <c r="BG2" s="45"/>
-      <c r="BH2" s="45"/>
-      <c r="BI2" s="45"/>
-      <c r="BJ2" s="45"/>
-      <c r="BK2" s="45"/>
-      <c r="BL2" s="45"/>
-      <c r="BM2" s="45"/>
-      <c r="BN2" s="45"/>
-      <c r="BO2" s="45"/>
-      <c r="BP2" s="45"/>
-      <c r="BQ2" s="45"/>
+      <c r="A2" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="91"/>
+      <c r="P2" s="91"/>
+      <c r="Q2" s="91"/>
+      <c r="R2" s="91"/>
+      <c r="S2" s="91"/>
+      <c r="T2" s="91"/>
+      <c r="U2" s="91"/>
+      <c r="V2" s="91"/>
+      <c r="W2" s="91"/>
+      <c r="X2" s="91"/>
+      <c r="Y2" s="91"/>
+      <c r="Z2" s="91"/>
+      <c r="AA2" s="91"/>
+      <c r="AB2" s="91"/>
+      <c r="AC2" s="91"/>
+      <c r="AD2" s="91"/>
+      <c r="AE2" s="91"/>
+      <c r="AF2" s="91"/>
+      <c r="AG2" s="91"/>
+      <c r="AH2" s="91"/>
+      <c r="AI2" s="91"/>
+      <c r="AJ2" s="91"/>
+      <c r="AK2" s="91"/>
+      <c r="AL2" s="91"/>
+      <c r="AM2" s="91"/>
+      <c r="AN2" s="91"/>
+      <c r="AO2" s="91"/>
+      <c r="AP2" s="91"/>
+      <c r="AQ2" s="91"/>
+      <c r="AR2" s="91"/>
+      <c r="AS2" s="91"/>
+      <c r="AT2" s="91"/>
+      <c r="AU2" s="91"/>
+      <c r="AV2" s="91"/>
+      <c r="AW2" s="91"/>
+      <c r="AX2" s="91"/>
+      <c r="AY2" s="91"/>
+      <c r="AZ2" s="91"/>
+      <c r="BA2" s="91"/>
+      <c r="BB2" s="91"/>
+      <c r="BC2" s="91"/>
+      <c r="BD2" s="91"/>
+      <c r="BE2" s="91"/>
+      <c r="BF2" s="91"/>
+      <c r="BG2" s="91"/>
+      <c r="BH2" s="91"/>
+      <c r="BI2" s="91"/>
+      <c r="BJ2" s="91"/>
+      <c r="BK2" s="91"/>
+      <c r="BL2" s="91"/>
+      <c r="BM2" s="91"/>
+      <c r="BN2" s="91"/>
+      <c r="BO2" s="91"/>
+      <c r="BP2" s="91"/>
+      <c r="BQ2" s="91"/>
     </row>
     <row r="3" spans="1:69" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="46"/>
-      <c r="R3" s="46"/>
-      <c r="S3" s="46"/>
-      <c r="T3" s="46"/>
-      <c r="U3" s="46"/>
-      <c r="V3" s="46"/>
-      <c r="W3" s="46"/>
-      <c r="X3" s="46"/>
-      <c r="Y3" s="46"/>
-      <c r="Z3" s="46"/>
-      <c r="AA3" s="46"/>
-      <c r="AB3" s="46"/>
-      <c r="AC3" s="46"/>
-      <c r="AD3" s="46"/>
-      <c r="AE3" s="46"/>
-      <c r="AF3" s="46"/>
-      <c r="AG3" s="46"/>
-      <c r="AH3" s="46"/>
-      <c r="AI3" s="46"/>
-      <c r="AJ3" s="46"/>
-      <c r="AK3" s="46"/>
-      <c r="AL3" s="46"/>
-      <c r="AM3" s="46"/>
-      <c r="AN3" s="46"/>
-      <c r="AO3" s="46"/>
-      <c r="AP3" s="46"/>
-      <c r="AQ3" s="46"/>
-      <c r="AR3" s="46"/>
-      <c r="AS3" s="46"/>
-      <c r="AT3" s="46"/>
-      <c r="AU3" s="46"/>
-      <c r="AV3" s="46"/>
-      <c r="AW3" s="46"/>
-      <c r="AX3" s="46"/>
-      <c r="AY3" s="46"/>
-      <c r="AZ3" s="46"/>
-      <c r="BA3" s="46"/>
-      <c r="BB3" s="46"/>
-      <c r="BC3" s="46"/>
-      <c r="BD3" s="46"/>
-      <c r="BE3" s="46"/>
-      <c r="BF3" s="46"/>
-      <c r="BG3" s="46"/>
-      <c r="BH3" s="46"/>
-      <c r="BI3" s="46"/>
-      <c r="BJ3" s="46"/>
-      <c r="BK3" s="46"/>
-      <c r="BL3" s="46"/>
-      <c r="BM3" s="46"/>
-      <c r="BN3" s="46"/>
-      <c r="BO3" s="46"/>
-      <c r="BP3" s="46"/>
-      <c r="BQ3" s="46"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="92"/>
+      <c r="Q3" s="92"/>
+      <c r="R3" s="92"/>
+      <c r="S3" s="92"/>
+      <c r="T3" s="92"/>
+      <c r="U3" s="92"/>
+      <c r="V3" s="92"/>
+      <c r="W3" s="92"/>
+      <c r="X3" s="92"/>
+      <c r="Y3" s="92"/>
+      <c r="Z3" s="92"/>
+      <c r="AA3" s="92"/>
+      <c r="AB3" s="92"/>
+      <c r="AC3" s="92"/>
+      <c r="AD3" s="92"/>
+      <c r="AE3" s="92"/>
+      <c r="AF3" s="92"/>
+      <c r="AG3" s="92"/>
+      <c r="AH3" s="92"/>
+      <c r="AI3" s="92"/>
+      <c r="AJ3" s="92"/>
+      <c r="AK3" s="92"/>
+      <c r="AL3" s="92"/>
+      <c r="AM3" s="92"/>
+      <c r="AN3" s="92"/>
+      <c r="AO3" s="92"/>
+      <c r="AP3" s="92"/>
+      <c r="AQ3" s="92"/>
+      <c r="AR3" s="92"/>
+      <c r="AS3" s="92"/>
+      <c r="AT3" s="92"/>
+      <c r="AU3" s="92"/>
+      <c r="AV3" s="92"/>
+      <c r="AW3" s="92"/>
+      <c r="AX3" s="92"/>
+      <c r="AY3" s="92"/>
+      <c r="AZ3" s="92"/>
+      <c r="BA3" s="92"/>
+      <c r="BB3" s="92"/>
+      <c r="BC3" s="92"/>
+      <c r="BD3" s="92"/>
+      <c r="BE3" s="92"/>
+      <c r="BF3" s="92"/>
+      <c r="BG3" s="92"/>
+      <c r="BH3" s="92"/>
+      <c r="BI3" s="92"/>
+      <c r="BJ3" s="92"/>
+      <c r="BK3" s="92"/>
+      <c r="BL3" s="92"/>
+      <c r="BM3" s="92"/>
+      <c r="BN3" s="92"/>
+      <c r="BO3" s="92"/>
+      <c r="BP3" s="92"/>
+      <c r="BQ3" s="92"/>
     </row>
     <row r="4" spans="1:69" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="W4" s="48"/>
-      <c r="X4" s="48"/>
-      <c r="Y4" s="48"/>
-      <c r="Z4" s="48"/>
-      <c r="AA4" s="48"/>
-      <c r="AB4" s="48"/>
-      <c r="AC4" s="48"/>
-      <c r="AD4" s="48"/>
-      <c r="AE4" s="48"/>
-      <c r="AF4" s="48"/>
-      <c r="AG4" s="48"/>
-      <c r="AH4" s="48"/>
-      <c r="AI4" s="48"/>
-      <c r="AJ4" s="48"/>
-      <c r="AK4" s="48"/>
-      <c r="AL4" s="48"/>
-      <c r="AM4" s="48"/>
-      <c r="AN4" s="48"/>
-      <c r="AO4" s="48"/>
-      <c r="AP4" s="48"/>
-      <c r="AQ4" s="48"/>
-      <c r="AR4" s="48"/>
-      <c r="AS4" s="48"/>
-      <c r="AT4" s="48"/>
-      <c r="AU4" s="48"/>
-      <c r="AV4" s="48"/>
-      <c r="AW4" s="48"/>
-      <c r="AX4" s="48"/>
-      <c r="AY4" s="48"/>
-      <c r="AZ4" s="48"/>
-      <c r="BA4" s="48"/>
-      <c r="BB4" s="48"/>
-      <c r="BC4" s="48"/>
-      <c r="BD4" s="48"/>
-      <c r="BE4" s="48"/>
-      <c r="BF4" s="48"/>
-      <c r="BG4" s="48"/>
-      <c r="BH4" s="48"/>
-      <c r="BI4" s="48"/>
-      <c r="BJ4" s="48"/>
-      <c r="BK4" s="48"/>
-      <c r="BL4" s="48"/>
-      <c r="BM4" s="48"/>
-      <c r="BN4" s="48"/>
-      <c r="BO4" s="48"/>
-      <c r="BP4" s="48"/>
-      <c r="BQ4" s="48"/>
+      <c r="A4" s="93" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="94"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="94"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="94"/>
+      <c r="V4" s="94"/>
+      <c r="W4" s="94"/>
+      <c r="X4" s="94"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
+      <c r="AB4" s="94"/>
+      <c r="AC4" s="94"/>
+      <c r="AD4" s="94"/>
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="94"/>
+      <c r="AQ4" s="94"/>
+      <c r="AR4" s="94"/>
+      <c r="AS4" s="94"/>
+      <c r="AT4" s="94"/>
+      <c r="AU4" s="94"/>
+      <c r="AV4" s="94"/>
+      <c r="AW4" s="94"/>
+      <c r="AX4" s="94"/>
+      <c r="AY4" s="94"/>
+      <c r="AZ4" s="94"/>
+      <c r="BA4" s="94"/>
+      <c r="BB4" s="94"/>
+      <c r="BC4" s="94"/>
+      <c r="BD4" s="94"/>
+      <c r="BE4" s="94"/>
+      <c r="BF4" s="94"/>
+      <c r="BG4" s="94"/>
+      <c r="BH4" s="94"/>
+      <c r="BI4" s="94"/>
+      <c r="BJ4" s="94"/>
+      <c r="BK4" s="94"/>
+      <c r="BL4" s="94"/>
+      <c r="BM4" s="94"/>
+      <c r="BN4" s="94"/>
+      <c r="BO4" s="94"/>
+      <c r="BP4" s="94"/>
+      <c r="BQ4" s="94"/>
     </row>
     <row r="5" spans="1:69" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="44"/>
-      <c r="T5" s="44"/>
-      <c r="U5" s="44"/>
-      <c r="V5" s="44"/>
-      <c r="W5" s="44"/>
-      <c r="X5" s="44"/>
-      <c r="Y5" s="44"/>
-      <c r="Z5" s="44"/>
-      <c r="AA5" s="44"/>
-      <c r="AB5" s="44"/>
-      <c r="AC5" s="44"/>
-      <c r="AD5" s="44"/>
-      <c r="AE5" s="44"/>
-      <c r="AF5" s="44"/>
-      <c r="AG5" s="44"/>
-      <c r="AH5" s="44"/>
-      <c r="AI5" s="44"/>
-      <c r="AJ5" s="44"/>
-      <c r="AK5" s="44"/>
-      <c r="AL5" s="44"/>
-      <c r="AM5" s="44"/>
-      <c r="AN5" s="44"/>
-      <c r="AO5" s="44"/>
-      <c r="AP5" s="44"/>
-      <c r="AQ5" s="44"/>
-      <c r="AR5" s="44"/>
-      <c r="AS5" s="44"/>
-      <c r="AT5" s="44"/>
-      <c r="AU5" s="44"/>
-      <c r="AV5" s="44"/>
-      <c r="AW5" s="44"/>
-      <c r="AX5" s="44"/>
-      <c r="AY5" s="44"/>
-      <c r="AZ5" s="44"/>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44"/>
-      <c r="BC5" s="44"/>
-      <c r="BD5" s="44"/>
-      <c r="BE5" s="44"/>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
-      <c r="BI5" s="44"/>
-      <c r="BJ5" s="44"/>
-      <c r="BK5" s="44"/>
-      <c r="BL5" s="44"/>
-      <c r="BM5" s="44"/>
-      <c r="BN5" s="44"/>
-      <c r="BO5" s="44"/>
-      <c r="BP5" s="44"/>
-      <c r="BQ5" s="44"/>
+      <c r="A5" s="89" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="90"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
+      <c r="W5" s="90"/>
+      <c r="X5" s="90"/>
+      <c r="Y5" s="90"/>
+      <c r="Z5" s="90"/>
+      <c r="AA5" s="90"/>
+      <c r="AB5" s="90"/>
+      <c r="AC5" s="90"/>
+      <c r="AD5" s="90"/>
+      <c r="AE5" s="90"/>
+      <c r="AF5" s="90"/>
+      <c r="AG5" s="90"/>
+      <c r="AH5" s="90"/>
+      <c r="AI5" s="90"/>
+      <c r="AJ5" s="90"/>
+      <c r="AK5" s="90"/>
+      <c r="AL5" s="90"/>
+      <c r="AM5" s="90"/>
+      <c r="AN5" s="90"/>
+      <c r="AO5" s="90"/>
+      <c r="AP5" s="90"/>
+      <c r="AQ5" s="90"/>
+      <c r="AR5" s="90"/>
+      <c r="AS5" s="90"/>
+      <c r="AT5" s="90"/>
+      <c r="AU5" s="90"/>
+      <c r="AV5" s="90"/>
+      <c r="AW5" s="90"/>
+      <c r="AX5" s="90"/>
+      <c r="AY5" s="90"/>
+      <c r="AZ5" s="90"/>
+      <c r="BA5" s="90"/>
+      <c r="BB5" s="90"/>
+      <c r="BC5" s="90"/>
+      <c r="BD5" s="90"/>
+      <c r="BE5" s="90"/>
+      <c r="BF5" s="90"/>
+      <c r="BG5" s="90"/>
+      <c r="BH5" s="90"/>
+      <c r="BI5" s="90"/>
+      <c r="BJ5" s="90"/>
+      <c r="BK5" s="90"/>
+      <c r="BL5" s="90"/>
+      <c r="BM5" s="90"/>
+      <c r="BN5" s="90"/>
+      <c r="BO5" s="90"/>
+      <c r="BP5" s="90"/>
+      <c r="BQ5" s="90"/>
     </row>
     <row r="6" spans="1:69" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="38" t="s">
+      <c r="B6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="41" t="s">
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="98"/>
+      <c r="K6" s="98"/>
+      <c r="L6" s="98"/>
+      <c r="M6" s="98"/>
+      <c r="N6" s="98"/>
+      <c r="O6" s="98"/>
+      <c r="P6" s="98"/>
+      <c r="Q6" s="98"/>
+      <c r="R6" s="99"/>
+      <c r="S6" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="T6" s="39"/>
-      <c r="U6" s="39"/>
-      <c r="V6" s="39"/>
-      <c r="W6" s="39"/>
-      <c r="X6" s="39"/>
-      <c r="Y6" s="39"/>
-      <c r="Z6" s="39"/>
-      <c r="AA6" s="39"/>
-      <c r="AB6" s="39"/>
-      <c r="AC6" s="39"/>
-      <c r="AD6" s="39"/>
-      <c r="AE6" s="39"/>
-      <c r="AF6" s="39"/>
-      <c r="AG6" s="39"/>
-      <c r="AH6" s="39"/>
-      <c r="AI6" s="39"/>
-      <c r="AJ6" s="39"/>
-      <c r="AK6" s="39"/>
-      <c r="AL6" s="42"/>
-      <c r="AM6" s="42"/>
-      <c r="AN6" s="40"/>
-      <c r="AO6" s="41" t="s">
+      <c r="T6" s="98"/>
+      <c r="U6" s="98"/>
+      <c r="V6" s="98"/>
+      <c r="W6" s="98"/>
+      <c r="X6" s="98"/>
+      <c r="Y6" s="98"/>
+      <c r="Z6" s="98"/>
+      <c r="AA6" s="98"/>
+      <c r="AB6" s="98"/>
+      <c r="AC6" s="98"/>
+      <c r="AD6" s="98"/>
+      <c r="AE6" s="98"/>
+      <c r="AF6" s="98"/>
+      <c r="AG6" s="98"/>
+      <c r="AH6" s="98"/>
+      <c r="AI6" s="98"/>
+      <c r="AJ6" s="98"/>
+      <c r="AK6" s="98"/>
+      <c r="AL6" s="101"/>
+      <c r="AM6" s="101"/>
+      <c r="AN6" s="99"/>
+      <c r="AO6" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="AP6" s="39"/>
-      <c r="AQ6" s="39"/>
-      <c r="AR6" s="39"/>
-      <c r="AS6" s="39"/>
-      <c r="AT6" s="39"/>
-      <c r="AU6" s="39"/>
-      <c r="AV6" s="39"/>
-      <c r="AW6" s="39"/>
-      <c r="AX6" s="39"/>
-      <c r="AY6" s="39"/>
-      <c r="AZ6" s="39"/>
-      <c r="BA6" s="39"/>
-      <c r="BB6" s="39"/>
-      <c r="BC6" s="39"/>
-      <c r="BD6" s="39"/>
-      <c r="BE6" s="39"/>
-      <c r="BF6" s="39"/>
-      <c r="BG6" s="39"/>
-      <c r="BH6" s="39"/>
-      <c r="BI6" s="40"/>
-      <c r="BJ6" s="41" t="s">
+      <c r="AP6" s="98"/>
+      <c r="AQ6" s="98"/>
+      <c r="AR6" s="98"/>
+      <c r="AS6" s="98"/>
+      <c r="AT6" s="98"/>
+      <c r="AU6" s="98"/>
+      <c r="AV6" s="98"/>
+      <c r="AW6" s="98"/>
+      <c r="AX6" s="98"/>
+      <c r="AY6" s="98"/>
+      <c r="AZ6" s="98"/>
+      <c r="BA6" s="98"/>
+      <c r="BB6" s="98"/>
+      <c r="BC6" s="98"/>
+      <c r="BD6" s="98"/>
+      <c r="BE6" s="98"/>
+      <c r="BF6" s="98"/>
+      <c r="BG6" s="98"/>
+      <c r="BH6" s="98"/>
+      <c r="BI6" s="99"/>
+      <c r="BJ6" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="BK6" s="39"/>
-      <c r="BL6" s="39"/>
-      <c r="BM6" s="79" t="s">
+      <c r="BK6" s="98"/>
+      <c r="BL6" s="98"/>
+      <c r="BM6" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="BN6" s="82" t="s">
+      <c r="BN6" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="BO6" s="85" t="s">
+      <c r="BO6" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="BP6" s="88" t="s">
+      <c r="BP6" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="BQ6" s="91" t="s">
-        <v>47</v>
+      <c r="BQ6" s="55" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:69" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49">
-        <f>+'1ER TRIMESTRE'!A7</f>
-        <v>0</v>
-      </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="52" t="s">
+      <c r="A7" s="58"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
-      <c r="R7" s="54"/>
-      <c r="S7" s="58" t="s">
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="63"/>
+      <c r="S7" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="T7" s="53"/>
-      <c r="U7" s="53"/>
-      <c r="V7" s="53"/>
-      <c r="W7" s="53"/>
-      <c r="X7" s="53"/>
-      <c r="Y7" s="53"/>
-      <c r="Z7" s="53"/>
-      <c r="AA7" s="53"/>
-      <c r="AB7" s="53"/>
-      <c r="AC7" s="53"/>
-      <c r="AD7" s="53"/>
-      <c r="AE7" s="53"/>
-      <c r="AF7" s="53"/>
-      <c r="AG7" s="53"/>
-      <c r="AH7" s="53"/>
-      <c r="AI7" s="53"/>
-      <c r="AJ7" s="53"/>
-      <c r="AK7" s="53"/>
-      <c r="AL7" s="59"/>
-      <c r="AM7" s="59"/>
-      <c r="AN7" s="54"/>
-      <c r="AO7" s="62" t="s">
+      <c r="T7" s="62"/>
+      <c r="U7" s="62"/>
+      <c r="V7" s="62"/>
+      <c r="W7" s="62"/>
+      <c r="X7" s="62"/>
+      <c r="Y7" s="62"/>
+      <c r="Z7" s="62"/>
+      <c r="AA7" s="62"/>
+      <c r="AB7" s="62"/>
+      <c r="AC7" s="62"/>
+      <c r="AD7" s="62"/>
+      <c r="AE7" s="62"/>
+      <c r="AF7" s="62"/>
+      <c r="AG7" s="62"/>
+      <c r="AH7" s="62"/>
+      <c r="AI7" s="62"/>
+      <c r="AJ7" s="62"/>
+      <c r="AK7" s="62"/>
+      <c r="AL7" s="68"/>
+      <c r="AM7" s="68"/>
+      <c r="AN7" s="63"/>
+      <c r="AO7" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="AP7" s="63"/>
-      <c r="AQ7" s="63"/>
-      <c r="AR7" s="63"/>
-      <c r="AS7" s="63"/>
-      <c r="AT7" s="63"/>
-      <c r="AU7" s="63"/>
-      <c r="AV7" s="63"/>
-      <c r="AW7" s="63"/>
-      <c r="AX7" s="63"/>
-      <c r="AY7" s="63"/>
-      <c r="AZ7" s="63"/>
-      <c r="BA7" s="63"/>
-      <c r="BB7" s="63"/>
-      <c r="BC7" s="63"/>
-      <c r="BD7" s="63"/>
-      <c r="BE7" s="63"/>
-      <c r="BF7" s="63"/>
-      <c r="BG7" s="63"/>
-      <c r="BH7" s="63"/>
-      <c r="BI7" s="64"/>
-      <c r="BJ7" s="68" t="s">
-        <v>36</v>
-      </c>
-      <c r="BK7" s="63"/>
-      <c r="BL7" s="63"/>
-      <c r="BM7" s="80"/>
-      <c r="BN7" s="83"/>
-      <c r="BO7" s="86"/>
-      <c r="BP7" s="89"/>
-      <c r="BQ7" s="92"/>
+      <c r="AP7" s="72"/>
+      <c r="AQ7" s="72"/>
+      <c r="AR7" s="72"/>
+      <c r="AS7" s="72"/>
+      <c r="AT7" s="72"/>
+      <c r="AU7" s="72"/>
+      <c r="AV7" s="72"/>
+      <c r="AW7" s="72"/>
+      <c r="AX7" s="72"/>
+      <c r="AY7" s="72"/>
+      <c r="AZ7" s="72"/>
+      <c r="BA7" s="72"/>
+      <c r="BB7" s="72"/>
+      <c r="BC7" s="72"/>
+      <c r="BD7" s="72"/>
+      <c r="BE7" s="72"/>
+      <c r="BF7" s="72"/>
+      <c r="BG7" s="72"/>
+      <c r="BH7" s="72"/>
+      <c r="BI7" s="73"/>
+      <c r="BJ7" s="77" t="s">
+        <v>35</v>
+      </c>
+      <c r="BK7" s="72"/>
+      <c r="BL7" s="72"/>
+      <c r="BM7" s="44"/>
+      <c r="BN7" s="47"/>
+      <c r="BO7" s="50"/>
+      <c r="BP7" s="53"/>
+      <c r="BQ7" s="56"/>
     </row>
     <row r="8" spans="1:69" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="79" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -13654,164 +13646,161 @@
       <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="55"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="56"/>
-      <c r="P8" s="56"/>
-      <c r="Q8" s="56"/>
-      <c r="R8" s="57"/>
-      <c r="S8" s="60"/>
-      <c r="T8" s="56"/>
-      <c r="U8" s="56"/>
-      <c r="V8" s="56"/>
-      <c r="W8" s="56"/>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="56"/>
-      <c r="Z8" s="56"/>
-      <c r="AA8" s="56"/>
-      <c r="AB8" s="56"/>
-      <c r="AC8" s="56"/>
-      <c r="AD8" s="56"/>
-      <c r="AE8" s="56"/>
-      <c r="AF8" s="56"/>
-      <c r="AG8" s="56"/>
-      <c r="AH8" s="56"/>
-      <c r="AI8" s="56"/>
-      <c r="AJ8" s="56"/>
-      <c r="AK8" s="56"/>
-      <c r="AL8" s="61"/>
-      <c r="AM8" s="61"/>
-      <c r="AN8" s="57"/>
-      <c r="AO8" s="65"/>
-      <c r="AP8" s="66"/>
-      <c r="AQ8" s="66"/>
-      <c r="AR8" s="66"/>
-      <c r="AS8" s="66"/>
-      <c r="AT8" s="66"/>
-      <c r="AU8" s="66"/>
-      <c r="AV8" s="66"/>
-      <c r="AW8" s="66"/>
-      <c r="AX8" s="66"/>
-      <c r="AY8" s="66"/>
-      <c r="AZ8" s="66"/>
-      <c r="BA8" s="66"/>
-      <c r="BB8" s="66"/>
-      <c r="BC8" s="66"/>
-      <c r="BD8" s="66"/>
-      <c r="BE8" s="66"/>
-      <c r="BF8" s="66"/>
-      <c r="BG8" s="66"/>
-      <c r="BH8" s="66"/>
-      <c r="BI8" s="67"/>
-      <c r="BJ8" s="69"/>
-      <c r="BK8" s="66"/>
-      <c r="BL8" s="66"/>
-      <c r="BM8" s="80"/>
-      <c r="BN8" s="83"/>
-      <c r="BO8" s="86"/>
-      <c r="BP8" s="89"/>
-      <c r="BQ8" s="92"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="65"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="65"/>
+      <c r="Q8" s="65"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="69"/>
+      <c r="T8" s="65"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="65"/>
+      <c r="W8" s="65"/>
+      <c r="X8" s="65"/>
+      <c r="Y8" s="65"/>
+      <c r="Z8" s="65"/>
+      <c r="AA8" s="65"/>
+      <c r="AB8" s="65"/>
+      <c r="AC8" s="65"/>
+      <c r="AD8" s="65"/>
+      <c r="AE8" s="65"/>
+      <c r="AF8" s="65"/>
+      <c r="AG8" s="65"/>
+      <c r="AH8" s="65"/>
+      <c r="AI8" s="65"/>
+      <c r="AJ8" s="65"/>
+      <c r="AK8" s="65"/>
+      <c r="AL8" s="70"/>
+      <c r="AM8" s="70"/>
+      <c r="AN8" s="66"/>
+      <c r="AO8" s="74"/>
+      <c r="AP8" s="75"/>
+      <c r="AQ8" s="75"/>
+      <c r="AR8" s="75"/>
+      <c r="AS8" s="75"/>
+      <c r="AT8" s="75"/>
+      <c r="AU8" s="75"/>
+      <c r="AV8" s="75"/>
+      <c r="AW8" s="75"/>
+      <c r="AX8" s="75"/>
+      <c r="AY8" s="75"/>
+      <c r="AZ8" s="75"/>
+      <c r="BA8" s="75"/>
+      <c r="BB8" s="75"/>
+      <c r="BC8" s="75"/>
+      <c r="BD8" s="75"/>
+      <c r="BE8" s="75"/>
+      <c r="BF8" s="75"/>
+      <c r="BG8" s="75"/>
+      <c r="BH8" s="75"/>
+      <c r="BI8" s="76"/>
+      <c r="BJ8" s="78"/>
+      <c r="BK8" s="75"/>
+      <c r="BL8" s="75"/>
+      <c r="BM8" s="44"/>
+      <c r="BN8" s="47"/>
+      <c r="BO8" s="50"/>
+      <c r="BP8" s="53"/>
+      <c r="BQ8" s="56"/>
     </row>
     <row r="9" spans="1:69" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="71"/>
+      <c r="A9" s="80"/>
       <c r="B9" s="25" t="str">
         <f>+'1ER TRIMESTRE'!B9</f>
         <v>MATUTINA</v>
       </c>
-      <c r="C9" s="25">
-        <f>+'1ER TRIMESTRE'!C9</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="73" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="74"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="74"/>
-      <c r="M9" s="74"/>
-      <c r="N9" s="74"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="74"/>
-      <c r="Q9" s="74"/>
-      <c r="R9" s="75"/>
-      <c r="S9" s="76" t="s">
+      <c r="C9" s="25"/>
+      <c r="D9" s="82" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="83"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="83"/>
+      <c r="Q9" s="83"/>
+      <c r="R9" s="84"/>
+      <c r="S9" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="T9" s="74"/>
-      <c r="U9" s="74"/>
-      <c r="V9" s="74"/>
-      <c r="W9" s="74"/>
-      <c r="X9" s="74"/>
-      <c r="Y9" s="74"/>
-      <c r="Z9" s="74"/>
-      <c r="AA9" s="74"/>
-      <c r="AB9" s="74"/>
-      <c r="AC9" s="74"/>
-      <c r="AD9" s="74"/>
-      <c r="AE9" s="74"/>
-      <c r="AF9" s="74"/>
-      <c r="AG9" s="74"/>
-      <c r="AH9" s="74"/>
-      <c r="AI9" s="74"/>
-      <c r="AJ9" s="74"/>
-      <c r="AK9" s="74"/>
-      <c r="AL9" s="77"/>
-      <c r="AM9" s="77"/>
-      <c r="AN9" s="75"/>
-      <c r="AO9" s="73" t="s">
+      <c r="T9" s="83"/>
+      <c r="U9" s="83"/>
+      <c r="V9" s="83"/>
+      <c r="W9" s="83"/>
+      <c r="X9" s="83"/>
+      <c r="Y9" s="83"/>
+      <c r="Z9" s="83"/>
+      <c r="AA9" s="83"/>
+      <c r="AB9" s="83"/>
+      <c r="AC9" s="83"/>
+      <c r="AD9" s="83"/>
+      <c r="AE9" s="83"/>
+      <c r="AF9" s="83"/>
+      <c r="AG9" s="83"/>
+      <c r="AH9" s="83"/>
+      <c r="AI9" s="83"/>
+      <c r="AJ9" s="83"/>
+      <c r="AK9" s="83"/>
+      <c r="AL9" s="86"/>
+      <c r="AM9" s="86"/>
+      <c r="AN9" s="84"/>
+      <c r="AO9" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="AP9" s="74"/>
-      <c r="AQ9" s="74"/>
-      <c r="AR9" s="74"/>
-      <c r="AS9" s="74"/>
-      <c r="AT9" s="74"/>
-      <c r="AU9" s="74"/>
-      <c r="AV9" s="74"/>
-      <c r="AW9" s="74"/>
-      <c r="AX9" s="74"/>
-      <c r="AY9" s="74"/>
-      <c r="AZ9" s="74"/>
-      <c r="BA9" s="74"/>
-      <c r="BB9" s="74"/>
-      <c r="BC9" s="74"/>
-      <c r="BD9" s="74"/>
-      <c r="BE9" s="74"/>
-      <c r="BF9" s="74"/>
-      <c r="BG9" s="74"/>
-      <c r="BH9" s="74"/>
-      <c r="BI9" s="75"/>
-      <c r="BJ9" s="76" t="s">
-        <v>37</v>
-      </c>
-      <c r="BK9" s="74"/>
-      <c r="BL9" s="74"/>
-      <c r="BM9" s="80"/>
-      <c r="BN9" s="83"/>
-      <c r="BO9" s="86"/>
-      <c r="BP9" s="89"/>
-      <c r="BQ9" s="92"/>
+      <c r="AP9" s="83"/>
+      <c r="AQ9" s="83"/>
+      <c r="AR9" s="83"/>
+      <c r="AS9" s="83"/>
+      <c r="AT9" s="83"/>
+      <c r="AU9" s="83"/>
+      <c r="AV9" s="83"/>
+      <c r="AW9" s="83"/>
+      <c r="AX9" s="83"/>
+      <c r="AY9" s="83"/>
+      <c r="AZ9" s="83"/>
+      <c r="BA9" s="83"/>
+      <c r="BB9" s="83"/>
+      <c r="BC9" s="83"/>
+      <c r="BD9" s="83"/>
+      <c r="BE9" s="83"/>
+      <c r="BF9" s="83"/>
+      <c r="BG9" s="83"/>
+      <c r="BH9" s="83"/>
+      <c r="BI9" s="84"/>
+      <c r="BJ9" s="85" t="s">
+        <v>36</v>
+      </c>
+      <c r="BK9" s="83"/>
+      <c r="BL9" s="83"/>
+      <c r="BM9" s="44"/>
+      <c r="BN9" s="47"/>
+      <c r="BO9" s="50"/>
+      <c r="BP9" s="53"/>
+      <c r="BQ9" s="56"/>
     </row>
     <row r="10" spans="1:69" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
-      <c r="B10" s="78" t="s">
+      <c r="A10" s="81"/>
+      <c r="B10" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="36"/>
+      <c r="C10" s="96"/>
       <c r="D10" s="7">
         <v>11</v>
       </c>
@@ -13995,21 +13984,18 @@
       <c r="BL10" s="4">
         <v>6</v>
       </c>
-      <c r="BM10" s="81"/>
-      <c r="BN10" s="84"/>
-      <c r="BO10" s="87"/>
-      <c r="BP10" s="90"/>
-      <c r="BQ10" s="93"/>
+      <c r="BM10" s="45"/>
+      <c r="BN10" s="48"/>
+      <c r="BO10" s="51"/>
+      <c r="BP10" s="54"/>
+      <c r="BQ10" s="57"/>
     </row>
     <row r="11" spans="1:69" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
-      <c r="B11" s="94" t="str">
-        <f>+'1ER TRIMESTRE'!B11</f>
-        <v xml:space="preserve">AGUILAR ORELLANA  FREDDY JOEL </v>
-      </c>
-      <c r="C11" s="95"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="40"/>
       <c r="D11" s="11" t="s">
         <v>24</v>
       </c>
@@ -14218,11 +14204,8 @@
       <c r="A12" s="1">
         <v>2</v>
       </c>
-      <c r="B12" s="94">
-        <f>+'1ER TRIMESTRE'!B12</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="95"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
       <c r="D12" s="11" t="s">
         <v>24</v>
       </c>
@@ -14431,11 +14414,8 @@
       <c r="A13" s="1">
         <v>3</v>
       </c>
-      <c r="B13" s="94">
-        <f>+'1ER TRIMESTRE'!B13</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="95"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="40"/>
       <c r="D13" s="11" t="s">
         <v>24</v>
       </c>
@@ -14644,11 +14624,8 @@
       <c r="A14" s="1">
         <v>4</v>
       </c>
-      <c r="B14" s="94">
-        <f>+'1ER TRIMESTRE'!B14</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="95"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
       <c r="D14" s="11" t="s">
         <v>24</v>
       </c>
@@ -14857,11 +14834,8 @@
       <c r="A15" s="1">
         <v>5</v>
       </c>
-      <c r="B15" s="94">
-        <f>+'1ER TRIMESTRE'!B15</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="95"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="40"/>
       <c r="D15" s="11" t="s">
         <v>24</v>
       </c>
@@ -15070,11 +15044,8 @@
       <c r="A16" s="1">
         <v>6</v>
       </c>
-      <c r="B16" s="94">
-        <f>+'1ER TRIMESTRE'!B16</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="95"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="11" t="s">
         <v>24</v>
       </c>
@@ -15283,11 +15254,8 @@
       <c r="A17" s="1">
         <v>7</v>
       </c>
-      <c r="B17" s="94">
-        <f>+'1ER TRIMESTRE'!B17</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="95"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="11" t="s">
         <v>24</v>
       </c>
@@ -15496,11 +15464,8 @@
       <c r="A18" s="1">
         <v>8</v>
       </c>
-      <c r="B18" s="94">
-        <f>+'1ER TRIMESTRE'!B18</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="95"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="40"/>
       <c r="D18" s="11" t="s">
         <v>24</v>
       </c>
@@ -15709,11 +15674,8 @@
       <c r="A19" s="1">
         <v>9</v>
       </c>
-      <c r="B19" s="94">
-        <f>+'1ER TRIMESTRE'!B19</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="95"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="40"/>
       <c r="D19" s="11" t="s">
         <v>24</v>
       </c>
@@ -15922,11 +15884,8 @@
       <c r="A20" s="1">
         <v>10</v>
       </c>
-      <c r="B20" s="94">
-        <f>+'1ER TRIMESTRE'!B20</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="95"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
       <c r="D20" s="11" t="s">
         <v>24</v>
       </c>
@@ -16135,11 +16094,8 @@
       <c r="A21" s="1">
         <v>11</v>
       </c>
-      <c r="B21" s="94">
-        <f>+'1ER TRIMESTRE'!B21</f>
-        <v>0</v>
-      </c>
-      <c r="C21" s="95"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
       <c r="D21" s="11" t="s">
         <v>24</v>
       </c>
@@ -16348,11 +16304,8 @@
       <c r="A22" s="1">
         <v>12</v>
       </c>
-      <c r="B22" s="94">
-        <f>+'1ER TRIMESTRE'!B22</f>
-        <v>0</v>
-      </c>
-      <c r="C22" s="95"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="11" t="s">
         <v>24</v>
       </c>
@@ -16561,11 +16514,8 @@
       <c r="A23" s="1">
         <v>13</v>
       </c>
-      <c r="B23" s="94">
-        <f>+'1ER TRIMESTRE'!B23</f>
-        <v>0</v>
-      </c>
-      <c r="C23" s="95"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="11" t="s">
         <v>24</v>
       </c>
@@ -16774,11 +16724,8 @@
       <c r="A24" s="1">
         <v>14</v>
       </c>
-      <c r="B24" s="94">
-        <f>+'1ER TRIMESTRE'!B24</f>
-        <v>0</v>
-      </c>
-      <c r="C24" s="95"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
       <c r="D24" s="11" t="s">
         <v>24</v>
       </c>
@@ -16987,11 +16934,8 @@
       <c r="A25" s="1">
         <v>15</v>
       </c>
-      <c r="B25" s="94">
-        <f>+'1ER TRIMESTRE'!B25</f>
-        <v>0</v>
-      </c>
-      <c r="C25" s="95"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
       <c r="D25" s="11" t="s">
         <v>24</v>
       </c>
@@ -17200,11 +17144,8 @@
       <c r="A26" s="1">
         <v>16</v>
       </c>
-      <c r="B26" s="94">
-        <f>+'1ER TRIMESTRE'!B26</f>
-        <v>0</v>
-      </c>
-      <c r="C26" s="95"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="11" t="s">
         <v>24</v>
       </c>
@@ -17413,11 +17354,8 @@
       <c r="A27" s="1">
         <v>17</v>
       </c>
-      <c r="B27" s="94">
-        <f>+'1ER TRIMESTRE'!B27</f>
-        <v>0</v>
-      </c>
-      <c r="C27" s="95"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="11" t="s">
         <v>24</v>
       </c>
@@ -17626,11 +17564,8 @@
       <c r="A28" s="1">
         <v>18</v>
       </c>
-      <c r="B28" s="94">
-        <f>+'1ER TRIMESTRE'!B28</f>
-        <v>0</v>
-      </c>
-      <c r="C28" s="95"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="40"/>
       <c r="D28" s="11" t="s">
         <v>24</v>
       </c>
@@ -17839,11 +17774,8 @@
       <c r="A29" s="1">
         <v>19</v>
       </c>
-      <c r="B29" s="94">
-        <f>+'1ER TRIMESTRE'!B29</f>
-        <v>0</v>
-      </c>
-      <c r="C29" s="95"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="40"/>
       <c r="D29" s="11" t="s">
         <v>24</v>
       </c>
@@ -18052,11 +17984,8 @@
       <c r="A30" s="1">
         <v>20</v>
       </c>
-      <c r="B30" s="94">
-        <f>+'1ER TRIMESTRE'!B30</f>
-        <v>0</v>
-      </c>
-      <c r="C30" s="95"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="40"/>
       <c r="D30" s="11" t="s">
         <v>24</v>
       </c>
@@ -18265,11 +18194,8 @@
       <c r="A31" s="1">
         <v>21</v>
       </c>
-      <c r="B31" s="94">
-        <f>+'1ER TRIMESTRE'!B31</f>
-        <v>0</v>
-      </c>
-      <c r="C31" s="95"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="40"/>
       <c r="D31" s="11" t="s">
         <v>24</v>
       </c>
@@ -18478,11 +18404,8 @@
       <c r="A32" s="1">
         <v>22</v>
       </c>
-      <c r="B32" s="94">
-        <f>+'1ER TRIMESTRE'!B32</f>
-        <v>0</v>
-      </c>
-      <c r="C32" s="95"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="40"/>
       <c r="D32" s="11" t="s">
         <v>24</v>
       </c>
@@ -18691,11 +18614,8 @@
       <c r="A33" s="1">
         <v>23</v>
       </c>
-      <c r="B33" s="94">
-        <f>+'1ER TRIMESTRE'!B33</f>
-        <v>0</v>
-      </c>
-      <c r="C33" s="95"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="40"/>
       <c r="D33" s="11" t="s">
         <v>24</v>
       </c>
@@ -18904,11 +18824,8 @@
       <c r="A34" s="1">
         <v>24</v>
       </c>
-      <c r="B34" s="94">
-        <f>+'1ER TRIMESTRE'!B34</f>
-        <v>0</v>
-      </c>
-      <c r="C34" s="95"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="40"/>
       <c r="D34" s="11" t="s">
         <v>24</v>
       </c>
@@ -19117,11 +19034,8 @@
       <c r="A35" s="1">
         <v>25</v>
       </c>
-      <c r="B35" s="94">
-        <f>+'1ER TRIMESTRE'!B35</f>
-        <v>0</v>
-      </c>
-      <c r="C35" s="95"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="40"/>
       <c r="D35" s="11" t="s">
         <v>24</v>
       </c>
@@ -19330,11 +19244,8 @@
       <c r="A36" s="1">
         <v>26</v>
       </c>
-      <c r="B36" s="94">
-        <f>+'1ER TRIMESTRE'!B36</f>
-        <v>0</v>
-      </c>
-      <c r="C36" s="95"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="40"/>
       <c r="D36" s="11" t="s">
         <v>24</v>
       </c>
@@ -19543,11 +19454,8 @@
       <c r="A37" s="1">
         <v>27</v>
       </c>
-      <c r="B37" s="94">
-        <f>+'1ER TRIMESTRE'!B37</f>
-        <v>0</v>
-      </c>
-      <c r="C37" s="95"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="40"/>
       <c r="D37" s="11" t="s">
         <v>24</v>
       </c>
@@ -19756,11 +19664,8 @@
       <c r="A38" s="1">
         <v>28</v>
       </c>
-      <c r="B38" s="94">
-        <f>+'1ER TRIMESTRE'!B38</f>
-        <v>0</v>
-      </c>
-      <c r="C38" s="95"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="40"/>
       <c r="D38" s="11" t="s">
         <v>24</v>
       </c>
@@ -19969,11 +19874,8 @@
       <c r="A39" s="1">
         <v>29</v>
       </c>
-      <c r="B39" s="94">
-        <f>+'1ER TRIMESTRE'!B39</f>
-        <v>0</v>
-      </c>
-      <c r="C39" s="95"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="40"/>
       <c r="D39" s="11" t="s">
         <v>24</v>
       </c>
@@ -20182,11 +20084,8 @@
       <c r="A40" s="1">
         <v>30</v>
       </c>
-      <c r="B40" s="94">
-        <f>+'1ER TRIMESTRE'!B40</f>
-        <v>0</v>
-      </c>
-      <c r="C40" s="95"/>
+      <c r="B40" s="39"/>
+      <c r="C40" s="40"/>
       <c r="D40" s="14" t="s">
         <v>24</v>
       </c>
@@ -20397,65 +20296,65 @@
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-      <c r="D43" s="99"/>
-      <c r="E43" s="99"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
-      <c r="K43" s="99"/>
-      <c r="L43" s="99"/>
-      <c r="M43" s="99"/>
-      <c r="N43" s="99"/>
-      <c r="O43" s="99"/>
-      <c r="P43" s="99"/>
-      <c r="Q43" s="99"/>
-      <c r="R43" s="99"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="35"/>
+      <c r="L43" s="35"/>
+      <c r="M43" s="35"/>
+      <c r="N43" s="35"/>
+      <c r="O43" s="35"/>
+      <c r="P43" s="35"/>
+      <c r="Q43" s="35"/>
+      <c r="R43" s="35"/>
       <c r="S43" s="2"/>
       <c r="T43" s="2"/>
-      <c r="U43" s="99"/>
-      <c r="V43" s="99"/>
-      <c r="W43" s="99"/>
-      <c r="X43" s="99"/>
-      <c r="Y43" s="99"/>
-      <c r="Z43" s="99"/>
-      <c r="AA43" s="99"/>
-      <c r="AB43" s="99"/>
-      <c r="AC43" s="99"/>
-      <c r="AD43" s="99"/>
-      <c r="AE43" s="99"/>
-      <c r="AF43" s="99"/>
-      <c r="AG43" s="99"/>
-      <c r="AH43" s="99"/>
-      <c r="AI43" s="99"/>
-      <c r="AM43" s="99"/>
-      <c r="AN43" s="99"/>
-      <c r="AO43" s="99"/>
-      <c r="AP43" s="99"/>
-      <c r="AQ43" s="99"/>
-      <c r="AR43" s="99"/>
-      <c r="AS43" s="99"/>
-      <c r="AT43" s="99"/>
-      <c r="AU43" s="99"/>
-      <c r="AV43" s="99"/>
-      <c r="AW43" s="99"/>
-      <c r="AX43" s="99"/>
-      <c r="AY43" s="99"/>
-      <c r="AZ43" s="99"/>
-      <c r="BA43" s="99"/>
-      <c r="BF43" s="99"/>
-      <c r="BG43" s="99"/>
-      <c r="BH43" s="99"/>
-      <c r="BI43" s="99"/>
-      <c r="BJ43" s="99"/>
-      <c r="BK43" s="99"/>
-      <c r="BL43" s="99"/>
-      <c r="BM43" s="99"/>
-      <c r="BN43" s="99"/>
-      <c r="BO43" s="99"/>
-      <c r="BP43" s="99"/>
-      <c r="BQ43" s="99"/>
+      <c r="U43" s="35"/>
+      <c r="V43" s="35"/>
+      <c r="W43" s="35"/>
+      <c r="X43" s="35"/>
+      <c r="Y43" s="35"/>
+      <c r="Z43" s="35"/>
+      <c r="AA43" s="35"/>
+      <c r="AB43" s="35"/>
+      <c r="AC43" s="35"/>
+      <c r="AD43" s="35"/>
+      <c r="AE43" s="35"/>
+      <c r="AF43" s="35"/>
+      <c r="AG43" s="35"/>
+      <c r="AH43" s="35"/>
+      <c r="AI43" s="35"/>
+      <c r="AM43" s="35"/>
+      <c r="AN43" s="35"/>
+      <c r="AO43" s="35"/>
+      <c r="AP43" s="35"/>
+      <c r="AQ43" s="35"/>
+      <c r="AR43" s="35"/>
+      <c r="AS43" s="35"/>
+      <c r="AT43" s="35"/>
+      <c r="AU43" s="35"/>
+      <c r="AV43" s="35"/>
+      <c r="AW43" s="35"/>
+      <c r="AX43" s="35"/>
+      <c r="AY43" s="35"/>
+      <c r="AZ43" s="35"/>
+      <c r="BA43" s="35"/>
+      <c r="BF43" s="35"/>
+      <c r="BG43" s="35"/>
+      <c r="BH43" s="35"/>
+      <c r="BI43" s="35"/>
+      <c r="BJ43" s="35"/>
+      <c r="BK43" s="35"/>
+      <c r="BL43" s="35"/>
+      <c r="BM43" s="35"/>
+      <c r="BN43" s="35"/>
+      <c r="BO43" s="35"/>
+      <c r="BP43" s="35"/>
+      <c r="BQ43" s="35"/>
       <c r="BX43" s="27"/>
       <c r="BY43" s="27"/>
       <c r="BZ43" s="27"/>
@@ -20464,141 +20363,141 @@
       <c r="CC43" s="28"/>
     </row>
     <row r="44" spans="1:81" s="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D44" s="100" t="s">
-        <v>55</v>
-      </c>
-      <c r="E44" s="100"/>
-      <c r="F44" s="100"/>
-      <c r="G44" s="100"/>
-      <c r="H44" s="100"/>
-      <c r="I44" s="100"/>
-      <c r="J44" s="100"/>
-      <c r="K44" s="100"/>
-      <c r="L44" s="100"/>
-      <c r="M44" s="100"/>
-      <c r="N44" s="100"/>
-      <c r="O44" s="100"/>
-      <c r="P44" s="100"/>
-      <c r="Q44" s="100"/>
-      <c r="R44" s="100"/>
-      <c r="U44" s="100" t="s">
-        <v>31</v>
-      </c>
-      <c r="V44" s="100"/>
-      <c r="W44" s="100"/>
-      <c r="X44" s="100"/>
-      <c r="Y44" s="100"/>
-      <c r="Z44" s="100"/>
-      <c r="AA44" s="100"/>
-      <c r="AB44" s="100"/>
-      <c r="AC44" s="100"/>
-      <c r="AD44" s="100"/>
-      <c r="AE44" s="100"/>
-      <c r="AF44" s="100"/>
-      <c r="AG44" s="100"/>
-      <c r="AH44" s="100"/>
-      <c r="AI44" s="100"/>
-      <c r="AM44" s="100" t="s">
-        <v>31</v>
-      </c>
-      <c r="AN44" s="100"/>
-      <c r="AO44" s="100"/>
-      <c r="AP44" s="100"/>
-      <c r="AQ44" s="100"/>
-      <c r="AR44" s="100"/>
-      <c r="AS44" s="100"/>
-      <c r="AT44" s="100"/>
-      <c r="AU44" s="100"/>
-      <c r="AV44" s="100"/>
-      <c r="AW44" s="100"/>
-      <c r="AX44" s="100"/>
-      <c r="AY44" s="100"/>
-      <c r="AZ44" s="100"/>
-      <c r="BA44" s="100"/>
-      <c r="BF44" s="101" t="s">
-        <v>53</v>
-      </c>
-      <c r="BG44" s="101"/>
-      <c r="BH44" s="101"/>
-      <c r="BI44" s="101"/>
-      <c r="BJ44" s="101"/>
-      <c r="BK44" s="101"/>
-      <c r="BL44" s="101"/>
-      <c r="BM44" s="101"/>
-      <c r="BN44" s="101"/>
-      <c r="BO44" s="101"/>
-      <c r="BP44" s="101"/>
-      <c r="BQ44" s="101"/>
+      <c r="D44" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="36"/>
+      <c r="M44" s="36"/>
+      <c r="N44" s="36"/>
+      <c r="O44" s="36"/>
+      <c r="P44" s="36"/>
+      <c r="Q44" s="36"/>
+      <c r="R44" s="36"/>
+      <c r="U44" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="V44" s="36"/>
+      <c r="W44" s="36"/>
+      <c r="X44" s="36"/>
+      <c r="Y44" s="36"/>
+      <c r="Z44" s="36"/>
+      <c r="AA44" s="36"/>
+      <c r="AB44" s="36"/>
+      <c r="AC44" s="36"/>
+      <c r="AD44" s="36"/>
+      <c r="AE44" s="36"/>
+      <c r="AF44" s="36"/>
+      <c r="AG44" s="36"/>
+      <c r="AH44" s="36"/>
+      <c r="AI44" s="36"/>
+      <c r="AM44" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="AN44" s="36"/>
+      <c r="AO44" s="36"/>
+      <c r="AP44" s="36"/>
+      <c r="AQ44" s="36"/>
+      <c r="AR44" s="36"/>
+      <c r="AS44" s="36"/>
+      <c r="AT44" s="36"/>
+      <c r="AU44" s="36"/>
+      <c r="AV44" s="36"/>
+      <c r="AW44" s="36"/>
+      <c r="AX44" s="36"/>
+      <c r="AY44" s="36"/>
+      <c r="AZ44" s="36"/>
+      <c r="BA44" s="36"/>
+      <c r="BF44" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="BG44" s="38"/>
+      <c r="BH44" s="38"/>
+      <c r="BI44" s="38"/>
+      <c r="BJ44" s="38"/>
+      <c r="BK44" s="38"/>
+      <c r="BL44" s="38"/>
+      <c r="BM44" s="38"/>
+      <c r="BN44" s="38"/>
+      <c r="BO44" s="38"/>
+      <c r="BP44" s="38"/>
+      <c r="BQ44" s="38"/>
       <c r="BX44" s="32"/>
       <c r="BY44" s="32"/>
       <c r="BZ44" s="32"/>
     </row>
     <row r="45" spans="1:81" s="29" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D45" s="96" t="s">
+      <c r="D45" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="E45" s="96"/>
-      <c r="F45" s="96"/>
-      <c r="G45" s="96"/>
-      <c r="H45" s="96"/>
-      <c r="I45" s="96"/>
-      <c r="J45" s="96"/>
-      <c r="K45" s="96"/>
-      <c r="L45" s="96"/>
-      <c r="M45" s="96"/>
-      <c r="N45" s="96"/>
-      <c r="O45" s="96"/>
-      <c r="P45" s="96"/>
-      <c r="Q45" s="96"/>
-      <c r="R45" s="96"/>
-      <c r="U45" s="96" t="s">
-        <v>41</v>
-      </c>
-      <c r="V45" s="96"/>
-      <c r="W45" s="96"/>
-      <c r="X45" s="96"/>
-      <c r="Y45" s="96"/>
-      <c r="Z45" s="96"/>
-      <c r="AA45" s="96"/>
-      <c r="AB45" s="96"/>
-      <c r="AC45" s="96"/>
-      <c r="AD45" s="96"/>
-      <c r="AE45" s="96"/>
-      <c r="AF45" s="96"/>
-      <c r="AG45" s="96"/>
-      <c r="AH45" s="96"/>
-      <c r="AI45" s="96"/>
-      <c r="AM45" s="96" t="s">
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="37"/>
+      <c r="I45" s="37"/>
+      <c r="J45" s="37"/>
+      <c r="K45" s="37"/>
+      <c r="L45" s="37"/>
+      <c r="M45" s="37"/>
+      <c r="N45" s="37"/>
+      <c r="O45" s="37"/>
+      <c r="P45" s="37"/>
+      <c r="Q45" s="37"/>
+      <c r="R45" s="37"/>
+      <c r="U45" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="V45" s="37"/>
+      <c r="W45" s="37"/>
+      <c r="X45" s="37"/>
+      <c r="Y45" s="37"/>
+      <c r="Z45" s="37"/>
+      <c r="AA45" s="37"/>
+      <c r="AB45" s="37"/>
+      <c r="AC45" s="37"/>
+      <c r="AD45" s="37"/>
+      <c r="AE45" s="37"/>
+      <c r="AF45" s="37"/>
+      <c r="AG45" s="37"/>
+      <c r="AH45" s="37"/>
+      <c r="AI45" s="37"/>
+      <c r="AM45" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN45" s="37"/>
+      <c r="AO45" s="37"/>
+      <c r="AP45" s="37"/>
+      <c r="AQ45" s="37"/>
+      <c r="AR45" s="37"/>
+      <c r="AS45" s="37"/>
+      <c r="AT45" s="37"/>
+      <c r="AU45" s="37"/>
+      <c r="AV45" s="37"/>
+      <c r="AW45" s="37"/>
+      <c r="AX45" s="37"/>
+      <c r="AY45" s="37"/>
+      <c r="AZ45" s="37"/>
+      <c r="BA45" s="37"/>
+      <c r="BF45" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="AN45" s="96"/>
-      <c r="AO45" s="96"/>
-      <c r="AP45" s="96"/>
-      <c r="AQ45" s="96"/>
-      <c r="AR45" s="96"/>
-      <c r="AS45" s="96"/>
-      <c r="AT45" s="96"/>
-      <c r="AU45" s="96"/>
-      <c r="AV45" s="96"/>
-      <c r="AW45" s="96"/>
-      <c r="AX45" s="96"/>
-      <c r="AY45" s="96"/>
-      <c r="AZ45" s="96"/>
-      <c r="BA45" s="96"/>
-      <c r="BF45" s="96" t="s">
-        <v>33</v>
-      </c>
-      <c r="BG45" s="96"/>
-      <c r="BH45" s="96"/>
-      <c r="BI45" s="96"/>
-      <c r="BJ45" s="96"/>
-      <c r="BK45" s="96"/>
-      <c r="BL45" s="96"/>
-      <c r="BM45" s="96"/>
-      <c r="BN45" s="96"/>
-      <c r="BO45" s="96"/>
-      <c r="BP45" s="96"/>
-      <c r="BQ45" s="96"/>
+      <c r="BG45" s="37"/>
+      <c r="BH45" s="37"/>
+      <c r="BI45" s="37"/>
+      <c r="BJ45" s="37"/>
+      <c r="BK45" s="37"/>
+      <c r="BL45" s="37"/>
+      <c r="BM45" s="37"/>
+      <c r="BN45" s="37"/>
+      <c r="BO45" s="37"/>
+      <c r="BP45" s="37"/>
+      <c r="BQ45" s="37"/>
       <c r="BX45" s="30"/>
       <c r="BY45" s="30"/>
       <c r="BZ45" s="30"/>
@@ -21553,6 +21452,58 @@
     <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="AM44:BA44"/>
+    <mergeCell ref="AM45:BA45"/>
+    <mergeCell ref="BF43:BQ43"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:R8"/>
+    <mergeCell ref="S7:AN8"/>
+    <mergeCell ref="AO7:BI8"/>
+    <mergeCell ref="BJ7:BL8"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="D9:R9"/>
+    <mergeCell ref="S9:AN9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:R6"/>
+    <mergeCell ref="S6:AN6"/>
+    <mergeCell ref="AO6:BI6"/>
+    <mergeCell ref="BJ6:BL6"/>
+    <mergeCell ref="A1:BQ1"/>
+    <mergeCell ref="A2:BQ2"/>
+    <mergeCell ref="A3:BQ3"/>
+    <mergeCell ref="A4:BQ4"/>
+    <mergeCell ref="A5:BQ5"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="D43:R43"/>
     <mergeCell ref="U43:AI43"/>
     <mergeCell ref="D45:R45"/>
@@ -21569,58 +21520,6 @@
     <mergeCell ref="BF44:BQ44"/>
     <mergeCell ref="BF45:BQ45"/>
     <mergeCell ref="AM43:BA43"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A1:BQ1"/>
-    <mergeCell ref="A2:BQ2"/>
-    <mergeCell ref="A3:BQ3"/>
-    <mergeCell ref="A4:BQ4"/>
-    <mergeCell ref="A5:BQ5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:R6"/>
-    <mergeCell ref="S6:AN6"/>
-    <mergeCell ref="AO6:BI6"/>
-    <mergeCell ref="BJ6:BL6"/>
-    <mergeCell ref="AM44:BA44"/>
-    <mergeCell ref="AM45:BA45"/>
-    <mergeCell ref="BF43:BQ43"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:R8"/>
-    <mergeCell ref="S7:AN8"/>
-    <mergeCell ref="AO7:BI8"/>
-    <mergeCell ref="BJ7:BL8"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="D9:R9"/>
-    <mergeCell ref="S9:AN9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <conditionalFormatting sqref="D11:BL40">
     <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="F">
@@ -21702,651 +21601,648 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:83" ht="28" x14ac:dyDescent="0.2">
-      <c r="A1" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
-      <c r="AB1" s="44"/>
-      <c r="AC1" s="44"/>
-      <c r="AD1" s="44"/>
-      <c r="AE1" s="44"/>
-      <c r="AF1" s="44"/>
-      <c r="AG1" s="44"/>
-      <c r="AH1" s="44"/>
-      <c r="AI1" s="44"/>
-      <c r="AJ1" s="44"/>
-      <c r="AK1" s="44"/>
-      <c r="AL1" s="44"/>
-      <c r="AM1" s="44"/>
-      <c r="AN1" s="44"/>
-      <c r="AO1" s="44"/>
-      <c r="AP1" s="44"/>
-      <c r="AQ1" s="44"/>
-      <c r="AR1" s="44"/>
-      <c r="AS1" s="44"/>
-      <c r="AT1" s="44"/>
-      <c r="AU1" s="44"/>
-      <c r="AV1" s="44"/>
-      <c r="AW1" s="44"/>
-      <c r="AX1" s="44"/>
-      <c r="AY1" s="44"/>
-      <c r="AZ1" s="44"/>
-      <c r="BA1" s="44"/>
-      <c r="BB1" s="44"/>
-      <c r="BC1" s="44"/>
-      <c r="BD1" s="44"/>
-      <c r="BE1" s="44"/>
-      <c r="BF1" s="44"/>
-      <c r="BG1" s="44"/>
-      <c r="BH1" s="44"/>
-      <c r="BI1" s="44"/>
-      <c r="BJ1" s="44"/>
-      <c r="BK1" s="44"/>
-      <c r="BL1" s="44"/>
-      <c r="BM1" s="44"/>
-      <c r="BN1" s="44"/>
-      <c r="BO1" s="44"/>
-      <c r="BP1" s="44"/>
-      <c r="BQ1" s="44"/>
-      <c r="BR1" s="44"/>
-      <c r="BS1" s="44"/>
-      <c r="BT1" s="44"/>
-      <c r="BU1" s="44"/>
-      <c r="BV1" s="44"/>
-      <c r="BW1" s="44"/>
-      <c r="BX1" s="44"/>
-      <c r="BY1" s="44"/>
-      <c r="BZ1" s="44"/>
+      <c r="A1" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
+      <c r="M1" s="90"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="90"/>
+      <c r="Q1" s="90"/>
+      <c r="R1" s="90"/>
+      <c r="S1" s="90"/>
+      <c r="T1" s="90"/>
+      <c r="U1" s="90"/>
+      <c r="V1" s="90"/>
+      <c r="W1" s="90"/>
+      <c r="X1" s="90"/>
+      <c r="Y1" s="90"/>
+      <c r="Z1" s="90"/>
+      <c r="AA1" s="90"/>
+      <c r="AB1" s="90"/>
+      <c r="AC1" s="90"/>
+      <c r="AD1" s="90"/>
+      <c r="AE1" s="90"/>
+      <c r="AF1" s="90"/>
+      <c r="AG1" s="90"/>
+      <c r="AH1" s="90"/>
+      <c r="AI1" s="90"/>
+      <c r="AJ1" s="90"/>
+      <c r="AK1" s="90"/>
+      <c r="AL1" s="90"/>
+      <c r="AM1" s="90"/>
+      <c r="AN1" s="90"/>
+      <c r="AO1" s="90"/>
+      <c r="AP1" s="90"/>
+      <c r="AQ1" s="90"/>
+      <c r="AR1" s="90"/>
+      <c r="AS1" s="90"/>
+      <c r="AT1" s="90"/>
+      <c r="AU1" s="90"/>
+      <c r="AV1" s="90"/>
+      <c r="AW1" s="90"/>
+      <c r="AX1" s="90"/>
+      <c r="AY1" s="90"/>
+      <c r="AZ1" s="90"/>
+      <c r="BA1" s="90"/>
+      <c r="BB1" s="90"/>
+      <c r="BC1" s="90"/>
+      <c r="BD1" s="90"/>
+      <c r="BE1" s="90"/>
+      <c r="BF1" s="90"/>
+      <c r="BG1" s="90"/>
+      <c r="BH1" s="90"/>
+      <c r="BI1" s="90"/>
+      <c r="BJ1" s="90"/>
+      <c r="BK1" s="90"/>
+      <c r="BL1" s="90"/>
+      <c r="BM1" s="90"/>
+      <c r="BN1" s="90"/>
+      <c r="BO1" s="90"/>
+      <c r="BP1" s="90"/>
+      <c r="BQ1" s="90"/>
+      <c r="BR1" s="90"/>
+      <c r="BS1" s="90"/>
+      <c r="BT1" s="90"/>
+      <c r="BU1" s="90"/>
+      <c r="BV1" s="90"/>
+      <c r="BW1" s="90"/>
+      <c r="BX1" s="90"/>
+      <c r="BY1" s="90"/>
+      <c r="BZ1" s="90"/>
       <c r="CA1" s="8"/>
       <c r="CB1" s="8"/>
       <c r="CC1" s="8"/>
       <c r="CD1" s="8"/>
     </row>
     <row r="2" spans="1:83" x14ac:dyDescent="0.2">
-      <c r="A2" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="46"/>
-      <c r="AC2" s="46"/>
-      <c r="AD2" s="46"/>
-      <c r="AE2" s="46"/>
-      <c r="AF2" s="46"/>
-      <c r="AG2" s="46"/>
-      <c r="AH2" s="46"/>
-      <c r="AI2" s="46"/>
-      <c r="AJ2" s="46"/>
-      <c r="AK2" s="46"/>
-      <c r="AL2" s="46"/>
-      <c r="AM2" s="46"/>
-      <c r="AN2" s="46"/>
-      <c r="AO2" s="46"/>
-      <c r="AP2" s="46"/>
-      <c r="AQ2" s="46"/>
-      <c r="AR2" s="46"/>
-      <c r="AS2" s="46"/>
-      <c r="AT2" s="46"/>
-      <c r="AU2" s="46"/>
-      <c r="AV2" s="46"/>
-      <c r="AW2" s="46"/>
-      <c r="AX2" s="46"/>
-      <c r="AY2" s="46"/>
-      <c r="AZ2" s="46"/>
-      <c r="BA2" s="46"/>
-      <c r="BB2" s="46"/>
-      <c r="BC2" s="46"/>
-      <c r="BD2" s="46"/>
-      <c r="BE2" s="46"/>
-      <c r="BF2" s="46"/>
-      <c r="BG2" s="46"/>
-      <c r="BH2" s="46"/>
-      <c r="BI2" s="46"/>
-      <c r="BJ2" s="46"/>
-      <c r="BK2" s="46"/>
-      <c r="BL2" s="46"/>
-      <c r="BM2" s="46"/>
-      <c r="BN2" s="46"/>
-      <c r="BO2" s="46"/>
-      <c r="BP2" s="46"/>
-      <c r="BQ2" s="46"/>
-      <c r="BR2" s="46"/>
-      <c r="BS2" s="46"/>
-      <c r="BT2" s="46"/>
-      <c r="BU2" s="46"/>
-      <c r="BV2" s="46"/>
-      <c r="BW2" s="46"/>
-      <c r="BX2" s="46"/>
-      <c r="BY2" s="46"/>
-      <c r="BZ2" s="46"/>
+      <c r="A2" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+      <c r="R2" s="92"/>
+      <c r="S2" s="92"/>
+      <c r="T2" s="92"/>
+      <c r="U2" s="92"/>
+      <c r="V2" s="92"/>
+      <c r="W2" s="92"/>
+      <c r="X2" s="92"/>
+      <c r="Y2" s="92"/>
+      <c r="Z2" s="92"/>
+      <c r="AA2" s="92"/>
+      <c r="AB2" s="92"/>
+      <c r="AC2" s="92"/>
+      <c r="AD2" s="92"/>
+      <c r="AE2" s="92"/>
+      <c r="AF2" s="92"/>
+      <c r="AG2" s="92"/>
+      <c r="AH2" s="92"/>
+      <c r="AI2" s="92"/>
+      <c r="AJ2" s="92"/>
+      <c r="AK2" s="92"/>
+      <c r="AL2" s="92"/>
+      <c r="AM2" s="92"/>
+      <c r="AN2" s="92"/>
+      <c r="AO2" s="92"/>
+      <c r="AP2" s="92"/>
+      <c r="AQ2" s="92"/>
+      <c r="AR2" s="92"/>
+      <c r="AS2" s="92"/>
+      <c r="AT2" s="92"/>
+      <c r="AU2" s="92"/>
+      <c r="AV2" s="92"/>
+      <c r="AW2" s="92"/>
+      <c r="AX2" s="92"/>
+      <c r="AY2" s="92"/>
+      <c r="AZ2" s="92"/>
+      <c r="BA2" s="92"/>
+      <c r="BB2" s="92"/>
+      <c r="BC2" s="92"/>
+      <c r="BD2" s="92"/>
+      <c r="BE2" s="92"/>
+      <c r="BF2" s="92"/>
+      <c r="BG2" s="92"/>
+      <c r="BH2" s="92"/>
+      <c r="BI2" s="92"/>
+      <c r="BJ2" s="92"/>
+      <c r="BK2" s="92"/>
+      <c r="BL2" s="92"/>
+      <c r="BM2" s="92"/>
+      <c r="BN2" s="92"/>
+      <c r="BO2" s="92"/>
+      <c r="BP2" s="92"/>
+      <c r="BQ2" s="92"/>
+      <c r="BR2" s="92"/>
+      <c r="BS2" s="92"/>
+      <c r="BT2" s="92"/>
+      <c r="BU2" s="92"/>
+      <c r="BV2" s="92"/>
+      <c r="BW2" s="92"/>
+      <c r="BX2" s="92"/>
+      <c r="BY2" s="92"/>
+      <c r="BZ2" s="92"/>
       <c r="CA2" s="9"/>
       <c r="CB2" s="9"/>
       <c r="CC2" s="9"/>
       <c r="CD2" s="9"/>
     </row>
     <row r="3" spans="1:83" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="46"/>
-      <c r="R3" s="46"/>
-      <c r="S3" s="46"/>
-      <c r="T3" s="46"/>
-      <c r="U3" s="46"/>
-      <c r="V3" s="46"/>
-      <c r="W3" s="46"/>
-      <c r="X3" s="46"/>
-      <c r="Y3" s="46"/>
-      <c r="Z3" s="46"/>
-      <c r="AA3" s="46"/>
-      <c r="AB3" s="46"/>
-      <c r="AC3" s="46"/>
-      <c r="AD3" s="46"/>
-      <c r="AE3" s="46"/>
-      <c r="AF3" s="46"/>
-      <c r="AG3" s="46"/>
-      <c r="AH3" s="46"/>
-      <c r="AI3" s="46"/>
-      <c r="AJ3" s="46"/>
-      <c r="AK3" s="46"/>
-      <c r="AL3" s="46"/>
-      <c r="AM3" s="46"/>
-      <c r="AN3" s="46"/>
-      <c r="AO3" s="46"/>
-      <c r="AP3" s="46"/>
-      <c r="AQ3" s="46"/>
-      <c r="AR3" s="46"/>
-      <c r="AS3" s="46"/>
-      <c r="AT3" s="46"/>
-      <c r="AU3" s="46"/>
-      <c r="AV3" s="46"/>
-      <c r="AW3" s="46"/>
-      <c r="AX3" s="46"/>
-      <c r="AY3" s="46"/>
-      <c r="AZ3" s="46"/>
-      <c r="BA3" s="46"/>
-      <c r="BB3" s="46"/>
-      <c r="BC3" s="46"/>
-      <c r="BD3" s="46"/>
-      <c r="BE3" s="46"/>
-      <c r="BF3" s="46"/>
-      <c r="BG3" s="46"/>
-      <c r="BH3" s="46"/>
-      <c r="BI3" s="46"/>
-      <c r="BJ3" s="46"/>
-      <c r="BK3" s="46"/>
-      <c r="BL3" s="46"/>
-      <c r="BM3" s="46"/>
-      <c r="BN3" s="46"/>
-      <c r="BO3" s="46"/>
-      <c r="BP3" s="46"/>
-      <c r="BQ3" s="46"/>
-      <c r="BR3" s="46"/>
-      <c r="BS3" s="46"/>
-      <c r="BT3" s="46"/>
-      <c r="BU3" s="46"/>
-      <c r="BV3" s="46"/>
-      <c r="BW3" s="46"/>
-      <c r="BX3" s="46"/>
-      <c r="BY3" s="46"/>
-      <c r="BZ3" s="46"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="92"/>
+      <c r="Q3" s="92"/>
+      <c r="R3" s="92"/>
+      <c r="S3" s="92"/>
+      <c r="T3" s="92"/>
+      <c r="U3" s="92"/>
+      <c r="V3" s="92"/>
+      <c r="W3" s="92"/>
+      <c r="X3" s="92"/>
+      <c r="Y3" s="92"/>
+      <c r="Z3" s="92"/>
+      <c r="AA3" s="92"/>
+      <c r="AB3" s="92"/>
+      <c r="AC3" s="92"/>
+      <c r="AD3" s="92"/>
+      <c r="AE3" s="92"/>
+      <c r="AF3" s="92"/>
+      <c r="AG3" s="92"/>
+      <c r="AH3" s="92"/>
+      <c r="AI3" s="92"/>
+      <c r="AJ3" s="92"/>
+      <c r="AK3" s="92"/>
+      <c r="AL3" s="92"/>
+      <c r="AM3" s="92"/>
+      <c r="AN3" s="92"/>
+      <c r="AO3" s="92"/>
+      <c r="AP3" s="92"/>
+      <c r="AQ3" s="92"/>
+      <c r="AR3" s="92"/>
+      <c r="AS3" s="92"/>
+      <c r="AT3" s="92"/>
+      <c r="AU3" s="92"/>
+      <c r="AV3" s="92"/>
+      <c r="AW3" s="92"/>
+      <c r="AX3" s="92"/>
+      <c r="AY3" s="92"/>
+      <c r="AZ3" s="92"/>
+      <c r="BA3" s="92"/>
+      <c r="BB3" s="92"/>
+      <c r="BC3" s="92"/>
+      <c r="BD3" s="92"/>
+      <c r="BE3" s="92"/>
+      <c r="BF3" s="92"/>
+      <c r="BG3" s="92"/>
+      <c r="BH3" s="92"/>
+      <c r="BI3" s="92"/>
+      <c r="BJ3" s="92"/>
+      <c r="BK3" s="92"/>
+      <c r="BL3" s="92"/>
+      <c r="BM3" s="92"/>
+      <c r="BN3" s="92"/>
+      <c r="BO3" s="92"/>
+      <c r="BP3" s="92"/>
+      <c r="BQ3" s="92"/>
+      <c r="BR3" s="92"/>
+      <c r="BS3" s="92"/>
+      <c r="BT3" s="92"/>
+      <c r="BU3" s="92"/>
+      <c r="BV3" s="92"/>
+      <c r="BW3" s="92"/>
+      <c r="BX3" s="92"/>
+      <c r="BY3" s="92"/>
+      <c r="BZ3" s="92"/>
       <c r="CA3" s="9"/>
       <c r="CB3" s="9"/>
       <c r="CC3" s="9"/>
       <c r="CD3" s="9"/>
     </row>
     <row r="4" spans="1:83" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="W4" s="48"/>
-      <c r="X4" s="48"/>
-      <c r="Y4" s="48"/>
-      <c r="Z4" s="48"/>
-      <c r="AA4" s="48"/>
-      <c r="AB4" s="48"/>
-      <c r="AC4" s="48"/>
-      <c r="AD4" s="48"/>
-      <c r="AE4" s="48"/>
-      <c r="AF4" s="48"/>
-      <c r="AG4" s="48"/>
-      <c r="AH4" s="48"/>
-      <c r="AI4" s="48"/>
-      <c r="AJ4" s="48"/>
-      <c r="AK4" s="48"/>
-      <c r="AL4" s="48"/>
-      <c r="AM4" s="48"/>
-      <c r="AN4" s="48"/>
-      <c r="AO4" s="48"/>
-      <c r="AP4" s="48"/>
-      <c r="AQ4" s="48"/>
-      <c r="AR4" s="48"/>
-      <c r="AS4" s="48"/>
-      <c r="AT4" s="48"/>
-      <c r="AU4" s="48"/>
-      <c r="AV4" s="48"/>
-      <c r="AW4" s="48"/>
-      <c r="AX4" s="48"/>
-      <c r="AY4" s="48"/>
-      <c r="AZ4" s="48"/>
-      <c r="BA4" s="48"/>
-      <c r="BB4" s="48"/>
-      <c r="BC4" s="48"/>
-      <c r="BD4" s="48"/>
-      <c r="BE4" s="48"/>
-      <c r="BF4" s="48"/>
-      <c r="BG4" s="48"/>
-      <c r="BH4" s="48"/>
-      <c r="BI4" s="48"/>
-      <c r="BJ4" s="48"/>
-      <c r="BK4" s="48"/>
-      <c r="BL4" s="48"/>
-      <c r="BM4" s="48"/>
-      <c r="BN4" s="48"/>
-      <c r="BO4" s="48"/>
-      <c r="BP4" s="48"/>
-      <c r="BQ4" s="48"/>
-      <c r="BR4" s="48"/>
-      <c r="BS4" s="48"/>
-      <c r="BT4" s="48"/>
-      <c r="BU4" s="48"/>
-      <c r="BV4" s="48"/>
-      <c r="BW4" s="48"/>
-      <c r="BX4" s="48"/>
-      <c r="BY4" s="48"/>
-      <c r="BZ4" s="48"/>
+      <c r="A4" s="93" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="94"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="94"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="94"/>
+      <c r="V4" s="94"/>
+      <c r="W4" s="94"/>
+      <c r="X4" s="94"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
+      <c r="AB4" s="94"/>
+      <c r="AC4" s="94"/>
+      <c r="AD4" s="94"/>
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="94"/>
+      <c r="AQ4" s="94"/>
+      <c r="AR4" s="94"/>
+      <c r="AS4" s="94"/>
+      <c r="AT4" s="94"/>
+      <c r="AU4" s="94"/>
+      <c r="AV4" s="94"/>
+      <c r="AW4" s="94"/>
+      <c r="AX4" s="94"/>
+      <c r="AY4" s="94"/>
+      <c r="AZ4" s="94"/>
+      <c r="BA4" s="94"/>
+      <c r="BB4" s="94"/>
+      <c r="BC4" s="94"/>
+      <c r="BD4" s="94"/>
+      <c r="BE4" s="94"/>
+      <c r="BF4" s="94"/>
+      <c r="BG4" s="94"/>
+      <c r="BH4" s="94"/>
+      <c r="BI4" s="94"/>
+      <c r="BJ4" s="94"/>
+      <c r="BK4" s="94"/>
+      <c r="BL4" s="94"/>
+      <c r="BM4" s="94"/>
+      <c r="BN4" s="94"/>
+      <c r="BO4" s="94"/>
+      <c r="BP4" s="94"/>
+      <c r="BQ4" s="94"/>
+      <c r="BR4" s="94"/>
+      <c r="BS4" s="94"/>
+      <c r="BT4" s="94"/>
+      <c r="BU4" s="94"/>
+      <c r="BV4" s="94"/>
+      <c r="BW4" s="94"/>
+      <c r="BX4" s="94"/>
+      <c r="BY4" s="94"/>
+      <c r="BZ4" s="94"/>
       <c r="CA4" s="10"/>
       <c r="CB4" s="10"/>
       <c r="CC4" s="10"/>
       <c r="CD4" s="10"/>
     </row>
     <row r="5" spans="1:83" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="44"/>
-      <c r="T5" s="44"/>
-      <c r="U5" s="44"/>
-      <c r="V5" s="44"/>
-      <c r="W5" s="44"/>
-      <c r="X5" s="44"/>
-      <c r="Y5" s="44"/>
-      <c r="Z5" s="44"/>
-      <c r="AA5" s="44"/>
-      <c r="AB5" s="44"/>
-      <c r="AC5" s="44"/>
-      <c r="AD5" s="44"/>
-      <c r="AE5" s="44"/>
-      <c r="AF5" s="44"/>
-      <c r="AG5" s="44"/>
-      <c r="AH5" s="44"/>
-      <c r="AI5" s="44"/>
-      <c r="AJ5" s="44"/>
-      <c r="AK5" s="44"/>
-      <c r="AL5" s="44"/>
-      <c r="AM5" s="44"/>
-      <c r="AN5" s="44"/>
-      <c r="AO5" s="44"/>
-      <c r="AP5" s="44"/>
-      <c r="AQ5" s="44"/>
-      <c r="AR5" s="44"/>
-      <c r="AS5" s="44"/>
-      <c r="AT5" s="44"/>
-      <c r="AU5" s="44"/>
-      <c r="AV5" s="44"/>
-      <c r="AW5" s="44"/>
-      <c r="AX5" s="44"/>
-      <c r="AY5" s="44"/>
-      <c r="AZ5" s="44"/>
-      <c r="BA5" s="44"/>
-      <c r="BB5" s="44"/>
-      <c r="BC5" s="44"/>
-      <c r="BD5" s="44"/>
-      <c r="BE5" s="44"/>
-      <c r="BF5" s="44"/>
-      <c r="BG5" s="44"/>
-      <c r="BH5" s="44"/>
-      <c r="BI5" s="44"/>
-      <c r="BJ5" s="44"/>
-      <c r="BK5" s="44"/>
-      <c r="BL5" s="44"/>
-      <c r="BM5" s="44"/>
-      <c r="BN5" s="44"/>
-      <c r="BO5" s="44"/>
-      <c r="BP5" s="44"/>
-      <c r="BQ5" s="44"/>
-      <c r="BR5" s="44"/>
-      <c r="BS5" s="44"/>
-      <c r="BT5" s="44"/>
-      <c r="BU5" s="44"/>
-      <c r="BV5" s="44"/>
-      <c r="BW5" s="44"/>
-      <c r="BX5" s="44"/>
-      <c r="BY5" s="44"/>
-      <c r="BZ5" s="44"/>
-      <c r="CA5" s="107" t="s">
-        <v>50</v>
-      </c>
-      <c r="CB5" s="108"/>
-      <c r="CC5" s="108"/>
-      <c r="CD5" s="108"/>
-      <c r="CE5" s="109"/>
+      <c r="A5" s="89" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="90"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
+      <c r="W5" s="90"/>
+      <c r="X5" s="90"/>
+      <c r="Y5" s="90"/>
+      <c r="Z5" s="90"/>
+      <c r="AA5" s="90"/>
+      <c r="AB5" s="90"/>
+      <c r="AC5" s="90"/>
+      <c r="AD5" s="90"/>
+      <c r="AE5" s="90"/>
+      <c r="AF5" s="90"/>
+      <c r="AG5" s="90"/>
+      <c r="AH5" s="90"/>
+      <c r="AI5" s="90"/>
+      <c r="AJ5" s="90"/>
+      <c r="AK5" s="90"/>
+      <c r="AL5" s="90"/>
+      <c r="AM5" s="90"/>
+      <c r="AN5" s="90"/>
+      <c r="AO5" s="90"/>
+      <c r="AP5" s="90"/>
+      <c r="AQ5" s="90"/>
+      <c r="AR5" s="90"/>
+      <c r="AS5" s="90"/>
+      <c r="AT5" s="90"/>
+      <c r="AU5" s="90"/>
+      <c r="AV5" s="90"/>
+      <c r="AW5" s="90"/>
+      <c r="AX5" s="90"/>
+      <c r="AY5" s="90"/>
+      <c r="AZ5" s="90"/>
+      <c r="BA5" s="90"/>
+      <c r="BB5" s="90"/>
+      <c r="BC5" s="90"/>
+      <c r="BD5" s="90"/>
+      <c r="BE5" s="90"/>
+      <c r="BF5" s="90"/>
+      <c r="BG5" s="90"/>
+      <c r="BH5" s="90"/>
+      <c r="BI5" s="90"/>
+      <c r="BJ5" s="90"/>
+      <c r="BK5" s="90"/>
+      <c r="BL5" s="90"/>
+      <c r="BM5" s="90"/>
+      <c r="BN5" s="90"/>
+      <c r="BO5" s="90"/>
+      <c r="BP5" s="90"/>
+      <c r="BQ5" s="90"/>
+      <c r="BR5" s="90"/>
+      <c r="BS5" s="90"/>
+      <c r="BT5" s="90"/>
+      <c r="BU5" s="90"/>
+      <c r="BV5" s="90"/>
+      <c r="BW5" s="90"/>
+      <c r="BX5" s="90"/>
+      <c r="BY5" s="90"/>
+      <c r="BZ5" s="90"/>
+      <c r="CA5" s="103" t="s">
+        <v>49</v>
+      </c>
+      <c r="CB5" s="104"/>
+      <c r="CC5" s="104"/>
+      <c r="CD5" s="104"/>
+      <c r="CE5" s="105"/>
     </row>
     <row r="6" spans="1:83" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="38" t="s">
+      <c r="B6" s="96"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="41" t="s">
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="98"/>
+      <c r="K6" s="98"/>
+      <c r="L6" s="98"/>
+      <c r="M6" s="98"/>
+      <c r="N6" s="98"/>
+      <c r="O6" s="98"/>
+      <c r="P6" s="98"/>
+      <c r="Q6" s="101"/>
+      <c r="R6" s="98"/>
+      <c r="S6" s="99"/>
+      <c r="T6" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="U6" s="39"/>
-      <c r="V6" s="39"/>
-      <c r="W6" s="39"/>
-      <c r="X6" s="39"/>
-      <c r="Y6" s="39"/>
-      <c r="Z6" s="39"/>
-      <c r="AA6" s="39"/>
-      <c r="AB6" s="39"/>
-      <c r="AC6" s="39"/>
-      <c r="AD6" s="39"/>
-      <c r="AE6" s="39"/>
-      <c r="AF6" s="39"/>
-      <c r="AG6" s="39"/>
-      <c r="AH6" s="39"/>
-      <c r="AI6" s="39"/>
-      <c r="AJ6" s="39"/>
-      <c r="AK6" s="40"/>
-      <c r="AL6" s="41" t="s">
+      <c r="U6" s="98"/>
+      <c r="V6" s="98"/>
+      <c r="W6" s="98"/>
+      <c r="X6" s="98"/>
+      <c r="Y6" s="98"/>
+      <c r="Z6" s="98"/>
+      <c r="AA6" s="98"/>
+      <c r="AB6" s="98"/>
+      <c r="AC6" s="98"/>
+      <c r="AD6" s="98"/>
+      <c r="AE6" s="98"/>
+      <c r="AF6" s="98"/>
+      <c r="AG6" s="98"/>
+      <c r="AH6" s="98"/>
+      <c r="AI6" s="98"/>
+      <c r="AJ6" s="98"/>
+      <c r="AK6" s="99"/>
+      <c r="AL6" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="AM6" s="39"/>
-      <c r="AN6" s="39"/>
-      <c r="AO6" s="39"/>
-      <c r="AP6" s="39"/>
-      <c r="AQ6" s="39"/>
-      <c r="AR6" s="39"/>
-      <c r="AS6" s="39"/>
-      <c r="AT6" s="39"/>
-      <c r="AU6" s="39"/>
-      <c r="AV6" s="39"/>
-      <c r="AW6" s="39"/>
-      <c r="AX6" s="39"/>
-      <c r="AY6" s="39"/>
-      <c r="AZ6" s="39"/>
-      <c r="BA6" s="39"/>
-      <c r="BB6" s="39"/>
-      <c r="BC6" s="39"/>
-      <c r="BD6" s="39"/>
-      <c r="BE6" s="40"/>
-      <c r="BF6" s="41" t="s">
+      <c r="AM6" s="98"/>
+      <c r="AN6" s="98"/>
+      <c r="AO6" s="98"/>
+      <c r="AP6" s="98"/>
+      <c r="AQ6" s="98"/>
+      <c r="AR6" s="98"/>
+      <c r="AS6" s="98"/>
+      <c r="AT6" s="98"/>
+      <c r="AU6" s="98"/>
+      <c r="AV6" s="98"/>
+      <c r="AW6" s="98"/>
+      <c r="AX6" s="98"/>
+      <c r="AY6" s="98"/>
+      <c r="AZ6" s="98"/>
+      <c r="BA6" s="98"/>
+      <c r="BB6" s="98"/>
+      <c r="BC6" s="98"/>
+      <c r="BD6" s="98"/>
+      <c r="BE6" s="99"/>
+      <c r="BF6" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="BG6" s="102"/>
-      <c r="BH6" s="102"/>
-      <c r="BI6" s="102"/>
-      <c r="BJ6" s="102"/>
-      <c r="BK6" s="102"/>
-      <c r="BL6" s="102"/>
-      <c r="BM6" s="102"/>
-      <c r="BN6" s="102"/>
-      <c r="BO6" s="102"/>
-      <c r="BP6" s="102"/>
-      <c r="BQ6" s="102"/>
-      <c r="BR6" s="102"/>
-      <c r="BS6" s="102"/>
-      <c r="BT6" s="102"/>
-      <c r="BU6" s="39"/>
-      <c r="BV6" s="79" t="s">
+      <c r="BG6" s="111"/>
+      <c r="BH6" s="111"/>
+      <c r="BI6" s="111"/>
+      <c r="BJ6" s="111"/>
+      <c r="BK6" s="111"/>
+      <c r="BL6" s="111"/>
+      <c r="BM6" s="111"/>
+      <c r="BN6" s="111"/>
+      <c r="BO6" s="111"/>
+      <c r="BP6" s="111"/>
+      <c r="BQ6" s="111"/>
+      <c r="BR6" s="111"/>
+      <c r="BS6" s="111"/>
+      <c r="BT6" s="111"/>
+      <c r="BU6" s="98"/>
+      <c r="BV6" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="BW6" s="82" t="s">
+      <c r="BW6" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="BX6" s="85" t="s">
+      <c r="BX6" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="BY6" s="88" t="s">
+      <c r="BY6" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="BZ6" s="91" t="s">
-        <v>49</v>
-      </c>
-      <c r="CA6" s="79" t="s">
+      <c r="BZ6" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="CA6" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="CB6" s="82" t="s">
+      <c r="CB6" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="CC6" s="85" t="s">
+      <c r="CC6" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="CD6" s="88" t="s">
+      <c r="CD6" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="CE6" s="91" t="s">
-        <v>51</v>
+      <c r="CE6" s="55" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:83" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49">
-        <f>+'1ER TRIMESTRE'!A7</f>
-        <v>0</v>
-      </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="52" t="s">
+      <c r="A7" s="58"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="53"/>
-      <c r="Q7" s="59"/>
-      <c r="R7" s="53"/>
-      <c r="S7" s="54"/>
-      <c r="T7" s="58" t="s">
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="68"/>
+      <c r="R7" s="62"/>
+      <c r="S7" s="63"/>
+      <c r="T7" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="U7" s="53"/>
-      <c r="V7" s="53"/>
-      <c r="W7" s="53"/>
-      <c r="X7" s="53"/>
-      <c r="Y7" s="53"/>
-      <c r="Z7" s="53"/>
-      <c r="AA7" s="53"/>
-      <c r="AB7" s="53"/>
-      <c r="AC7" s="53"/>
-      <c r="AD7" s="53"/>
-      <c r="AE7" s="53"/>
-      <c r="AF7" s="53"/>
-      <c r="AG7" s="53"/>
-      <c r="AH7" s="53"/>
-      <c r="AI7" s="53"/>
-      <c r="AJ7" s="53"/>
-      <c r="AK7" s="54"/>
-      <c r="AL7" s="62" t="s">
+      <c r="U7" s="62"/>
+      <c r="V7" s="62"/>
+      <c r="W7" s="62"/>
+      <c r="X7" s="62"/>
+      <c r="Y7" s="62"/>
+      <c r="Z7" s="62"/>
+      <c r="AA7" s="62"/>
+      <c r="AB7" s="62"/>
+      <c r="AC7" s="62"/>
+      <c r="AD7" s="62"/>
+      <c r="AE7" s="62"/>
+      <c r="AF7" s="62"/>
+      <c r="AG7" s="62"/>
+      <c r="AH7" s="62"/>
+      <c r="AI7" s="62"/>
+      <c r="AJ7" s="62"/>
+      <c r="AK7" s="63"/>
+      <c r="AL7" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM7" s="72"/>
+      <c r="AN7" s="72"/>
+      <c r="AO7" s="72"/>
+      <c r="AP7" s="72"/>
+      <c r="AQ7" s="72"/>
+      <c r="AR7" s="72"/>
+      <c r="AS7" s="72"/>
+      <c r="AT7" s="72"/>
+      <c r="AU7" s="72"/>
+      <c r="AV7" s="72"/>
+      <c r="AW7" s="72"/>
+      <c r="AX7" s="72"/>
+      <c r="AY7" s="72"/>
+      <c r="AZ7" s="72"/>
+      <c r="BA7" s="72"/>
+      <c r="BB7" s="72"/>
+      <c r="BC7" s="72"/>
+      <c r="BD7" s="72"/>
+      <c r="BE7" s="73"/>
+      <c r="BF7" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="AM7" s="63"/>
-      <c r="AN7" s="63"/>
-      <c r="AO7" s="63"/>
-      <c r="AP7" s="63"/>
-      <c r="AQ7" s="63"/>
-      <c r="AR7" s="63"/>
-      <c r="AS7" s="63"/>
-      <c r="AT7" s="63"/>
-      <c r="AU7" s="63"/>
-      <c r="AV7" s="63"/>
-      <c r="AW7" s="63"/>
-      <c r="AX7" s="63"/>
-      <c r="AY7" s="63"/>
-      <c r="AZ7" s="63"/>
-      <c r="BA7" s="63"/>
-      <c r="BB7" s="63"/>
-      <c r="BC7" s="63"/>
-      <c r="BD7" s="63"/>
-      <c r="BE7" s="64"/>
-      <c r="BF7" s="68" t="s">
-        <v>40</v>
-      </c>
-      <c r="BG7" s="103"/>
-      <c r="BH7" s="103"/>
-      <c r="BI7" s="103"/>
-      <c r="BJ7" s="103"/>
-      <c r="BK7" s="103"/>
-      <c r="BL7" s="103"/>
-      <c r="BM7" s="103"/>
-      <c r="BN7" s="103"/>
-      <c r="BO7" s="103"/>
-      <c r="BP7" s="103"/>
-      <c r="BQ7" s="103"/>
-      <c r="BR7" s="103"/>
-      <c r="BS7" s="103"/>
-      <c r="BT7" s="103"/>
-      <c r="BU7" s="63"/>
-      <c r="BV7" s="80"/>
-      <c r="BW7" s="83"/>
-      <c r="BX7" s="86"/>
-      <c r="BY7" s="89"/>
-      <c r="BZ7" s="92"/>
-      <c r="CA7" s="80"/>
-      <c r="CB7" s="83"/>
-      <c r="CC7" s="86"/>
-      <c r="CD7" s="89"/>
-      <c r="CE7" s="110"/>
+      <c r="BG7" s="108"/>
+      <c r="BH7" s="108"/>
+      <c r="BI7" s="108"/>
+      <c r="BJ7" s="108"/>
+      <c r="BK7" s="108"/>
+      <c r="BL7" s="108"/>
+      <c r="BM7" s="108"/>
+      <c r="BN7" s="108"/>
+      <c r="BO7" s="108"/>
+      <c r="BP7" s="108"/>
+      <c r="BQ7" s="108"/>
+      <c r="BR7" s="108"/>
+      <c r="BS7" s="108"/>
+      <c r="BT7" s="108"/>
+      <c r="BU7" s="72"/>
+      <c r="BV7" s="44"/>
+      <c r="BW7" s="47"/>
+      <c r="BX7" s="50"/>
+      <c r="BY7" s="53"/>
+      <c r="BZ7" s="56"/>
+      <c r="CA7" s="44"/>
+      <c r="CB7" s="47"/>
+      <c r="CC7" s="50"/>
+      <c r="CD7" s="53"/>
+      <c r="CE7" s="106"/>
     </row>
     <row r="8" spans="1:83" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="79" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -22355,192 +22251,189 @@
       <c r="C8" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="55"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="56"/>
-      <c r="P8" s="56"/>
-      <c r="Q8" s="61"/>
-      <c r="R8" s="56"/>
-      <c r="S8" s="57"/>
-      <c r="T8" s="60"/>
-      <c r="U8" s="56"/>
-      <c r="V8" s="56"/>
-      <c r="W8" s="56"/>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="56"/>
-      <c r="Z8" s="56"/>
-      <c r="AA8" s="56"/>
-      <c r="AB8" s="56"/>
-      <c r="AC8" s="56"/>
-      <c r="AD8" s="56"/>
-      <c r="AE8" s="56"/>
-      <c r="AF8" s="56"/>
-      <c r="AG8" s="56"/>
-      <c r="AH8" s="56"/>
-      <c r="AI8" s="56"/>
-      <c r="AJ8" s="56"/>
-      <c r="AK8" s="57"/>
-      <c r="AL8" s="65"/>
-      <c r="AM8" s="66"/>
-      <c r="AN8" s="66"/>
-      <c r="AO8" s="66"/>
-      <c r="AP8" s="66"/>
-      <c r="AQ8" s="66"/>
-      <c r="AR8" s="66"/>
-      <c r="AS8" s="66"/>
-      <c r="AT8" s="66"/>
-      <c r="AU8" s="66"/>
-      <c r="AV8" s="66"/>
-      <c r="AW8" s="66"/>
-      <c r="AX8" s="66"/>
-      <c r="AY8" s="66"/>
-      <c r="AZ8" s="66"/>
-      <c r="BA8" s="66"/>
-      <c r="BB8" s="66"/>
-      <c r="BC8" s="66"/>
-      <c r="BD8" s="66"/>
-      <c r="BE8" s="67"/>
-      <c r="BF8" s="69"/>
-      <c r="BG8" s="104"/>
-      <c r="BH8" s="104"/>
-      <c r="BI8" s="104"/>
-      <c r="BJ8" s="104"/>
-      <c r="BK8" s="104"/>
-      <c r="BL8" s="104"/>
-      <c r="BM8" s="104"/>
-      <c r="BN8" s="104"/>
-      <c r="BO8" s="104"/>
-      <c r="BP8" s="104"/>
-      <c r="BQ8" s="104"/>
-      <c r="BR8" s="104"/>
-      <c r="BS8" s="104"/>
-      <c r="BT8" s="104"/>
-      <c r="BU8" s="66"/>
-      <c r="BV8" s="80"/>
-      <c r="BW8" s="83"/>
-      <c r="BX8" s="86"/>
-      <c r="BY8" s="89"/>
-      <c r="BZ8" s="92"/>
-      <c r="CA8" s="80"/>
-      <c r="CB8" s="83"/>
-      <c r="CC8" s="86"/>
-      <c r="CD8" s="89"/>
-      <c r="CE8" s="110"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="65"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="65"/>
+      <c r="Q8" s="70"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="66"/>
+      <c r="T8" s="69"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="65"/>
+      <c r="W8" s="65"/>
+      <c r="X8" s="65"/>
+      <c r="Y8" s="65"/>
+      <c r="Z8" s="65"/>
+      <c r="AA8" s="65"/>
+      <c r="AB8" s="65"/>
+      <c r="AC8" s="65"/>
+      <c r="AD8" s="65"/>
+      <c r="AE8" s="65"/>
+      <c r="AF8" s="65"/>
+      <c r="AG8" s="65"/>
+      <c r="AH8" s="65"/>
+      <c r="AI8" s="65"/>
+      <c r="AJ8" s="65"/>
+      <c r="AK8" s="66"/>
+      <c r="AL8" s="74"/>
+      <c r="AM8" s="75"/>
+      <c r="AN8" s="75"/>
+      <c r="AO8" s="75"/>
+      <c r="AP8" s="75"/>
+      <c r="AQ8" s="75"/>
+      <c r="AR8" s="75"/>
+      <c r="AS8" s="75"/>
+      <c r="AT8" s="75"/>
+      <c r="AU8" s="75"/>
+      <c r="AV8" s="75"/>
+      <c r="AW8" s="75"/>
+      <c r="AX8" s="75"/>
+      <c r="AY8" s="75"/>
+      <c r="AZ8" s="75"/>
+      <c r="BA8" s="75"/>
+      <c r="BB8" s="75"/>
+      <c r="BC8" s="75"/>
+      <c r="BD8" s="75"/>
+      <c r="BE8" s="76"/>
+      <c r="BF8" s="78"/>
+      <c r="BG8" s="109"/>
+      <c r="BH8" s="109"/>
+      <c r="BI8" s="109"/>
+      <c r="BJ8" s="109"/>
+      <c r="BK8" s="109"/>
+      <c r="BL8" s="109"/>
+      <c r="BM8" s="109"/>
+      <c r="BN8" s="109"/>
+      <c r="BO8" s="109"/>
+      <c r="BP8" s="109"/>
+      <c r="BQ8" s="109"/>
+      <c r="BR8" s="109"/>
+      <c r="BS8" s="109"/>
+      <c r="BT8" s="109"/>
+      <c r="BU8" s="75"/>
+      <c r="BV8" s="44"/>
+      <c r="BW8" s="47"/>
+      <c r="BX8" s="50"/>
+      <c r="BY8" s="53"/>
+      <c r="BZ8" s="56"/>
+      <c r="CA8" s="44"/>
+      <c r="CB8" s="47"/>
+      <c r="CC8" s="50"/>
+      <c r="CD8" s="53"/>
+      <c r="CE8" s="106"/>
     </row>
     <row r="9" spans="1:83" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="71"/>
+      <c r="A9" s="80"/>
       <c r="B9" s="25" t="str">
         <f>+'1ER TRIMESTRE'!B9</f>
         <v>MATUTINA</v>
       </c>
-      <c r="C9" s="26">
-        <f>+'1ER TRIMESTRE'!C9</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="73" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="74"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="74"/>
-      <c r="M9" s="74"/>
-      <c r="N9" s="74"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="74"/>
-      <c r="Q9" s="77"/>
-      <c r="R9" s="74"/>
-      <c r="S9" s="75"/>
-      <c r="T9" s="76" t="s">
+      <c r="C9" s="26"/>
+      <c r="D9" s="82" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="83"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="83"/>
+      <c r="Q9" s="86"/>
+      <c r="R9" s="83"/>
+      <c r="S9" s="84"/>
+      <c r="T9" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="U9" s="74"/>
-      <c r="V9" s="74"/>
-      <c r="W9" s="74"/>
-      <c r="X9" s="74"/>
-      <c r="Y9" s="74"/>
-      <c r="Z9" s="74"/>
-      <c r="AA9" s="74"/>
-      <c r="AB9" s="74"/>
-      <c r="AC9" s="74"/>
-      <c r="AD9" s="74"/>
-      <c r="AE9" s="74"/>
-      <c r="AF9" s="74"/>
-      <c r="AG9" s="74"/>
-      <c r="AH9" s="74"/>
-      <c r="AI9" s="74"/>
-      <c r="AJ9" s="74"/>
-      <c r="AK9" s="75"/>
-      <c r="AL9" s="73" t="s">
+      <c r="U9" s="83"/>
+      <c r="V9" s="83"/>
+      <c r="W9" s="83"/>
+      <c r="X9" s="83"/>
+      <c r="Y9" s="83"/>
+      <c r="Z9" s="83"/>
+      <c r="AA9" s="83"/>
+      <c r="AB9" s="83"/>
+      <c r="AC9" s="83"/>
+      <c r="AD9" s="83"/>
+      <c r="AE9" s="83"/>
+      <c r="AF9" s="83"/>
+      <c r="AG9" s="83"/>
+      <c r="AH9" s="83"/>
+      <c r="AI9" s="83"/>
+      <c r="AJ9" s="83"/>
+      <c r="AK9" s="84"/>
+      <c r="AL9" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="AM9" s="74"/>
-      <c r="AN9" s="74"/>
-      <c r="AO9" s="74"/>
-      <c r="AP9" s="74"/>
-      <c r="AQ9" s="74"/>
-      <c r="AR9" s="74"/>
-      <c r="AS9" s="74"/>
-      <c r="AT9" s="74"/>
-      <c r="AU9" s="74"/>
-      <c r="AV9" s="74"/>
-      <c r="AW9" s="74"/>
-      <c r="AX9" s="74"/>
-      <c r="AY9" s="74"/>
-      <c r="AZ9" s="74"/>
-      <c r="BA9" s="74"/>
-      <c r="BB9" s="74"/>
-      <c r="BC9" s="74"/>
-      <c r="BD9" s="74"/>
-      <c r="BE9" s="75"/>
-      <c r="BF9" s="76" t="s">
-        <v>35</v>
-      </c>
-      <c r="BG9" s="105"/>
-      <c r="BH9" s="105"/>
-      <c r="BI9" s="105"/>
-      <c r="BJ9" s="105"/>
-      <c r="BK9" s="105"/>
-      <c r="BL9" s="105"/>
-      <c r="BM9" s="105"/>
-      <c r="BN9" s="105"/>
-      <c r="BO9" s="105"/>
-      <c r="BP9" s="105"/>
-      <c r="BQ9" s="105"/>
-      <c r="BR9" s="105"/>
-      <c r="BS9" s="105"/>
-      <c r="BT9" s="105"/>
-      <c r="BU9" s="74"/>
-      <c r="BV9" s="80"/>
-      <c r="BW9" s="83"/>
-      <c r="BX9" s="86"/>
-      <c r="BY9" s="89"/>
-      <c r="BZ9" s="92"/>
-      <c r="CA9" s="80"/>
-      <c r="CB9" s="83"/>
-      <c r="CC9" s="86"/>
-      <c r="CD9" s="89"/>
-      <c r="CE9" s="110"/>
+      <c r="AM9" s="83"/>
+      <c r="AN9" s="83"/>
+      <c r="AO9" s="83"/>
+      <c r="AP9" s="83"/>
+      <c r="AQ9" s="83"/>
+      <c r="AR9" s="83"/>
+      <c r="AS9" s="83"/>
+      <c r="AT9" s="83"/>
+      <c r="AU9" s="83"/>
+      <c r="AV9" s="83"/>
+      <c r="AW9" s="83"/>
+      <c r="AX9" s="83"/>
+      <c r="AY9" s="83"/>
+      <c r="AZ9" s="83"/>
+      <c r="BA9" s="83"/>
+      <c r="BB9" s="83"/>
+      <c r="BC9" s="83"/>
+      <c r="BD9" s="83"/>
+      <c r="BE9" s="84"/>
+      <c r="BF9" s="85" t="s">
+        <v>34</v>
+      </c>
+      <c r="BG9" s="110"/>
+      <c r="BH9" s="110"/>
+      <c r="BI9" s="110"/>
+      <c r="BJ9" s="110"/>
+      <c r="BK9" s="110"/>
+      <c r="BL9" s="110"/>
+      <c r="BM9" s="110"/>
+      <c r="BN9" s="110"/>
+      <c r="BO9" s="110"/>
+      <c r="BP9" s="110"/>
+      <c r="BQ9" s="110"/>
+      <c r="BR9" s="110"/>
+      <c r="BS9" s="110"/>
+      <c r="BT9" s="110"/>
+      <c r="BU9" s="83"/>
+      <c r="BV9" s="44"/>
+      <c r="BW9" s="47"/>
+      <c r="BX9" s="50"/>
+      <c r="BY9" s="53"/>
+      <c r="BZ9" s="56"/>
+      <c r="CA9" s="44"/>
+      <c r="CB9" s="47"/>
+      <c r="CC9" s="50"/>
+      <c r="CD9" s="53"/>
+      <c r="CE9" s="106"/>
     </row>
     <row r="10" spans="1:83" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
-      <c r="B10" s="78" t="s">
+      <c r="A10" s="81"/>
+      <c r="B10" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="37"/>
+      <c r="C10" s="88"/>
       <c r="D10" s="22">
         <v>9</v>
       </c>
@@ -22751,26 +22644,23 @@
       <c r="BU10" s="4">
         <v>24</v>
       </c>
-      <c r="BV10" s="81"/>
-      <c r="BW10" s="84"/>
-      <c r="BX10" s="87"/>
-      <c r="BY10" s="90"/>
-      <c r="BZ10" s="93"/>
-      <c r="CA10" s="81"/>
-      <c r="CB10" s="84"/>
-      <c r="CC10" s="87"/>
-      <c r="CD10" s="90"/>
-      <c r="CE10" s="111"/>
+      <c r="BV10" s="45"/>
+      <c r="BW10" s="48"/>
+      <c r="BX10" s="51"/>
+      <c r="BY10" s="54"/>
+      <c r="BZ10" s="57"/>
+      <c r="CA10" s="45"/>
+      <c r="CB10" s="48"/>
+      <c r="CC10" s="51"/>
+      <c r="CD10" s="54"/>
+      <c r="CE10" s="107"/>
     </row>
     <row r="11" spans="1:83" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
-      <c r="B11" s="94" t="str">
-        <f>+'1ER TRIMESTRE'!B11</f>
-        <v xml:space="preserve">AGUILAR ORELLANA  FREDDY JOEL </v>
-      </c>
-      <c r="C11" s="95"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="40"/>
       <c r="D11" s="11" t="s">
         <v>24</v>
       </c>
@@ -23026,11 +22916,8 @@
       <c r="A12" s="1">
         <v>2</v>
       </c>
-      <c r="B12" s="94">
-        <f>+'1ER TRIMESTRE'!B12</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="95"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
       <c r="D12" s="11" t="s">
         <v>24</v>
       </c>
@@ -23286,11 +23173,8 @@
       <c r="A13" s="1">
         <v>3</v>
       </c>
-      <c r="B13" s="94">
-        <f>+'1ER TRIMESTRE'!B13</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="95"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="40"/>
       <c r="D13" s="11" t="s">
         <v>24</v>
       </c>
@@ -23546,11 +23430,8 @@
       <c r="A14" s="1">
         <v>4</v>
       </c>
-      <c r="B14" s="94">
-        <f>+'1ER TRIMESTRE'!B14</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="95"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
       <c r="D14" s="11" t="s">
         <v>24</v>
       </c>
@@ -23806,11 +23687,8 @@
       <c r="A15" s="1">
         <v>5</v>
       </c>
-      <c r="B15" s="94">
-        <f>+'1ER TRIMESTRE'!B15</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="95"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="40"/>
       <c r="D15" s="11" t="s">
         <v>24</v>
       </c>
@@ -24066,11 +23944,8 @@
       <c r="A16" s="1">
         <v>6</v>
       </c>
-      <c r="B16" s="94">
-        <f>+'1ER TRIMESTRE'!B16</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="95"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="11" t="s">
         <v>24</v>
       </c>
@@ -24326,11 +24201,8 @@
       <c r="A17" s="1">
         <v>7</v>
       </c>
-      <c r="B17" s="94">
-        <f>+'1ER TRIMESTRE'!B17</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="95"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="11" t="s">
         <v>24</v>
       </c>
@@ -24586,11 +24458,8 @@
       <c r="A18" s="1">
         <v>8</v>
       </c>
-      <c r="B18" s="94">
-        <f>+'1ER TRIMESTRE'!B18</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="95"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="40"/>
       <c r="D18" s="11" t="s">
         <v>24</v>
       </c>
@@ -24846,11 +24715,8 @@
       <c r="A19" s="1">
         <v>9</v>
       </c>
-      <c r="B19" s="94">
-        <f>+'1ER TRIMESTRE'!B19</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="95"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="40"/>
       <c r="D19" s="11" t="s">
         <v>24</v>
       </c>
@@ -25106,11 +24972,8 @@
       <c r="A20" s="1">
         <v>10</v>
       </c>
-      <c r="B20" s="94">
-        <f>+'1ER TRIMESTRE'!B20</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="95"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
       <c r="D20" s="11" t="s">
         <v>24</v>
       </c>
@@ -25366,11 +25229,8 @@
       <c r="A21" s="1">
         <v>11</v>
       </c>
-      <c r="B21" s="94">
-        <f>+'1ER TRIMESTRE'!B21</f>
-        <v>0</v>
-      </c>
-      <c r="C21" s="95"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
       <c r="D21" s="11" t="s">
         <v>24</v>
       </c>
@@ -25626,11 +25486,8 @@
       <c r="A22" s="1">
         <v>12</v>
       </c>
-      <c r="B22" s="94">
-        <f>+'1ER TRIMESTRE'!B22</f>
-        <v>0</v>
-      </c>
-      <c r="C22" s="95"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="11" t="s">
         <v>24</v>
       </c>
@@ -25886,11 +25743,8 @@
       <c r="A23" s="1">
         <v>13</v>
       </c>
-      <c r="B23" s="94">
-        <f>+'1ER TRIMESTRE'!B23</f>
-        <v>0</v>
-      </c>
-      <c r="C23" s="95"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="11" t="s">
         <v>24</v>
       </c>
@@ -26146,11 +26000,8 @@
       <c r="A24" s="1">
         <v>14</v>
       </c>
-      <c r="B24" s="94">
-        <f>+'1ER TRIMESTRE'!B24</f>
-        <v>0</v>
-      </c>
-      <c r="C24" s="95"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
       <c r="D24" s="11" t="s">
         <v>24</v>
       </c>
@@ -26406,11 +26257,8 @@
       <c r="A25" s="1">
         <v>15</v>
       </c>
-      <c r="B25" s="94">
-        <f>+'1ER TRIMESTRE'!B25</f>
-        <v>0</v>
-      </c>
-      <c r="C25" s="95"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
       <c r="D25" s="11" t="s">
         <v>24</v>
       </c>
@@ -26666,11 +26514,8 @@
       <c r="A26" s="1">
         <v>16</v>
       </c>
-      <c r="B26" s="94">
-        <f>+'1ER TRIMESTRE'!B26</f>
-        <v>0</v>
-      </c>
-      <c r="C26" s="95"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="11" t="s">
         <v>24</v>
       </c>
@@ -26926,11 +26771,8 @@
       <c r="A27" s="1">
         <v>17</v>
       </c>
-      <c r="B27" s="94">
-        <f>+'1ER TRIMESTRE'!B27</f>
-        <v>0</v>
-      </c>
-      <c r="C27" s="95"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="11" t="s">
         <v>24</v>
       </c>
@@ -27186,11 +27028,8 @@
       <c r="A28" s="1">
         <v>18</v>
       </c>
-      <c r="B28" s="94">
-        <f>+'1ER TRIMESTRE'!B28</f>
-        <v>0</v>
-      </c>
-      <c r="C28" s="95"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="40"/>
       <c r="D28" s="11" t="s">
         <v>24</v>
       </c>
@@ -27446,11 +27285,8 @@
       <c r="A29" s="1">
         <v>19</v>
       </c>
-      <c r="B29" s="94">
-        <f>+'1ER TRIMESTRE'!B29</f>
-        <v>0</v>
-      </c>
-      <c r="C29" s="95"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="40"/>
       <c r="D29" s="11" t="s">
         <v>24</v>
       </c>
@@ -27706,11 +27542,8 @@
       <c r="A30" s="1">
         <v>20</v>
       </c>
-      <c r="B30" s="94">
-        <f>+'1ER TRIMESTRE'!B30</f>
-        <v>0</v>
-      </c>
-      <c r="C30" s="95"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="40"/>
       <c r="D30" s="11" t="s">
         <v>24</v>
       </c>
@@ -27966,11 +27799,8 @@
       <c r="A31" s="1">
         <v>21</v>
       </c>
-      <c r="B31" s="94">
-        <f>+'1ER TRIMESTRE'!B31</f>
-        <v>0</v>
-      </c>
-      <c r="C31" s="95"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="40"/>
       <c r="D31" s="11" t="s">
         <v>24</v>
       </c>
@@ -28226,11 +28056,8 @@
       <c r="A32" s="1">
         <v>22</v>
       </c>
-      <c r="B32" s="94">
-        <f>+'1ER TRIMESTRE'!B32</f>
-        <v>0</v>
-      </c>
-      <c r="C32" s="95"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="40"/>
       <c r="D32" s="11" t="s">
         <v>24</v>
       </c>
@@ -28486,11 +28313,8 @@
       <c r="A33" s="1">
         <v>23</v>
       </c>
-      <c r="B33" s="94">
-        <f>+'1ER TRIMESTRE'!B33</f>
-        <v>0</v>
-      </c>
-      <c r="C33" s="95"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="40"/>
       <c r="D33" s="11" t="s">
         <v>24</v>
       </c>
@@ -28746,11 +28570,8 @@
       <c r="A34" s="1">
         <v>24</v>
       </c>
-      <c r="B34" s="94">
-        <f>+'1ER TRIMESTRE'!B34</f>
-        <v>0</v>
-      </c>
-      <c r="C34" s="95"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="40"/>
       <c r="D34" s="11" t="s">
         <v>24</v>
       </c>
@@ -29006,11 +28827,8 @@
       <c r="A35" s="1">
         <v>25</v>
       </c>
-      <c r="B35" s="94">
-        <f>+'1ER TRIMESTRE'!B34</f>
-        <v>0</v>
-      </c>
-      <c r="C35" s="95"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="40"/>
       <c r="D35" s="11" t="s">
         <v>24</v>
       </c>
@@ -29266,11 +29084,8 @@
       <c r="A36" s="1">
         <v>26</v>
       </c>
-      <c r="B36" s="94">
-        <f>+'1ER TRIMESTRE'!B35</f>
-        <v>0</v>
-      </c>
-      <c r="C36" s="95"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="40"/>
       <c r="D36" s="11" t="s">
         <v>24</v>
       </c>
@@ -29526,11 +29341,8 @@
       <c r="A37" s="1">
         <v>27</v>
       </c>
-      <c r="B37" s="94">
-        <f>+'1ER TRIMESTRE'!B36</f>
-        <v>0</v>
-      </c>
-      <c r="C37" s="95"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="40"/>
       <c r="D37" s="11" t="s">
         <v>24</v>
       </c>
@@ -29786,11 +29598,8 @@
       <c r="A38" s="1">
         <v>28</v>
       </c>
-      <c r="B38" s="94">
-        <f>+'1ER TRIMESTRE'!B37</f>
-        <v>0</v>
-      </c>
-      <c r="C38" s="95"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="40"/>
       <c r="D38" s="11" t="s">
         <v>24</v>
       </c>
@@ -30046,11 +29855,8 @@
       <c r="A39" s="1">
         <v>29</v>
       </c>
-      <c r="B39" s="94">
-        <f>+'1ER TRIMESTRE'!B39</f>
-        <v>0</v>
-      </c>
-      <c r="C39" s="95"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="40"/>
       <c r="D39" s="11" t="s">
         <v>24</v>
       </c>
@@ -30306,11 +30112,8 @@
       <c r="A40" s="1">
         <v>30</v>
       </c>
-      <c r="B40" s="94">
-        <f>+'1ER TRIMESTRE'!B40</f>
-        <v>0</v>
-      </c>
-      <c r="C40" s="95"/>
+      <c r="B40" s="39"/>
+      <c r="C40" s="40"/>
       <c r="D40" s="14" t="s">
         <v>24</v>
       </c>
@@ -30563,13 +30366,13 @@
       </c>
     </row>
     <row r="41" spans="1:83" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="BV41" s="106" t="s">
-        <v>42</v>
-      </c>
-      <c r="BW41" s="106"/>
-      <c r="BX41" s="106"/>
-      <c r="BY41" s="106"/>
-      <c r="BZ41" s="106"/>
+      <c r="BV41" s="102" t="s">
+        <v>41</v>
+      </c>
+      <c r="BW41" s="102"/>
+      <c r="BX41" s="102"/>
+      <c r="BY41" s="102"/>
+      <c r="BZ41" s="102"/>
       <c r="CA41" s="33">
         <f>SUM(CA11:CA40)</f>
         <v>0</v>
@@ -30598,21 +30401,21 @@
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
-      <c r="D45" s="99"/>
-      <c r="E45" s="99"/>
-      <c r="F45" s="99"/>
-      <c r="G45" s="99"/>
-      <c r="H45" s="99"/>
-      <c r="I45" s="99"/>
-      <c r="J45" s="99"/>
-      <c r="K45" s="99"/>
-      <c r="L45" s="99"/>
-      <c r="M45" s="99"/>
-      <c r="N45" s="99"/>
-      <c r="O45" s="99"/>
-      <c r="P45" s="99"/>
-      <c r="Q45" s="99"/>
-      <c r="R45" s="99"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="35"/>
+      <c r="F45" s="35"/>
+      <c r="G45" s="35"/>
+      <c r="H45" s="35"/>
+      <c r="I45" s="35"/>
+      <c r="J45" s="35"/>
+      <c r="K45" s="35"/>
+      <c r="L45" s="35"/>
+      <c r="M45" s="35"/>
+      <c r="N45" s="35"/>
+      <c r="O45" s="35"/>
+      <c r="P45" s="35"/>
+      <c r="Q45" s="35"/>
+      <c r="R45" s="35"/>
       <c r="S45" s="2"/>
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
@@ -30620,48 +30423,48 @@
       <c r="W45" s="2"/>
       <c r="X45" s="2"/>
       <c r="Y45" s="2"/>
-      <c r="Z45" s="99"/>
-      <c r="AA45" s="99"/>
-      <c r="AB45" s="99"/>
-      <c r="AC45" s="99"/>
-      <c r="AD45" s="99"/>
-      <c r="AE45" s="99"/>
-      <c r="AF45" s="99"/>
-      <c r="AG45" s="99"/>
-      <c r="AH45" s="99"/>
-      <c r="AI45" s="99"/>
-      <c r="AJ45" s="99"/>
-      <c r="AK45" s="99"/>
-      <c r="AL45" s="99"/>
-      <c r="AM45" s="99"/>
-      <c r="AN45" s="99"/>
-      <c r="AS45" s="99"/>
-      <c r="AT45" s="99"/>
-      <c r="AU45" s="99"/>
-      <c r="AV45" s="99"/>
-      <c r="AW45" s="99"/>
-      <c r="AX45" s="99"/>
-      <c r="AY45" s="99"/>
-      <c r="AZ45" s="99"/>
-      <c r="BA45" s="99"/>
-      <c r="BB45" s="99"/>
-      <c r="BC45" s="99"/>
-      <c r="BD45" s="99"/>
-      <c r="BE45" s="99"/>
-      <c r="BF45" s="99"/>
-      <c r="BG45" s="99"/>
-      <c r="BL45" s="99"/>
-      <c r="BM45" s="99"/>
-      <c r="BN45" s="99"/>
-      <c r="BO45" s="99"/>
-      <c r="BP45" s="99"/>
-      <c r="BQ45" s="99"/>
-      <c r="BR45" s="99"/>
-      <c r="BS45" s="99"/>
-      <c r="BT45" s="99"/>
-      <c r="BU45" s="99"/>
-      <c r="BV45" s="99"/>
-      <c r="BW45" s="99"/>
+      <c r="Z45" s="35"/>
+      <c r="AA45" s="35"/>
+      <c r="AB45" s="35"/>
+      <c r="AC45" s="35"/>
+      <c r="AD45" s="35"/>
+      <c r="AE45" s="35"/>
+      <c r="AF45" s="35"/>
+      <c r="AG45" s="35"/>
+      <c r="AH45" s="35"/>
+      <c r="AI45" s="35"/>
+      <c r="AJ45" s="35"/>
+      <c r="AK45" s="35"/>
+      <c r="AL45" s="35"/>
+      <c r="AM45" s="35"/>
+      <c r="AN45" s="35"/>
+      <c r="AS45" s="35"/>
+      <c r="AT45" s="35"/>
+      <c r="AU45" s="35"/>
+      <c r="AV45" s="35"/>
+      <c r="AW45" s="35"/>
+      <c r="AX45" s="35"/>
+      <c r="AY45" s="35"/>
+      <c r="AZ45" s="35"/>
+      <c r="BA45" s="35"/>
+      <c r="BB45" s="35"/>
+      <c r="BC45" s="35"/>
+      <c r="BD45" s="35"/>
+      <c r="BE45" s="35"/>
+      <c r="BF45" s="35"/>
+      <c r="BG45" s="35"/>
+      <c r="BL45" s="35"/>
+      <c r="BM45" s="35"/>
+      <c r="BN45" s="35"/>
+      <c r="BO45" s="35"/>
+      <c r="BP45" s="35"/>
+      <c r="BQ45" s="35"/>
+      <c r="BR45" s="35"/>
+      <c r="BS45" s="35"/>
+      <c r="BT45" s="35"/>
+      <c r="BU45" s="35"/>
+      <c r="BV45" s="35"/>
+      <c r="BW45" s="35"/>
       <c r="BX45" s="27"/>
       <c r="BY45" s="27"/>
       <c r="BZ45" s="27"/>
@@ -30670,141 +30473,141 @@
       <c r="CC45" s="28"/>
     </row>
     <row r="46" spans="1:83" s="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D46" s="100" t="s">
-        <v>54</v>
-      </c>
-      <c r="E46" s="100"/>
-      <c r="F46" s="100"/>
-      <c r="G46" s="100"/>
-      <c r="H46" s="100"/>
-      <c r="I46" s="100"/>
-      <c r="J46" s="100"/>
-      <c r="K46" s="100"/>
-      <c r="L46" s="100"/>
-      <c r="M46" s="100"/>
-      <c r="N46" s="100"/>
-      <c r="O46" s="100"/>
-      <c r="P46" s="100"/>
-      <c r="Q46" s="100"/>
-      <c r="R46" s="100"/>
-      <c r="Z46" s="100" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA46" s="100"/>
-      <c r="AB46" s="100"/>
-      <c r="AC46" s="100"/>
-      <c r="AD46" s="100"/>
-      <c r="AE46" s="100"/>
-      <c r="AF46" s="100"/>
-      <c r="AG46" s="100"/>
-      <c r="AH46" s="100"/>
-      <c r="AI46" s="100"/>
-      <c r="AJ46" s="100"/>
-      <c r="AK46" s="100"/>
-      <c r="AL46" s="100"/>
-      <c r="AM46" s="100"/>
-      <c r="AN46" s="100"/>
-      <c r="AS46" s="100" t="s">
-        <v>31</v>
-      </c>
-      <c r="AT46" s="100"/>
-      <c r="AU46" s="100"/>
-      <c r="AV46" s="100"/>
-      <c r="AW46" s="100"/>
-      <c r="AX46" s="100"/>
-      <c r="AY46" s="100"/>
-      <c r="AZ46" s="100"/>
-      <c r="BA46" s="100"/>
-      <c r="BB46" s="100"/>
-      <c r="BC46" s="100"/>
-      <c r="BD46" s="100"/>
-      <c r="BE46" s="100"/>
-      <c r="BF46" s="100"/>
-      <c r="BG46" s="100"/>
-      <c r="BL46" s="101" t="s">
+      <c r="D46" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="BM46" s="101"/>
-      <c r="BN46" s="101"/>
-      <c r="BO46" s="101"/>
-      <c r="BP46" s="101"/>
-      <c r="BQ46" s="101"/>
-      <c r="BR46" s="101"/>
-      <c r="BS46" s="101"/>
-      <c r="BT46" s="101"/>
-      <c r="BU46" s="101"/>
-      <c r="BV46" s="101"/>
-      <c r="BW46" s="101"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="36"/>
+      <c r="M46" s="36"/>
+      <c r="N46" s="36"/>
+      <c r="O46" s="36"/>
+      <c r="P46" s="36"/>
+      <c r="Q46" s="36"/>
+      <c r="R46" s="36"/>
+      <c r="Z46" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA46" s="36"/>
+      <c r="AB46" s="36"/>
+      <c r="AC46" s="36"/>
+      <c r="AD46" s="36"/>
+      <c r="AE46" s="36"/>
+      <c r="AF46" s="36"/>
+      <c r="AG46" s="36"/>
+      <c r="AH46" s="36"/>
+      <c r="AI46" s="36"/>
+      <c r="AJ46" s="36"/>
+      <c r="AK46" s="36"/>
+      <c r="AL46" s="36"/>
+      <c r="AM46" s="36"/>
+      <c r="AN46" s="36"/>
+      <c r="AS46" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT46" s="36"/>
+      <c r="AU46" s="36"/>
+      <c r="AV46" s="36"/>
+      <c r="AW46" s="36"/>
+      <c r="AX46" s="36"/>
+      <c r="AY46" s="36"/>
+      <c r="AZ46" s="36"/>
+      <c r="BA46" s="36"/>
+      <c r="BB46" s="36"/>
+      <c r="BC46" s="36"/>
+      <c r="BD46" s="36"/>
+      <c r="BE46" s="36"/>
+      <c r="BF46" s="36"/>
+      <c r="BG46" s="36"/>
+      <c r="BL46" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="BM46" s="38"/>
+      <c r="BN46" s="38"/>
+      <c r="BO46" s="38"/>
+      <c r="BP46" s="38"/>
+      <c r="BQ46" s="38"/>
+      <c r="BR46" s="38"/>
+      <c r="BS46" s="38"/>
+      <c r="BT46" s="38"/>
+      <c r="BU46" s="38"/>
+      <c r="BV46" s="38"/>
+      <c r="BW46" s="38"/>
       <c r="BX46" s="32"/>
       <c r="BY46" s="32"/>
       <c r="BZ46" s="32"/>
     </row>
     <row r="47" spans="1:83" s="29" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D47" s="96" t="s">
+      <c r="D47" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="E47" s="96"/>
-      <c r="F47" s="96"/>
-      <c r="G47" s="96"/>
-      <c r="H47" s="96"/>
-      <c r="I47" s="96"/>
-      <c r="J47" s="96"/>
-      <c r="K47" s="96"/>
-      <c r="L47" s="96"/>
-      <c r="M47" s="96"/>
-      <c r="N47" s="96"/>
-      <c r="O47" s="96"/>
-      <c r="P47" s="96"/>
-      <c r="Q47" s="96"/>
-      <c r="R47" s="96"/>
-      <c r="Z47" s="96" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA47" s="96"/>
-      <c r="AB47" s="96"/>
-      <c r="AC47" s="96"/>
-      <c r="AD47" s="96"/>
-      <c r="AE47" s="96"/>
-      <c r="AF47" s="96"/>
-      <c r="AG47" s="96"/>
-      <c r="AH47" s="96"/>
-      <c r="AI47" s="96"/>
-      <c r="AJ47" s="96"/>
-      <c r="AK47" s="96"/>
-      <c r="AL47" s="96"/>
-      <c r="AM47" s="96"/>
-      <c r="AN47" s="96"/>
-      <c r="AS47" s="96" t="s">
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="37"/>
+      <c r="I47" s="37"/>
+      <c r="J47" s="37"/>
+      <c r="K47" s="37"/>
+      <c r="L47" s="37"/>
+      <c r="M47" s="37"/>
+      <c r="N47" s="37"/>
+      <c r="O47" s="37"/>
+      <c r="P47" s="37"/>
+      <c r="Q47" s="37"/>
+      <c r="R47" s="37"/>
+      <c r="Z47" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA47" s="37"/>
+      <c r="AB47" s="37"/>
+      <c r="AC47" s="37"/>
+      <c r="AD47" s="37"/>
+      <c r="AE47" s="37"/>
+      <c r="AF47" s="37"/>
+      <c r="AG47" s="37"/>
+      <c r="AH47" s="37"/>
+      <c r="AI47" s="37"/>
+      <c r="AJ47" s="37"/>
+      <c r="AK47" s="37"/>
+      <c r="AL47" s="37"/>
+      <c r="AM47" s="37"/>
+      <c r="AN47" s="37"/>
+      <c r="AS47" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="AT47" s="37"/>
+      <c r="AU47" s="37"/>
+      <c r="AV47" s="37"/>
+      <c r="AW47" s="37"/>
+      <c r="AX47" s="37"/>
+      <c r="AY47" s="37"/>
+      <c r="AZ47" s="37"/>
+      <c r="BA47" s="37"/>
+      <c r="BB47" s="37"/>
+      <c r="BC47" s="37"/>
+      <c r="BD47" s="37"/>
+      <c r="BE47" s="37"/>
+      <c r="BF47" s="37"/>
+      <c r="BG47" s="37"/>
+      <c r="BL47" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="AT47" s="96"/>
-      <c r="AU47" s="96"/>
-      <c r="AV47" s="96"/>
-      <c r="AW47" s="96"/>
-      <c r="AX47" s="96"/>
-      <c r="AY47" s="96"/>
-      <c r="AZ47" s="96"/>
-      <c r="BA47" s="96"/>
-      <c r="BB47" s="96"/>
-      <c r="BC47" s="96"/>
-      <c r="BD47" s="96"/>
-      <c r="BE47" s="96"/>
-      <c r="BF47" s="96"/>
-      <c r="BG47" s="96"/>
-      <c r="BL47" s="96" t="s">
-        <v>33</v>
-      </c>
-      <c r="BM47" s="96"/>
-      <c r="BN47" s="96"/>
-      <c r="BO47" s="96"/>
-      <c r="BP47" s="96"/>
-      <c r="BQ47" s="96"/>
-      <c r="BR47" s="96"/>
-      <c r="BS47" s="96"/>
-      <c r="BT47" s="96"/>
-      <c r="BU47" s="96"/>
-      <c r="BV47" s="96"/>
-      <c r="BW47" s="96"/>
+      <c r="BM47" s="37"/>
+      <c r="BN47" s="37"/>
+      <c r="BO47" s="37"/>
+      <c r="BP47" s="37"/>
+      <c r="BQ47" s="37"/>
+      <c r="BR47" s="37"/>
+      <c r="BS47" s="37"/>
+      <c r="BT47" s="37"/>
+      <c r="BU47" s="37"/>
+      <c r="BV47" s="37"/>
+      <c r="BW47" s="37"/>
       <c r="BX47" s="30"/>
       <c r="BY47" s="30"/>
       <c r="BZ47" s="30"/>
@@ -31765,6 +31568,65 @@
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="75">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D47:R47"/>
+    <mergeCell ref="Z47:AN47"/>
+    <mergeCell ref="AS47:BG47"/>
+    <mergeCell ref="BL47:BW47"/>
+    <mergeCell ref="D45:R45"/>
+    <mergeCell ref="Z45:AN45"/>
+    <mergeCell ref="AS45:BG45"/>
+    <mergeCell ref="BL45:BW45"/>
+    <mergeCell ref="D46:R46"/>
+    <mergeCell ref="Z46:AN46"/>
+    <mergeCell ref="AS46:BG46"/>
+    <mergeCell ref="BL46:BW46"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:S6"/>
+    <mergeCell ref="T6:AK6"/>
+    <mergeCell ref="AL6:BE6"/>
+    <mergeCell ref="BF6:BU6"/>
+    <mergeCell ref="A1:BZ1"/>
+    <mergeCell ref="A2:BZ2"/>
+    <mergeCell ref="A3:BZ3"/>
+    <mergeCell ref="A4:BZ4"/>
+    <mergeCell ref="A5:BZ5"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:S8"/>
+    <mergeCell ref="T7:AK8"/>
+    <mergeCell ref="AL7:BE8"/>
+    <mergeCell ref="BF7:BU8"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="D9:S9"/>
+    <mergeCell ref="T9:AK9"/>
+    <mergeCell ref="AL9:BE9"/>
+    <mergeCell ref="BF9:BU9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="BV41:BZ41"/>
@@ -31781,65 +31643,6 @@
     <mergeCell ref="CD6:CD10"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:S8"/>
-    <mergeCell ref="T7:AK8"/>
-    <mergeCell ref="AL7:BE8"/>
-    <mergeCell ref="BF7:BU8"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="D9:S9"/>
-    <mergeCell ref="T9:AK9"/>
-    <mergeCell ref="AL9:BE9"/>
-    <mergeCell ref="BF9:BU9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="A1:BZ1"/>
-    <mergeCell ref="A2:BZ2"/>
-    <mergeCell ref="A3:BZ3"/>
-    <mergeCell ref="A4:BZ4"/>
-    <mergeCell ref="A5:BZ5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:S6"/>
-    <mergeCell ref="T6:AK6"/>
-    <mergeCell ref="AL6:BE6"/>
-    <mergeCell ref="BF6:BU6"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D47:R47"/>
-    <mergeCell ref="Z47:AN47"/>
-    <mergeCell ref="AS47:BG47"/>
-    <mergeCell ref="BL47:BW47"/>
-    <mergeCell ref="D45:R45"/>
-    <mergeCell ref="Z45:AN45"/>
-    <mergeCell ref="AS45:BG45"/>
-    <mergeCell ref="BL45:BW45"/>
-    <mergeCell ref="D46:R46"/>
-    <mergeCell ref="Z46:AN46"/>
-    <mergeCell ref="AS46:BG46"/>
-    <mergeCell ref="BL46:BW46"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <conditionalFormatting sqref="D11:BU40">
     <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="F">
